--- a/docs/dataroom/sold-direct-model.xlsx
+++ b/docs/dataroom/sold-direct-model.xlsx
@@ -561,7 +561,7 @@
     <row r="5">
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Bond referral rate (% of bond)</t>
+          <t>Bond referral / facilitation-fee rate (% of value)</t>
         </is>
       </c>
       <c r="C5" s="5" t="n">
@@ -684,7 +684,7 @@
     <row r="15">
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Bonded share of deals</t>
+          <t>Bonded share (qualifying ≥80% bond → free)</t>
         </is>
       </c>
       <c r="C15" s="5" t="n">
@@ -733,7 +733,7 @@
     <row r="17">
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>Bond referral / bonded deal (R)</t>
+          <t>Referral per bonded deal (R) = rate x bond</t>
         </is>
       </c>
       <c r="C17" s="13">
@@ -760,27 +760,27 @@
     <row r="18">
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>Bond referral / deal, blended (R)</t>
+          <t>Bond referral OR 0.5% fee / deal, blended (R)</t>
         </is>
       </c>
       <c r="C18" s="13">
-        <f>C17*C15</f>
+        <f>C17*C15+(1-C15)*$C$5*C14*1000000</f>
         <v/>
       </c>
       <c r="D18" s="13">
-        <f>D17*D15</f>
+        <f>D17*D15+(1-D15)*$C$5*D14*1000000</f>
         <v/>
       </c>
       <c r="E18" s="13">
-        <f>E17*E15</f>
+        <f>E17*E15+(1-E15)*$C$5*E14*1000000</f>
         <v/>
       </c>
       <c r="F18" s="13">
-        <f>F17*F15</f>
+        <f>F17*F15+(1-F15)*$C$5*F14*1000000</f>
         <v/>
       </c>
       <c r="G18" s="13">
-        <f>G17*G15</f>
+        <f>G17*G15+(1-G15)*$C$5*G14*1000000</f>
         <v/>
       </c>
     </row>
@@ -2859,7 +2859,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:B19"/>
+  <dimension ref="B1:B23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="2" max="2"/>
@@ -2893,90 +2893,114 @@
       <c r="B5" s="33" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="B6" s="35" t="inlineStr">
-        <is>
-          <t>KEY SOURCED ANCHORS (see docs/dataroom/00-assumptions.md for full citations &amp; reliability flags):</t>
+      <c r="B6" s="34" t="inlineStr">
+        <is>
+          <t>MONETISATION POLICY (every deal pays ~0.5% of value): the free 0% tier requires a qualifying bond (&gt;=80% LTV) so we earn the</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="33" t="inlineStr">
         <is>
-          <t>• Cape Town: median ~R3.4m, average ~R2.1m; R6m+ = prime freehold band (Lightstone / Property24, 2024–26).</t>
+          <t>bank-paid origination referral. Cash buyers / sub-80% bonds instead pay a 0.5% facilitation fee on the price — still ~10-14x</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="33" t="inlineStr">
         <is>
-          <t>• ~50% of SA transfers are bonded; prime skews more cash — model uses 40% bonded (Lightstone 2024).</t>
+          <t>cheaper than 5-7% agent commission. This removes the cash-deal revenue gap; bonded-share becomes a minor mix assumption, not a cliff.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="33" t="inlineStr">
-        <is>
-          <t>• Bond origination commission paid by banks 1.0–1.9% of loan; referral-partner share ~0.5% (ooba / IOL).</t>
-        </is>
-      </c>
+      <c r="B9" s="33" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="B10" s="33" t="inlineStr">
-        <is>
-          <t>• Estate-agency commission 5–7% + 15% VAT — the consumer saving Sold Direct displaces (Private Property).</t>
+      <c r="B10" s="35" t="inlineStr">
+        <is>
+          <t>KEY SOURCED ANCHORS (see docs/dataroom/00-assumptions.md for full citations &amp; reliability flags):</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="33" t="inlineStr">
         <is>
-          <t>• WhatsApp service/utility within 24h = free; marketing templates the main paid line (Meta, Jul 2025).</t>
+          <t>• Cape Town: median ~R3.4m, average ~R2.1m; R6m+ = prime freehold band (Lightstone / Property24, 2024–26).</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="33" t="inlineStr">
         <is>
-          <t>• Proptech ~8.8x EV/revenue globally — discounted to 4–6x for SA early stage (Finro 2025).</t>
+          <t>• ~50% of SA transfers are bonded; prime skews more cash — model uses 40% bonded (Lightstone 2024).</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="33" t="inlineStr">
         <is>
-          <t>• Salaries: eng intermediate ~R48k/mo, senior ~R100k/mo; +~30% load for 13th cheque/benefits (OfferZen 2025).</t>
+          <t>• Bond origination commission paid by banks 1.0–1.9% of loan; referral-partner share ~0.5% (ooba / IOL).</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="33" t="inlineStr">
         <is>
-          <t>• Cautionary comp: Purplebricks (IPO £240m → peak &gt;£1bn → sold for £1, 2023) — CAC discipline is rule #1.</t>
+          <t>• Estate-agency commission 5–7% + 15% VAT — the consumer saving Sold Direct displaces (Private Property).</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="33" t="inlineStr"/>
+      <c r="B15" s="33" t="inlineStr">
+        <is>
+          <t>• WhatsApp service/utility within 24h = free; marketing templates the main paid line (Meta, Jul 2025).</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="B16" s="35" t="inlineStr">
-        <is>
-          <t>CONFIRM BEFORE INVESTOR CIRCULATION (model-grade, not audit-grade):</t>
+      <c r="B16" s="33" t="inlineStr">
+        <is>
+          <t>• Proptech ~8.8x EV/revenue globally — discounted to 4–6x for SA early stage (Finro 2025).</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="33" t="inlineStr">
         <is>
+          <t>• Salaries: eng intermediate ~R48k/mo, senior ~R100k/mo; +~30% load for 13th cheque/benefits (OfferZen 2025).</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="33" t="inlineStr">
+        <is>
+          <t>• Cautionary comp: Purplebricks (IPO £240m → peak &gt;£1bn → sold for £1, 2023) — CAC discipline is rule #1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="33" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="B20" s="35" t="inlineStr">
+        <is>
+          <t>CONFIRM BEFORE INVESTOR CIRCULATION (model-grade, not audit-grade):</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="33" t="inlineStr">
+        <is>
           <t>1. 0.5% bond referral share (ooba)   2. conveyancing panel %   3. prime transfer counts   4. bonded share in prime.</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="B18" s="33" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="B19" s="34" t="inlineStr">
+    <row r="22">
+      <c r="B22" s="33" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="B23" s="34" t="inlineStr">
         <is>
           <t>HOW TO USE: edit amber cells on the Assumptions tab. P&amp;L, Scenarios and Valuation recalculate automatically.</t>
         </is>

--- a/docs/dataroom/sold-direct-model.xlsx
+++ b/docs/dataroom/sold-direct-model.xlsx
@@ -20,11 +20,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="#,##0.0"/>
-    <numFmt numFmtId="166" formatCode="0.0"/>
-    <numFmt numFmtId="167" formatCode="R#,##0"/>
+    <numFmt numFmtId="166" formatCode="R#,##0"/>
   </numFmts>
   <fonts count="8">
     <font>
@@ -106,7 +105,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -114,24 +113,23 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="5" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="5" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="5" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="7" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="7" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="5" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="7" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="7" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -139,7 +137,7 @@
     <xf numFmtId="4" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -519,10 +517,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:H48"/>
+  <dimension ref="B1:H54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
@@ -534,14 +532,14 @@
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Sold Direct — Model Assumptions (Prime / Upper-Market Focus)</t>
+          <t>Sold Direct — Model Assumptions (Prime · Nedbank-0% · AI-lean)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Amber cells = editable inputs. Grey = calculated. All other tabs link to this one.</t>
+          <t>Amber = editable input. Grey = calculated. Every other tab links here.</t>
         </is>
       </c>
     </row>
@@ -561,7 +559,7 @@
     <row r="5">
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Bond referral / facilitation-fee rate (% of value)</t>
+          <t>Nedbank partner kickback (% of bond)</t>
         </is>
       </c>
       <c r="C5" s="5" t="n">
@@ -571,707 +569,839 @@
     <row r="6">
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Gross margin</t>
+          <t>Facilitation fee — non-partner deals (% of price)</t>
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>0.88</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>ZAR per USD</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="n">
-        <v>18.5</v>
+          <t>Gross margin</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.88</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Valuation multiple — low (x revenue)</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="n">
-        <v>4</v>
+          <t>ZAR per USD</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>18.5</v>
       </c>
     </row>
     <row r="9">
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Valuation multiple — high (x revenue)</t>
-        </is>
-      </c>
-      <c r="C9" s="7" t="n">
-        <v>6</v>
+          <t>Valuation multiple — low (x revenue)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="4" t="inlineStr">
         <is>
+          <t>Valuation multiple — high (x revenue)</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="4" t="inlineStr">
+        <is>
           <t>Working-capital / contingency buffer (Rm)</t>
         </is>
       </c>
-      <c r="C10" s="8" t="n">
+      <c r="C11" s="7" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="12">
-      <c r="B12" s="3" t="inlineStr">
+    <row r="13">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>PER-YEAR REVENUE DRIVERS (BASE)</t>
         </is>
       </c>
-      <c r="C12" s="3" t="n"/>
-      <c r="D12" s="3" t="n"/>
-      <c r="E12" s="3" t="n"/>
-      <c r="F12" s="3" t="n"/>
-      <c r="G12" s="3" t="n"/>
-      <c r="H12" s="3" t="n"/>
-    </row>
-    <row r="13">
-      <c r="B13" s="9" t="inlineStr"/>
-      <c r="C13" s="10" t="inlineStr">
+      <c r="C13" s="3" t="n"/>
+      <c r="D13" s="3" t="n"/>
+      <c r="E13" s="3" t="n"/>
+      <c r="F13" s="3" t="n"/>
+      <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
+    </row>
+    <row r="14">
+      <c r="C14" s="8" t="inlineStr">
         <is>
           <t>Y1</t>
         </is>
       </c>
-      <c r="D13" s="10" t="inlineStr">
+      <c r="D14" s="8" t="inlineStr">
         <is>
           <t>Y2</t>
         </is>
       </c>
-      <c r="E13" s="10" t="inlineStr">
+      <c r="E14" s="8" t="inlineStr">
         <is>
           <t>Y3</t>
         </is>
       </c>
-      <c r="F13" s="10" t="inlineStr">
+      <c r="F14" s="8" t="inlineStr">
         <is>
           <t>Y4</t>
         </is>
       </c>
-      <c r="G13" s="10" t="inlineStr">
+      <c r="G14" s="8" t="inlineStr">
         <is>
           <t>Y5</t>
         </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>Avg transacting price (Rm)</t>
-        </is>
-      </c>
-      <c r="C14" s="8" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="D14" s="8" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="E14" s="8" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="F14" s="8" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="G14" s="8" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Bonded share (qualifying ≥80% bond → free)</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="n">
+          <t>Avg transacting price (Rm)</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="D15" s="7" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="E15" s="7" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="F15" s="7" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="G15" s="7" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Bonded-with-Nedbank share (&gt;=80% -&gt; free)</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
         <v>0.4</v>
       </c>
-      <c r="D15" s="5" t="n">
+      <c r="D16" s="5" t="n">
         <v>0.4</v>
       </c>
-      <c r="E15" s="5" t="n">
+      <c r="E16" s="5" t="n">
         <v>0.4</v>
       </c>
-      <c r="F15" s="5" t="n">
+      <c r="F16" s="5" t="n">
         <v>0.42</v>
       </c>
-      <c r="G15" s="5" t="n">
+      <c r="G16" s="5" t="n">
         <v>0.42</v>
       </c>
     </row>
-    <row r="16">
-      <c r="B16" s="11" t="inlineStr">
+    <row r="17">
+      <c r="B17" s="9" t="inlineStr">
         <is>
           <t>Bond size = 90% of price (Rm)</t>
         </is>
       </c>
-      <c r="C16" s="12">
-        <f>C14*0.9</f>
-        <v/>
-      </c>
-      <c r="D16" s="12">
-        <f>D14*0.9</f>
-        <v/>
-      </c>
-      <c r="E16" s="12">
-        <f>E14*0.9</f>
-        <v/>
-      </c>
-      <c r="F16" s="12">
-        <f>F14*0.9</f>
-        <v/>
-      </c>
-      <c r="G16" s="12">
-        <f>G14*0.9</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" s="11" t="inlineStr">
-        <is>
-          <t>Referral per bonded deal (R) = rate x bond</t>
-        </is>
-      </c>
-      <c r="C17" s="13">
-        <f>C16*1000000*$C$5</f>
-        <v/>
-      </c>
-      <c r="D17" s="13">
-        <f>D16*1000000*$C$5</f>
-        <v/>
-      </c>
-      <c r="E17" s="13">
-        <f>E16*1000000*$C$5</f>
-        <v/>
-      </c>
-      <c r="F17" s="13">
-        <f>F16*1000000*$C$5</f>
-        <v/>
-      </c>
-      <c r="G17" s="13">
-        <f>G16*1000000*$C$5</f>
+      <c r="C17" s="10">
+        <f>C15*0.9</f>
+        <v/>
+      </c>
+      <c r="D17" s="10">
+        <f>D15*0.9</f>
+        <v/>
+      </c>
+      <c r="E17" s="10">
+        <f>E15*0.9</f>
+        <v/>
+      </c>
+      <c r="F17" s="10">
+        <f>F15*0.9</f>
+        <v/>
+      </c>
+      <c r="G17" s="10">
+        <f>G15*0.9</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="11" t="inlineStr">
-        <is>
-          <t>Bond referral OR 0.5% fee / deal, blended (R)</t>
-        </is>
-      </c>
-      <c r="C18" s="13">
-        <f>C17*C15+(1-C15)*$C$5*C14*1000000</f>
-        <v/>
-      </c>
-      <c r="D18" s="13">
-        <f>D17*D15+(1-D15)*$C$5*D14*1000000</f>
-        <v/>
-      </c>
-      <c r="E18" s="13">
-        <f>E17*E15+(1-E15)*$C$5*E14*1000000</f>
-        <v/>
-      </c>
-      <c r="F18" s="13">
-        <f>F17*F15+(1-F15)*$C$5*F14*1000000</f>
-        <v/>
-      </c>
-      <c r="G18" s="13">
-        <f>G17*G15+(1-G15)*$C$5*G14*1000000</f>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>Nedbank kickback / qualifying deal (R)</t>
+        </is>
+      </c>
+      <c r="C18" s="11">
+        <f>C17*1000000*$C$5</f>
+        <v/>
+      </c>
+      <c r="D18" s="11">
+        <f>D17*1000000*$C$5</f>
+        <v/>
+      </c>
+      <c r="E18" s="11">
+        <f>E17*1000000*$C$5</f>
+        <v/>
+      </c>
+      <c r="F18" s="11">
+        <f>F17*1000000*$C$5</f>
+        <v/>
+      </c>
+      <c r="G18" s="11">
+        <f>G17*1000000*$C$5</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>Facilitation fee / non-partner deal (R)</t>
+        </is>
+      </c>
+      <c r="C19" s="11">
+        <f>C15*1000000*$C$6</f>
+        <v/>
+      </c>
+      <c r="D19" s="11">
+        <f>D15*1000000*$C$6</f>
+        <v/>
+      </c>
+      <c r="E19" s="11">
+        <f>E15*1000000*$C$6</f>
+        <v/>
+      </c>
+      <c r="F19" s="11">
+        <f>F15*1000000*$C$6</f>
+        <v/>
+      </c>
+      <c r="G19" s="11">
+        <f>G15*1000000*$C$6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>Kickback OR fee / deal, blended (R)</t>
+        </is>
+      </c>
+      <c r="C20" s="11">
+        <f>C16*C18+(1-C16)*C19</f>
+        <v/>
+      </c>
+      <c r="D20" s="11">
+        <f>D16*D18+(1-D16)*D19</f>
+        <v/>
+      </c>
+      <c r="E20" s="11">
+        <f>E16*E18+(1-E16)*E19</f>
+        <v/>
+      </c>
+      <c r="F20" s="11">
+        <f>F16*F18+(1-F16)*F19</f>
+        <v/>
+      </c>
+      <c r="G20" s="11">
+        <f>G16*G18+(1-G16)*G19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>Conveyancing referral / deal (R)</t>
         </is>
       </c>
-      <c r="C19" s="14" t="n">
+      <c r="C21" s="12" t="n">
         <v>9000</v>
       </c>
-      <c r="D19" s="14" t="n">
+      <c r="D21" s="12" t="n">
         <v>9000</v>
       </c>
-      <c r="E19" s="14" t="n">
+      <c r="E21" s="12" t="n">
         <v>9500</v>
       </c>
-      <c r="F19" s="14" t="n">
+      <c r="F21" s="12" t="n">
         <v>10000</v>
       </c>
-      <c r="G19" s="14" t="n">
+      <c r="G21" s="12" t="n">
         <v>10000</v>
       </c>
     </row>
-    <row r="20">
-      <c r="B20" s="4" t="inlineStr">
+    <row r="22">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>Add-ons / deal (R)</t>
         </is>
       </c>
-      <c r="C20" s="14" t="n">
+      <c r="C22" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="D20" s="14" t="n">
+      <c r="D22" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E20" s="14" t="n">
+      <c r="E22" s="12" t="n">
         <v>5500</v>
       </c>
-      <c r="F20" s="14" t="n">
+      <c r="F22" s="12" t="n">
         <v>6000</v>
       </c>
-      <c r="G20" s="14" t="n">
+      <c r="G22" s="12" t="n">
         <v>6500</v>
       </c>
     </row>
-    <row r="21">
-      <c r="B21" s="15" t="inlineStr">
+    <row r="23">
+      <c r="B23" s="13" t="inlineStr">
         <is>
           <t>Revenue per deal (R)</t>
         </is>
       </c>
-      <c r="C21" s="16">
-        <f>C18+C19+C20</f>
-        <v/>
-      </c>
-      <c r="D21" s="16">
-        <f>D18+D19+D20</f>
-        <v/>
-      </c>
-      <c r="E21" s="16">
-        <f>E18+E19+E20</f>
-        <v/>
-      </c>
-      <c r="F21" s="16">
-        <f>F18+F19+F20</f>
-        <v/>
-      </c>
-      <c r="G21" s="16">
-        <f>G18+G19+G20</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="3" t="inlineStr">
+      <c r="C23" s="14">
+        <f>C20+C21+C22</f>
+        <v/>
+      </c>
+      <c r="D23" s="14">
+        <f>D20+D21+D22</f>
+        <v/>
+      </c>
+      <c r="E23" s="14">
+        <f>E20+E21+E22</f>
+        <v/>
+      </c>
+      <c r="F23" s="14">
+        <f>F20+F21+F22</f>
+        <v/>
+      </c>
+      <c r="G23" s="14">
+        <f>G20+G21+G22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="3" t="inlineStr">
         <is>
           <t>REGISTERED DEALS BY SCENARIO</t>
         </is>
       </c>
-      <c r="C23" s="3" t="n"/>
-      <c r="D23" s="3" t="n"/>
-      <c r="E23" s="3" t="n"/>
-      <c r="F23" s="3" t="n"/>
-      <c r="G23" s="3" t="n"/>
-      <c r="H23" s="3" t="n"/>
-    </row>
-    <row r="24">
-      <c r="B24" s="9" t="inlineStr"/>
-      <c r="C24" s="10" t="inlineStr">
+      <c r="C25" s="3" t="n"/>
+      <c r="D25" s="3" t="n"/>
+      <c r="E25" s="3" t="n"/>
+      <c r="F25" s="3" t="n"/>
+      <c r="G25" s="3" t="n"/>
+      <c r="H25" s="3" t="n"/>
+    </row>
+    <row r="26">
+      <c r="C26" s="8" t="inlineStr">
         <is>
           <t>Y1</t>
         </is>
       </c>
-      <c r="D24" s="10" t="inlineStr">
+      <c r="D26" s="8" t="inlineStr">
         <is>
           <t>Y2</t>
         </is>
       </c>
-      <c r="E24" s="10" t="inlineStr">
+      <c r="E26" s="8" t="inlineStr">
         <is>
           <t>Y3</t>
         </is>
       </c>
-      <c r="F24" s="10" t="inlineStr">
+      <c r="F26" s="8" t="inlineStr">
         <is>
           <t>Y4</t>
         </is>
       </c>
-      <c r="G24" s="10" t="inlineStr">
+      <c r="G26" s="8" t="inlineStr">
         <is>
           <t>Y5</t>
         </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>Conservative</t>
-        </is>
-      </c>
-      <c r="C25" s="17" t="n">
-        <v>25</v>
-      </c>
-      <c r="D25" s="17" t="n">
-        <v>100</v>
-      </c>
-      <c r="E25" s="17" t="n">
-        <v>280</v>
-      </c>
-      <c r="F25" s="17" t="n">
-        <v>550</v>
-      </c>
-      <c r="G25" s="17" t="n">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>Base</t>
-        </is>
-      </c>
-      <c r="C26" s="17" t="n">
-        <v>40</v>
-      </c>
-      <c r="D26" s="17" t="n">
-        <v>160</v>
-      </c>
-      <c r="E26" s="17" t="n">
-        <v>450</v>
-      </c>
-      <c r="F26" s="17" t="n">
-        <v>900</v>
-      </c>
-      <c r="G26" s="17" t="n">
-        <v>1600</v>
       </c>
     </row>
     <row r="27">
       <c r="B27" s="4" t="inlineStr">
         <is>
+          <t>Conservative</t>
+        </is>
+      </c>
+      <c r="C27" s="15" t="n">
+        <v>25</v>
+      </c>
+      <c r="D27" s="15" t="n">
+        <v>100</v>
+      </c>
+      <c r="E27" s="15" t="n">
+        <v>280</v>
+      </c>
+      <c r="F27" s="15" t="n">
+        <v>550</v>
+      </c>
+      <c r="G27" s="15" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="C28" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="D28" s="15" t="n">
+        <v>160</v>
+      </c>
+      <c r="E28" s="15" t="n">
+        <v>450</v>
+      </c>
+      <c r="F28" s="15" t="n">
+        <v>900</v>
+      </c>
+      <c r="G28" s="15" t="n">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="4" t="inlineStr">
+        <is>
           <t>Aggressive</t>
         </is>
       </c>
-      <c r="C27" s="17" t="n">
+      <c r="C29" s="15" t="n">
         <v>60</v>
       </c>
-      <c r="D27" s="17" t="n">
+      <c r="D29" s="15" t="n">
         <v>250</v>
       </c>
-      <c r="E27" s="17" t="n">
+      <c r="E29" s="15" t="n">
         <v>700</v>
       </c>
-      <c r="F27" s="17" t="n">
+      <c r="F29" s="15" t="n">
         <v>1400</v>
       </c>
-      <c r="G27" s="17" t="n">
+      <c r="G29" s="15" t="n">
         <v>2600</v>
       </c>
     </row>
-    <row r="29">
-      <c r="B29" s="3" t="inlineStr">
+    <row r="31">
+      <c r="B31" s="3" t="inlineStr">
         <is>
           <t>REVENUE/DEAL MULTIPLIER BY SCENARIO</t>
         </is>
       </c>
-      <c r="C29" s="3" t="n"/>
-      <c r="D29" s="3" t="n"/>
-      <c r="E29" s="3" t="n"/>
-      <c r="F29" s="3" t="n"/>
-      <c r="G29" s="3" t="n"/>
-      <c r="H29" s="3" t="n"/>
-    </row>
-    <row r="30">
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>Conservative</t>
-        </is>
-      </c>
-      <c r="C30" s="18" t="n">
-        <v>0.92</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>Base</t>
-        </is>
-      </c>
-      <c r="C31" s="18" t="n">
-        <v>1</v>
-      </c>
+      <c r="C31" s="3" t="n"/>
+      <c r="D31" s="3" t="n"/>
+      <c r="E31" s="3" t="n"/>
+      <c r="F31" s="3" t="n"/>
+      <c r="G31" s="3" t="n"/>
+      <c r="H31" s="3" t="n"/>
     </row>
     <row r="32">
       <c r="B32" s="4" t="inlineStr">
         <is>
+          <t>Conservative</t>
+        </is>
+      </c>
+      <c r="C32" s="16" t="n">
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="C33" s="16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="4" t="inlineStr">
+        <is>
           <t>Aggressive</t>
         </is>
       </c>
-      <c r="C32" s="18" t="n">
+      <c r="C34" s="16" t="n">
         <v>1.1</v>
       </c>
     </row>
-    <row r="34">
-      <c r="B34" s="3" t="inlineStr">
+    <row r="36">
+      <c r="B36" s="3" t="inlineStr">
         <is>
           <t>OPERATING EXPENSE INPUTS (BASE)</t>
         </is>
       </c>
-      <c r="C34" s="3" t="n"/>
-      <c r="D34" s="3" t="n"/>
-      <c r="E34" s="3" t="n"/>
-      <c r="F34" s="3" t="n"/>
-      <c r="G34" s="3" t="n"/>
-      <c r="H34" s="3" t="n"/>
-    </row>
-    <row r="35">
-      <c r="B35" s="9" t="inlineStr"/>
-      <c r="C35" s="10" t="inlineStr">
+      <c r="C36" s="3" t="n"/>
+      <c r="D36" s="3" t="n"/>
+      <c r="E36" s="3" t="n"/>
+      <c r="F36" s="3" t="n"/>
+      <c r="G36" s="3" t="n"/>
+      <c r="H36" s="3" t="n"/>
+    </row>
+    <row r="37">
+      <c r="C37" s="8" t="inlineStr">
         <is>
           <t>Y1</t>
         </is>
       </c>
-      <c r="D35" s="10" t="inlineStr">
+      <c r="D37" s="8" t="inlineStr">
         <is>
           <t>Y2</t>
         </is>
       </c>
-      <c r="E35" s="10" t="inlineStr">
+      <c r="E37" s="8" t="inlineStr">
         <is>
           <t>Y3</t>
         </is>
       </c>
-      <c r="F35" s="10" t="inlineStr">
+      <c r="F37" s="8" t="inlineStr">
         <is>
           <t>Y4</t>
         </is>
       </c>
-      <c r="G35" s="10" t="inlineStr">
+      <c r="G37" s="8" t="inlineStr">
         <is>
           <t>Y5</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="B36" s="4" t="inlineStr">
-        <is>
-          <t>Headcount</t>
-        </is>
-      </c>
-      <c r="C36" s="17" t="n">
+    <row r="38">
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>Total headcount (workers)</t>
+        </is>
+      </c>
+      <c r="C38" s="15" t="n">
         <v>6</v>
       </c>
-      <c r="D36" s="17" t="n">
+      <c r="D38" s="15" t="n">
         <v>9</v>
       </c>
-      <c r="E36" s="17" t="n">
+      <c r="E38" s="15" t="n">
         <v>13</v>
       </c>
-      <c r="F36" s="17" t="n">
+      <c r="F38" s="15" t="n">
         <v>18</v>
       </c>
-      <c r="G36" s="17" t="n">
+      <c r="G38" s="15" t="n">
         <v>24</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="B37" s="4" t="inlineStr">
-        <is>
-          <t>Avg fully-loaded cost / FTE (Rm/yr)</t>
-        </is>
-      </c>
-      <c r="C37" s="8" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="D37" s="8" t="n">
-        <v>0.722</v>
-      </c>
-      <c r="E37" s="8" t="n">
-        <v>0.738</v>
-      </c>
-      <c r="F37" s="8" t="n">
-        <v>0.761</v>
-      </c>
-      <c r="G37" s="8" t="n">
-        <v>0.779</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" s="11" t="inlineStr">
-        <is>
-          <t>Payroll (Rm)</t>
-        </is>
-      </c>
-      <c r="C38" s="12">
-        <f>C36*C37</f>
-        <v/>
-      </c>
-      <c r="D38" s="12">
-        <f>D36*D37</f>
-        <v/>
-      </c>
-      <c r="E38" s="12">
-        <f>E36*E37</f>
-        <v/>
-      </c>
-      <c r="F38" s="12">
-        <f>F36*F37</f>
-        <v/>
-      </c>
-      <c r="G38" s="12">
-        <f>G36*G37</f>
-        <v/>
       </c>
     </row>
     <row r="39">
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Marketing (Rm)</t>
-        </is>
-      </c>
-      <c r="C39" s="8" t="n">
+          <t>AI-agent share of headcount</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="n">
         <v>0.5</v>
       </c>
-      <c r="D39" s="8" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="E39" s="8" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="F39" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="G39" s="8" t="n">
-        <v>5.5</v>
+      <c r="D39" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E39" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F39" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G39" s="5" t="n">
+        <v>0.5</v>
       </c>
     </row>
     <row r="40">
-      <c r="B40" s="4" t="inlineStr">
-        <is>
-          <t>Tech &amp; tools (Rm)</t>
-        </is>
-      </c>
-      <c r="C40" s="8" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D40" s="8" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E40" s="8" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="F40" s="8" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="G40" s="8" t="n">
-        <v>2.2</v>
+      <c r="B40" s="9" t="inlineStr">
+        <is>
+          <t>Human FTEs</t>
+        </is>
+      </c>
+      <c r="C40" s="17">
+        <f>C38*(1-C39)</f>
+        <v/>
+      </c>
+      <c r="D40" s="17">
+        <f>D38*(1-D39)</f>
+        <v/>
+      </c>
+      <c r="E40" s="17">
+        <f>E38*(1-E39)</f>
+        <v/>
+      </c>
+      <c r="F40" s="17">
+        <f>F38*(1-F39)</f>
+        <v/>
+      </c>
+      <c r="G40" s="17">
+        <f>G38*(1-G39)</f>
+        <v/>
       </c>
     </row>
     <row r="41">
-      <c r="B41" s="4" t="inlineStr">
-        <is>
-          <t>Legal / compliance / insurance (Rm)</t>
-        </is>
-      </c>
-      <c r="C41" s="8" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="D41" s="8" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="E41" s="8" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="F41" s="8" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="G41" s="8" t="n">
-        <v>2</v>
+      <c r="B41" s="9" t="inlineStr">
+        <is>
+          <t>AI agents</t>
+        </is>
+      </c>
+      <c r="C41" s="17">
+        <f>C38*C39</f>
+        <v/>
+      </c>
+      <c r="D41" s="17">
+        <f>D38*D39</f>
+        <v/>
+      </c>
+      <c r="E41" s="17">
+        <f>E38*E39</f>
+        <v/>
+      </c>
+      <c r="F41" s="17">
+        <f>F38*F39</f>
+        <v/>
+      </c>
+      <c r="G41" s="17">
+        <f>G38*G39</f>
+        <v/>
       </c>
     </row>
     <row r="42">
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>G&amp;A / office / other (Rm)</t>
-        </is>
-      </c>
-      <c r="C42" s="8" t="n">
+          <t>Human fully-loaded cost / FTE (Rm/yr)</t>
+        </is>
+      </c>
+      <c r="C42" s="7" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D42" s="7" t="n">
+        <v>0.722</v>
+      </c>
+      <c r="E42" s="7" t="n">
+        <v>0.738</v>
+      </c>
+      <c r="F42" s="7" t="n">
+        <v>0.761</v>
+      </c>
+      <c r="G42" s="7" t="n">
+        <v>0.779</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>AI-agent run cost each (Rm/yr)</t>
+        </is>
+      </c>
+      <c r="C43" s="7" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D43" s="7" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E43" s="7" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F43" s="7" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="G43" s="7" t="n">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="13" t="inlineStr">
+        <is>
+          <t>Payroll + AI agents (Rm)</t>
+        </is>
+      </c>
+      <c r="C44" s="18">
+        <f>C40*C42+C41*C43</f>
+        <v/>
+      </c>
+      <c r="D44" s="18">
+        <f>D40*D42+D41*D43</f>
+        <v/>
+      </c>
+      <c r="E44" s="18">
+        <f>E40*E42+E41*E43</f>
+        <v/>
+      </c>
+      <c r="F44" s="18">
+        <f>F40*F42+F41*F43</f>
+        <v/>
+      </c>
+      <c r="G44" s="18">
+        <f>G40*G42+G41*G43</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>Marketing (Rm)</t>
+        </is>
+      </c>
+      <c r="C45" s="7" t="n">
         <v>0.5</v>
       </c>
-      <c r="D42" s="8" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E42" s="8" t="n">
+      <c r="D45" s="7" t="n">
         <v>1.2</v>
       </c>
-      <c r="F42" s="8" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="G42" s="8" t="n">
-        <v>2.4</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="B43" s="15" t="inlineStr">
-        <is>
-          <t>Total opex — BASE (Rm)</t>
-        </is>
-      </c>
-      <c r="C43" s="19">
-        <f>SUM(C38:C42)</f>
-        <v/>
-      </c>
-      <c r="D43" s="19">
-        <f>SUM(D38:D42)</f>
-        <v/>
-      </c>
-      <c r="E43" s="19">
-        <f>SUM(E38:E42)</f>
-        <v/>
-      </c>
-      <c r="F43" s="19">
-        <f>SUM(F38:F42)</f>
-        <v/>
-      </c>
-      <c r="G43" s="19">
-        <f>SUM(G38:G42)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45">
-      <c r="B45" s="3" t="inlineStr">
-        <is>
-          <t>OPEX SCALING BY SCENARIO (applied to base total opex)</t>
-        </is>
-      </c>
-      <c r="C45" s="3" t="n"/>
-      <c r="D45" s="3" t="n"/>
-      <c r="E45" s="3" t="n"/>
-      <c r="F45" s="3" t="n"/>
-      <c r="G45" s="3" t="n"/>
-      <c r="H45" s="3" t="n"/>
+      <c r="E45" s="7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F45" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="G45" s="7" t="n">
+        <v>5.5</v>
+      </c>
     </row>
     <row r="46">
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>Conservative</t>
-        </is>
-      </c>
-      <c r="C46" s="18" t="n">
-        <v>0.72</v>
+          <t>Tech &amp; tools (Rm)</t>
+        </is>
+      </c>
+      <c r="C46" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D46" s="7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E46" s="7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F46" s="7" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="G46" s="7" t="n">
+        <v>2.2</v>
       </c>
     </row>
     <row r="47">
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>Base</t>
-        </is>
-      </c>
-      <c r="C47" s="18" t="n">
-        <v>1</v>
+          <t>Legal / compliance / insurance (Rm)</t>
+        </is>
+      </c>
+      <c r="C47" s="7" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D47" s="7" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E47" s="7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F47" s="7" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="G47" s="7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="48">
       <c r="B48" s="4" t="inlineStr">
         <is>
+          <t>G&amp;A / office / other (Rm)</t>
+        </is>
+      </c>
+      <c r="C48" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D48" s="7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E48" s="7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F48" s="7" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G48" s="7" t="n">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" s="13" t="inlineStr">
+        <is>
+          <t>Total opex — BASE (Rm)</t>
+        </is>
+      </c>
+      <c r="C49" s="18">
+        <f>SUM(C44:C48)</f>
+        <v/>
+      </c>
+      <c r="D49" s="18">
+        <f>SUM(D44:D48)</f>
+        <v/>
+      </c>
+      <c r="E49" s="18">
+        <f>SUM(E44:E48)</f>
+        <v/>
+      </c>
+      <c r="F49" s="18">
+        <f>SUM(F44:F48)</f>
+        <v/>
+      </c>
+      <c r="G49" s="18">
+        <f>SUM(G44:G48)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>OPEX SCALING BY SCENARIO</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="n"/>
+      <c r="D51" s="3" t="n"/>
+      <c r="E51" s="3" t="n"/>
+      <c r="F51" s="3" t="n"/>
+      <c r="G51" s="3" t="n"/>
+      <c r="H51" s="3" t="n"/>
+    </row>
+    <row r="52">
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>Conservative</t>
+        </is>
+      </c>
+      <c r="C52" s="16" t="n">
+        <v>0.72</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="C53" s="16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" s="4" t="inlineStr">
+        <is>
           <t>Aggressive</t>
         </is>
       </c>
-      <c r="C48" s="18" t="n">
+      <c r="C54" s="16" t="n">
         <v>1.3</v>
       </c>
     </row>
@@ -1306,434 +1436,433 @@
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="9" t="inlineStr"/>
-      <c r="C3" s="10" t="inlineStr">
+      <c r="C3" s="8" t="inlineStr">
         <is>
           <t>Y1</t>
         </is>
       </c>
-      <c r="D3" s="10" t="inlineStr">
+      <c r="D3" s="8" t="inlineStr">
         <is>
           <t>Y2</t>
         </is>
       </c>
-      <c r="E3" s="10" t="inlineStr">
+      <c r="E3" s="8" t="inlineStr">
         <is>
           <t>Y3</t>
         </is>
       </c>
-      <c r="F3" s="10" t="inlineStr">
+      <c r="F3" s="8" t="inlineStr">
         <is>
           <t>Y4</t>
         </is>
       </c>
-      <c r="G3" s="10" t="inlineStr">
+      <c r="G3" s="8" t="inlineStr">
         <is>
           <t>Y5</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="20" t="inlineStr">
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>Registered deals</t>
         </is>
       </c>
-      <c r="C4" s="21">
-        <f>Assumptions!C26</f>
-        <v/>
-      </c>
-      <c r="D4" s="21">
-        <f>Assumptions!D26</f>
-        <v/>
-      </c>
-      <c r="E4" s="21">
-        <f>Assumptions!E26</f>
-        <v/>
-      </c>
-      <c r="F4" s="21">
-        <f>Assumptions!F26</f>
-        <v/>
-      </c>
-      <c r="G4" s="21">
-        <f>Assumptions!G26</f>
+      <c r="C4" s="20">
+        <f>Assumptions!C28</f>
+        <v/>
+      </c>
+      <c r="D4" s="20">
+        <f>Assumptions!D28</f>
+        <v/>
+      </c>
+      <c r="E4" s="20">
+        <f>Assumptions!E28</f>
+        <v/>
+      </c>
+      <c r="F4" s="20">
+        <f>Assumptions!F28</f>
+        <v/>
+      </c>
+      <c r="G4" s="20">
+        <f>Assumptions!G28</f>
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="20" t="inlineStr">
+      <c r="B5" s="19" t="inlineStr">
         <is>
           <t>Revenue per deal (R)</t>
         </is>
       </c>
-      <c r="C5" s="22">
-        <f>Assumptions!C21*Assumptions!$C$31</f>
-        <v/>
-      </c>
-      <c r="D5" s="22">
-        <f>Assumptions!D21*Assumptions!$C$31</f>
-        <v/>
-      </c>
-      <c r="E5" s="22">
-        <f>Assumptions!E21*Assumptions!$C$31</f>
-        <v/>
-      </c>
-      <c r="F5" s="22">
-        <f>Assumptions!F21*Assumptions!$C$31</f>
-        <v/>
-      </c>
-      <c r="G5" s="22">
-        <f>Assumptions!G21*Assumptions!$C$31</f>
+      <c r="C5" s="21">
+        <f>Assumptions!C23*Assumptions!$C$33</f>
+        <v/>
+      </c>
+      <c r="D5" s="21">
+        <f>Assumptions!D23*Assumptions!$C$33</f>
+        <v/>
+      </c>
+      <c r="E5" s="21">
+        <f>Assumptions!E23*Assumptions!$C$33</f>
+        <v/>
+      </c>
+      <c r="F5" s="21">
+        <f>Assumptions!F23*Assumptions!$C$33</f>
+        <v/>
+      </c>
+      <c r="G5" s="21">
+        <f>Assumptions!G23*Assumptions!$C$33</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B6" s="22" t="inlineStr">
         <is>
           <t>Revenue</t>
         </is>
       </c>
-      <c r="C6" s="24">
+      <c r="C6" s="23">
         <f>C4*C5/1000000</f>
         <v/>
       </c>
-      <c r="D6" s="24">
+      <c r="D6" s="23">
         <f>D4*D5/1000000</f>
         <v/>
       </c>
-      <c r="E6" s="24">
+      <c r="E6" s="23">
         <f>E4*E5/1000000</f>
         <v/>
       </c>
-      <c r="F6" s="24">
+      <c r="F6" s="23">
         <f>F4*F5/1000000</f>
         <v/>
       </c>
-      <c r="G6" s="24">
+      <c r="G6" s="23">
         <f>G4*G5/1000000</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="20" t="inlineStr">
+      <c r="B7" s="19" t="inlineStr">
         <is>
           <t>COGS</t>
         </is>
       </c>
-      <c r="C7" s="25">
-        <f>-C6*(1-Assumptions!$C$6)</f>
-        <v/>
-      </c>
-      <c r="D7" s="25">
-        <f>-D6*(1-Assumptions!$C$6)</f>
-        <v/>
-      </c>
-      <c r="E7" s="25">
-        <f>-E6*(1-Assumptions!$C$6)</f>
-        <v/>
-      </c>
-      <c r="F7" s="25">
-        <f>-F6*(1-Assumptions!$C$6)</f>
-        <v/>
-      </c>
-      <c r="G7" s="25">
-        <f>-G6*(1-Assumptions!$C$6)</f>
+      <c r="C7" s="24">
+        <f>-C6*(1-Assumptions!$C$7)</f>
+        <v/>
+      </c>
+      <c r="D7" s="24">
+        <f>-D6*(1-Assumptions!$C$7)</f>
+        <v/>
+      </c>
+      <c r="E7" s="24">
+        <f>-E6*(1-Assumptions!$C$7)</f>
+        <v/>
+      </c>
+      <c r="F7" s="24">
+        <f>-F6*(1-Assumptions!$C$7)</f>
+        <v/>
+      </c>
+      <c r="G7" s="24">
+        <f>-G6*(1-Assumptions!$C$7)</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="26" t="inlineStr">
+      <c r="B8" s="25" t="inlineStr">
         <is>
           <t>Gross profit</t>
         </is>
       </c>
-      <c r="C8" s="27">
-        <f>C6*Assumptions!$C$6</f>
-        <v/>
-      </c>
-      <c r="D8" s="27">
-        <f>D6*Assumptions!$C$6</f>
-        <v/>
-      </c>
-      <c r="E8" s="27">
-        <f>E6*Assumptions!$C$6</f>
-        <v/>
-      </c>
-      <c r="F8" s="27">
-        <f>F6*Assumptions!$C$6</f>
-        <v/>
-      </c>
-      <c r="G8" s="27">
-        <f>G6*Assumptions!$C$6</f>
+      <c r="C8" s="26">
+        <f>C6*Assumptions!$C$7</f>
+        <v/>
+      </c>
+      <c r="D8" s="26">
+        <f>D6*Assumptions!$C$7</f>
+        <v/>
+      </c>
+      <c r="E8" s="26">
+        <f>E6*Assumptions!$C$7</f>
+        <v/>
+      </c>
+      <c r="F8" s="26">
+        <f>F6*Assumptions!$C$7</f>
+        <v/>
+      </c>
+      <c r="G8" s="26">
+        <f>G6*Assumptions!$C$7</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="20" t="inlineStr">
+      <c r="B9" s="19" t="inlineStr">
         <is>
           <t>Gross margin</t>
         </is>
       </c>
-      <c r="C9" s="28">
+      <c r="C9" s="27">
         <f>IF(C6=0,"",C8/C6)</f>
         <v/>
       </c>
-      <c r="D9" s="28">
+      <c r="D9" s="27">
         <f>IF(D6=0,"",D8/D6)</f>
         <v/>
       </c>
-      <c r="E9" s="28">
+      <c r="E9" s="27">
         <f>IF(E6=0,"",E8/E6)</f>
         <v/>
       </c>
-      <c r="F9" s="28">
+      <c r="F9" s="27">
         <f>IF(F6=0,"",F8/F6)</f>
         <v/>
       </c>
-      <c r="G9" s="28">
+      <c r="G9" s="27">
         <f>IF(G6=0,"",G8/G6)</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="20" t="inlineStr">
-        <is>
-          <t>Payroll</t>
-        </is>
-      </c>
-      <c r="C10" s="25">
-        <f>Assumptions!C38</f>
-        <v/>
-      </c>
-      <c r="D10" s="25">
-        <f>Assumptions!D38</f>
-        <v/>
-      </c>
-      <c r="E10" s="25">
-        <f>Assumptions!E38</f>
-        <v/>
-      </c>
-      <c r="F10" s="25">
-        <f>Assumptions!F38</f>
-        <v/>
-      </c>
-      <c r="G10" s="25">
-        <f>Assumptions!G38</f>
+      <c r="B10" s="19" t="inlineStr">
+        <is>
+          <t>Payroll + AI agents</t>
+        </is>
+      </c>
+      <c r="C10" s="24">
+        <f>Assumptions!C44</f>
+        <v/>
+      </c>
+      <c r="D10" s="24">
+        <f>Assumptions!D44</f>
+        <v/>
+      </c>
+      <c r="E10" s="24">
+        <f>Assumptions!E44</f>
+        <v/>
+      </c>
+      <c r="F10" s="24">
+        <f>Assumptions!F44</f>
+        <v/>
+      </c>
+      <c r="G10" s="24">
+        <f>Assumptions!G44</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="20" t="inlineStr">
+      <c r="B11" s="19" t="inlineStr">
         <is>
           <t>Marketing</t>
         </is>
       </c>
-      <c r="C11" s="25">
-        <f>Assumptions!C39</f>
-        <v/>
-      </c>
-      <c r="D11" s="25">
-        <f>Assumptions!D39</f>
-        <v/>
-      </c>
-      <c r="E11" s="25">
-        <f>Assumptions!E39</f>
-        <v/>
-      </c>
-      <c r="F11" s="25">
-        <f>Assumptions!F39</f>
-        <v/>
-      </c>
-      <c r="G11" s="25">
-        <f>Assumptions!G39</f>
+      <c r="C11" s="24">
+        <f>Assumptions!C45</f>
+        <v/>
+      </c>
+      <c r="D11" s="24">
+        <f>Assumptions!D45</f>
+        <v/>
+      </c>
+      <c r="E11" s="24">
+        <f>Assumptions!E45</f>
+        <v/>
+      </c>
+      <c r="F11" s="24">
+        <f>Assumptions!F45</f>
+        <v/>
+      </c>
+      <c r="G11" s="24">
+        <f>Assumptions!G45</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="20" t="inlineStr">
+      <c r="B12" s="19" t="inlineStr">
         <is>
           <t>Tech &amp; tools</t>
         </is>
       </c>
-      <c r="C12" s="25">
-        <f>Assumptions!C40</f>
-        <v/>
-      </c>
-      <c r="D12" s="25">
-        <f>Assumptions!D40</f>
-        <v/>
-      </c>
-      <c r="E12" s="25">
-        <f>Assumptions!E40</f>
-        <v/>
-      </c>
-      <c r="F12" s="25">
-        <f>Assumptions!F40</f>
-        <v/>
-      </c>
-      <c r="G12" s="25">
-        <f>Assumptions!G40</f>
+      <c r="C12" s="24">
+        <f>Assumptions!C46</f>
+        <v/>
+      </c>
+      <c r="D12" s="24">
+        <f>Assumptions!D46</f>
+        <v/>
+      </c>
+      <c r="E12" s="24">
+        <f>Assumptions!E46</f>
+        <v/>
+      </c>
+      <c r="F12" s="24">
+        <f>Assumptions!F46</f>
+        <v/>
+      </c>
+      <c r="G12" s="24">
+        <f>Assumptions!G46</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="20" t="inlineStr">
+      <c r="B13" s="19" t="inlineStr">
         <is>
           <t>Legal / compliance / insurance</t>
         </is>
       </c>
-      <c r="C13" s="25">
-        <f>Assumptions!C41</f>
-        <v/>
-      </c>
-      <c r="D13" s="25">
-        <f>Assumptions!D41</f>
-        <v/>
-      </c>
-      <c r="E13" s="25">
-        <f>Assumptions!E41</f>
-        <v/>
-      </c>
-      <c r="F13" s="25">
-        <f>Assumptions!F41</f>
-        <v/>
-      </c>
-      <c r="G13" s="25">
-        <f>Assumptions!G41</f>
+      <c r="C13" s="24">
+        <f>Assumptions!C47</f>
+        <v/>
+      </c>
+      <c r="D13" s="24">
+        <f>Assumptions!D47</f>
+        <v/>
+      </c>
+      <c r="E13" s="24">
+        <f>Assumptions!E47</f>
+        <v/>
+      </c>
+      <c r="F13" s="24">
+        <f>Assumptions!F47</f>
+        <v/>
+      </c>
+      <c r="G13" s="24">
+        <f>Assumptions!G47</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="20" t="inlineStr">
+      <c r="B14" s="19" t="inlineStr">
         <is>
           <t>G&amp;A / office / other</t>
         </is>
       </c>
-      <c r="C14" s="25">
-        <f>Assumptions!C42</f>
-        <v/>
-      </c>
-      <c r="D14" s="25">
-        <f>Assumptions!D42</f>
-        <v/>
-      </c>
-      <c r="E14" s="25">
-        <f>Assumptions!E42</f>
-        <v/>
-      </c>
-      <c r="F14" s="25">
-        <f>Assumptions!F42</f>
-        <v/>
-      </c>
-      <c r="G14" s="25">
-        <f>Assumptions!G42</f>
+      <c r="C14" s="24">
+        <f>Assumptions!C48</f>
+        <v/>
+      </c>
+      <c r="D14" s="24">
+        <f>Assumptions!D48</f>
+        <v/>
+      </c>
+      <c r="E14" s="24">
+        <f>Assumptions!E48</f>
+        <v/>
+      </c>
+      <c r="F14" s="24">
+        <f>Assumptions!F48</f>
+        <v/>
+      </c>
+      <c r="G14" s="24">
+        <f>Assumptions!G48</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="26" t="inlineStr">
+      <c r="B15" s="25" t="inlineStr">
         <is>
           <t>Total operating expenses</t>
         </is>
       </c>
-      <c r="C15" s="27">
+      <c r="C15" s="26">
         <f>SUM(C10:C14)</f>
         <v/>
       </c>
-      <c r="D15" s="27">
+      <c r="D15" s="26">
         <f>SUM(D10:D14)</f>
         <v/>
       </c>
-      <c r="E15" s="27">
+      <c r="E15" s="26">
         <f>SUM(E10:E14)</f>
         <v/>
       </c>
-      <c r="F15" s="27">
+      <c r="F15" s="26">
         <f>SUM(F10:F14)</f>
         <v/>
       </c>
-      <c r="G15" s="27">
+      <c r="G15" s="26">
         <f>SUM(G10:G14)</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="23" t="inlineStr">
+      <c r="B16" s="22" t="inlineStr">
         <is>
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="C16" s="24">
+      <c r="C16" s="23">
         <f>C8-C15</f>
         <v/>
       </c>
-      <c r="D16" s="24">
+      <c r="D16" s="23">
         <f>D8-D15</f>
         <v/>
       </c>
-      <c r="E16" s="24">
+      <c r="E16" s="23">
         <f>E8-E15</f>
         <v/>
       </c>
-      <c r="F16" s="24">
+      <c r="F16" s="23">
         <f>F8-F15</f>
         <v/>
       </c>
-      <c r="G16" s="24">
+      <c r="G16" s="23">
         <f>G8-G15</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="20" t="inlineStr">
+      <c r="B17" s="19" t="inlineStr">
         <is>
           <t>EBITDA margin</t>
         </is>
       </c>
-      <c r="C17" s="28">
+      <c r="C17" s="27">
         <f>IF(C6=0,"",C16/C6)</f>
         <v/>
       </c>
-      <c r="D17" s="28">
+      <c r="D17" s="27">
         <f>IF(D6=0,"",D16/D6)</f>
         <v/>
       </c>
-      <c r="E17" s="28">
+      <c r="E17" s="27">
         <f>IF(E6=0,"",E16/E6)</f>
         <v/>
       </c>
-      <c r="F17" s="28">
+      <c r="F17" s="27">
         <f>IF(F6=0,"",F16/F6)</f>
         <v/>
       </c>
-      <c r="G17" s="28">
+      <c r="G17" s="27">
         <f>IF(G6=0,"",G16/G6)</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="26" t="inlineStr">
+      <c r="B18" s="25" t="inlineStr">
         <is>
           <t>Cumulative EBITDA (cash proxy)</t>
         </is>
       </c>
-      <c r="C18" s="27">
+      <c r="C18" s="26">
         <f>C16</f>
         <v/>
       </c>
-      <c r="D18" s="27">
+      <c r="D18" s="26">
         <f>C18+D16</f>
         <v/>
       </c>
-      <c r="E18" s="27">
+      <c r="E18" s="26">
         <f>D18+E16</f>
         <v/>
       </c>
-      <c r="F18" s="27">
+      <c r="F18" s="26">
         <f>E18+F16</f>
         <v/>
       </c>
-      <c r="G18" s="27">
+      <c r="G18" s="26">
         <f>F18+G16</f>
         <v/>
       </c>
@@ -1782,191 +1911,190 @@
       <c r="H3" s="3" t="n"/>
     </row>
     <row r="4">
-      <c r="B4" s="9" t="inlineStr"/>
-      <c r="C4" s="10" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>Y1</t>
         </is>
       </c>
-      <c r="D4" s="10" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>Y2</t>
         </is>
       </c>
-      <c r="E4" s="10" t="inlineStr">
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>Y3</t>
         </is>
       </c>
-      <c r="F4" s="10" t="inlineStr">
+      <c r="F4" s="8" t="inlineStr">
         <is>
           <t>Y4</t>
         </is>
       </c>
-      <c r="G4" s="10" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
         <is>
           <t>Y5</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="20" t="inlineStr">
+      <c r="B5" s="19" t="inlineStr">
         <is>
           <t>Revenue</t>
         </is>
       </c>
-      <c r="C5" s="25">
-        <f>Assumptions!C25*Assumptions!C21*Assumptions!$C$30/1000000</f>
-        <v/>
-      </c>
-      <c r="D5" s="25">
-        <f>Assumptions!D25*Assumptions!D21*Assumptions!$C$30/1000000</f>
-        <v/>
-      </c>
-      <c r="E5" s="25">
-        <f>Assumptions!E25*Assumptions!E21*Assumptions!$C$30/1000000</f>
-        <v/>
-      </c>
-      <c r="F5" s="25">
-        <f>Assumptions!F25*Assumptions!F21*Assumptions!$C$30/1000000</f>
-        <v/>
-      </c>
-      <c r="G5" s="25">
-        <f>Assumptions!G25*Assumptions!G21*Assumptions!$C$30/1000000</f>
+      <c r="C5" s="24">
+        <f>Assumptions!C27*Assumptions!C23*Assumptions!$C$32/1000000</f>
+        <v/>
+      </c>
+      <c r="D5" s="24">
+        <f>Assumptions!D27*Assumptions!D23*Assumptions!$C$32/1000000</f>
+        <v/>
+      </c>
+      <c r="E5" s="24">
+        <f>Assumptions!E27*Assumptions!E23*Assumptions!$C$32/1000000</f>
+        <v/>
+      </c>
+      <c r="F5" s="24">
+        <f>Assumptions!F27*Assumptions!F23*Assumptions!$C$32/1000000</f>
+        <v/>
+      </c>
+      <c r="G5" s="24">
+        <f>Assumptions!G27*Assumptions!G23*Assumptions!$C$32/1000000</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="20" t="inlineStr">
+      <c r="B6" s="19" t="inlineStr">
         <is>
           <t>Gross profit</t>
         </is>
       </c>
-      <c r="C6" s="25">
-        <f>C5*Assumptions!$C$6</f>
-        <v/>
-      </c>
-      <c r="D6" s="25">
-        <f>D5*Assumptions!$C$6</f>
-        <v/>
-      </c>
-      <c r="E6" s="25">
-        <f>E5*Assumptions!$C$6</f>
-        <v/>
-      </c>
-      <c r="F6" s="25">
-        <f>F5*Assumptions!$C$6</f>
-        <v/>
-      </c>
-      <c r="G6" s="25">
-        <f>G5*Assumptions!$C$6</f>
+      <c r="C6" s="24">
+        <f>C5*Assumptions!$C$7</f>
+        <v/>
+      </c>
+      <c r="D6" s="24">
+        <f>D5*Assumptions!$C$7</f>
+        <v/>
+      </c>
+      <c r="E6" s="24">
+        <f>E5*Assumptions!$C$7</f>
+        <v/>
+      </c>
+      <c r="F6" s="24">
+        <f>F5*Assumptions!$C$7</f>
+        <v/>
+      </c>
+      <c r="G6" s="24">
+        <f>G5*Assumptions!$C$7</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="20" t="inlineStr">
+      <c r="B7" s="19" t="inlineStr">
         <is>
           <t>Operating expenses</t>
         </is>
       </c>
-      <c r="C7" s="25">
-        <f>Assumptions!C43*Assumptions!$C$46</f>
-        <v/>
-      </c>
-      <c r="D7" s="25">
-        <f>Assumptions!D43*Assumptions!$C$46</f>
-        <v/>
-      </c>
-      <c r="E7" s="25">
-        <f>Assumptions!E43*Assumptions!$C$46</f>
-        <v/>
-      </c>
-      <c r="F7" s="25">
-        <f>Assumptions!F43*Assumptions!$C$46</f>
-        <v/>
-      </c>
-      <c r="G7" s="25">
-        <f>Assumptions!G43*Assumptions!$C$46</f>
+      <c r="C7" s="24">
+        <f>Assumptions!C49*Assumptions!$C$52</f>
+        <v/>
+      </c>
+      <c r="D7" s="24">
+        <f>Assumptions!D49*Assumptions!$C$52</f>
+        <v/>
+      </c>
+      <c r="E7" s="24">
+        <f>Assumptions!E49*Assumptions!$C$52</f>
+        <v/>
+      </c>
+      <c r="F7" s="24">
+        <f>Assumptions!F49*Assumptions!$C$52</f>
+        <v/>
+      </c>
+      <c r="G7" s="24">
+        <f>Assumptions!G49*Assumptions!$C$52</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="26" t="inlineStr">
+      <c r="B8" s="25" t="inlineStr">
         <is>
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="C8" s="27">
+      <c r="C8" s="26">
         <f>C6-C7</f>
         <v/>
       </c>
-      <c r="D8" s="27">
+      <c r="D8" s="26">
         <f>D6-D7</f>
         <v/>
       </c>
-      <c r="E8" s="27">
+      <c r="E8" s="26">
         <f>E6-E7</f>
         <v/>
       </c>
-      <c r="F8" s="27">
+      <c r="F8" s="26">
         <f>F6-F7</f>
         <v/>
       </c>
-      <c r="G8" s="27">
+      <c r="G8" s="26">
         <f>G6-G7</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="20" t="inlineStr">
+      <c r="B9" s="19" t="inlineStr">
         <is>
           <t>Cumulative EBITDA</t>
         </is>
       </c>
-      <c r="C9" s="25">
+      <c r="C9" s="24">
         <f>C8</f>
         <v/>
       </c>
-      <c r="D9" s="25">
+      <c r="D9" s="24">
         <f>C9+D8</f>
         <v/>
       </c>
-      <c r="E9" s="25">
+      <c r="E9" s="24">
         <f>D9+E8</f>
         <v/>
       </c>
-      <c r="F9" s="25">
+      <c r="F9" s="24">
         <f>E9+F8</f>
         <v/>
       </c>
-      <c r="G9" s="25">
+      <c r="G9" s="24">
         <f>F9+G8</f>
         <v/>
       </c>
     </row>
     <row r="10" hidden="1">
-      <c r="B10" s="20" t="inlineStr">
-        <is>
-          <t>First EBITDA+ helper</t>
-        </is>
-      </c>
-      <c r="C10" s="21">
+      <c r="B10" s="19" t="inlineStr">
+        <is>
+          <t>profit-year helper</t>
+        </is>
+      </c>
+      <c r="C10" s="20">
         <f>IF(C8&gt;0,C$60,99)</f>
         <v/>
       </c>
-      <c r="D10" s="21">
+      <c r="D10" s="20">
         <f>IF(D8&gt;0,D$60,99)</f>
         <v/>
       </c>
-      <c r="E10" s="21">
+      <c r="E10" s="20">
         <f>IF(E8&gt;0,E$60,99)</f>
         <v/>
       </c>
-      <c r="F10" s="21">
+      <c r="F10" s="20">
         <f>IF(F8&gt;0,F$60,99)</f>
         <v/>
       </c>
-      <c r="G10" s="21">
+      <c r="G10" s="20">
         <f>IF(G8&gt;0,G$60,99)</f>
         <v/>
       </c>
@@ -1985,191 +2113,190 @@
       <c r="H13" s="3" t="n"/>
     </row>
     <row r="14">
-      <c r="B14" s="9" t="inlineStr"/>
-      <c r="C14" s="10" t="inlineStr">
+      <c r="C14" s="8" t="inlineStr">
         <is>
           <t>Y1</t>
         </is>
       </c>
-      <c r="D14" s="10" t="inlineStr">
+      <c r="D14" s="8" t="inlineStr">
         <is>
           <t>Y2</t>
         </is>
       </c>
-      <c r="E14" s="10" t="inlineStr">
+      <c r="E14" s="8" t="inlineStr">
         <is>
           <t>Y3</t>
         </is>
       </c>
-      <c r="F14" s="10" t="inlineStr">
+      <c r="F14" s="8" t="inlineStr">
         <is>
           <t>Y4</t>
         </is>
       </c>
-      <c r="G14" s="10" t="inlineStr">
+      <c r="G14" s="8" t="inlineStr">
         <is>
           <t>Y5</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="20" t="inlineStr">
+      <c r="B15" s="19" t="inlineStr">
         <is>
           <t>Revenue</t>
         </is>
       </c>
-      <c r="C15" s="25">
-        <f>Assumptions!C26*Assumptions!C21*Assumptions!$C$31/1000000</f>
-        <v/>
-      </c>
-      <c r="D15" s="25">
-        <f>Assumptions!D26*Assumptions!D21*Assumptions!$C$31/1000000</f>
-        <v/>
-      </c>
-      <c r="E15" s="25">
-        <f>Assumptions!E26*Assumptions!E21*Assumptions!$C$31/1000000</f>
-        <v/>
-      </c>
-      <c r="F15" s="25">
-        <f>Assumptions!F26*Assumptions!F21*Assumptions!$C$31/1000000</f>
-        <v/>
-      </c>
-      <c r="G15" s="25">
-        <f>Assumptions!G26*Assumptions!G21*Assumptions!$C$31/1000000</f>
+      <c r="C15" s="24">
+        <f>Assumptions!C28*Assumptions!C23*Assumptions!$C$33/1000000</f>
+        <v/>
+      </c>
+      <c r="D15" s="24">
+        <f>Assumptions!D28*Assumptions!D23*Assumptions!$C$33/1000000</f>
+        <v/>
+      </c>
+      <c r="E15" s="24">
+        <f>Assumptions!E28*Assumptions!E23*Assumptions!$C$33/1000000</f>
+        <v/>
+      </c>
+      <c r="F15" s="24">
+        <f>Assumptions!F28*Assumptions!F23*Assumptions!$C$33/1000000</f>
+        <v/>
+      </c>
+      <c r="G15" s="24">
+        <f>Assumptions!G28*Assumptions!G23*Assumptions!$C$33/1000000</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="20" t="inlineStr">
+      <c r="B16" s="19" t="inlineStr">
         <is>
           <t>Gross profit</t>
         </is>
       </c>
-      <c r="C16" s="25">
-        <f>C15*Assumptions!$C$6</f>
-        <v/>
-      </c>
-      <c r="D16" s="25">
-        <f>D15*Assumptions!$C$6</f>
-        <v/>
-      </c>
-      <c r="E16" s="25">
-        <f>E15*Assumptions!$C$6</f>
-        <v/>
-      </c>
-      <c r="F16" s="25">
-        <f>F15*Assumptions!$C$6</f>
-        <v/>
-      </c>
-      <c r="G16" s="25">
-        <f>G15*Assumptions!$C$6</f>
+      <c r="C16" s="24">
+        <f>C15*Assumptions!$C$7</f>
+        <v/>
+      </c>
+      <c r="D16" s="24">
+        <f>D15*Assumptions!$C$7</f>
+        <v/>
+      </c>
+      <c r="E16" s="24">
+        <f>E15*Assumptions!$C$7</f>
+        <v/>
+      </c>
+      <c r="F16" s="24">
+        <f>F15*Assumptions!$C$7</f>
+        <v/>
+      </c>
+      <c r="G16" s="24">
+        <f>G15*Assumptions!$C$7</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="20" t="inlineStr">
+      <c r="B17" s="19" t="inlineStr">
         <is>
           <t>Operating expenses</t>
         </is>
       </c>
-      <c r="C17" s="25">
-        <f>Assumptions!C43*Assumptions!$C$47</f>
-        <v/>
-      </c>
-      <c r="D17" s="25">
-        <f>Assumptions!D43*Assumptions!$C$47</f>
-        <v/>
-      </c>
-      <c r="E17" s="25">
-        <f>Assumptions!E43*Assumptions!$C$47</f>
-        <v/>
-      </c>
-      <c r="F17" s="25">
-        <f>Assumptions!F43*Assumptions!$C$47</f>
-        <v/>
-      </c>
-      <c r="G17" s="25">
-        <f>Assumptions!G43*Assumptions!$C$47</f>
+      <c r="C17" s="24">
+        <f>Assumptions!C49*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="D17" s="24">
+        <f>Assumptions!D49*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="E17" s="24">
+        <f>Assumptions!E49*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="F17" s="24">
+        <f>Assumptions!F49*Assumptions!$C$53</f>
+        <v/>
+      </c>
+      <c r="G17" s="24">
+        <f>Assumptions!G49*Assumptions!$C$53</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="26" t="inlineStr">
+      <c r="B18" s="25" t="inlineStr">
         <is>
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="C18" s="27">
+      <c r="C18" s="26">
         <f>C16-C17</f>
         <v/>
       </c>
-      <c r="D18" s="27">
+      <c r="D18" s="26">
         <f>D16-D17</f>
         <v/>
       </c>
-      <c r="E18" s="27">
+      <c r="E18" s="26">
         <f>E16-E17</f>
         <v/>
       </c>
-      <c r="F18" s="27">
+      <c r="F18" s="26">
         <f>F16-F17</f>
         <v/>
       </c>
-      <c r="G18" s="27">
+      <c r="G18" s="26">
         <f>G16-G17</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="20" t="inlineStr">
+      <c r="B19" s="19" t="inlineStr">
         <is>
           <t>Cumulative EBITDA</t>
         </is>
       </c>
-      <c r="C19" s="25">
+      <c r="C19" s="24">
         <f>C18</f>
         <v/>
       </c>
-      <c r="D19" s="25">
+      <c r="D19" s="24">
         <f>C19+D18</f>
         <v/>
       </c>
-      <c r="E19" s="25">
+      <c r="E19" s="24">
         <f>D19+E18</f>
         <v/>
       </c>
-      <c r="F19" s="25">
+      <c r="F19" s="24">
         <f>E19+F18</f>
         <v/>
       </c>
-      <c r="G19" s="25">
+      <c r="G19" s="24">
         <f>F19+G18</f>
         <v/>
       </c>
     </row>
     <row r="20" hidden="1">
-      <c r="B20" s="20" t="inlineStr">
-        <is>
-          <t>First EBITDA+ helper</t>
-        </is>
-      </c>
-      <c r="C20" s="21">
+      <c r="B20" s="19" t="inlineStr">
+        <is>
+          <t>profit-year helper</t>
+        </is>
+      </c>
+      <c r="C20" s="20">
         <f>IF(C18&gt;0,C$60,99)</f>
         <v/>
       </c>
-      <c r="D20" s="21">
+      <c r="D20" s="20">
         <f>IF(D18&gt;0,D$60,99)</f>
         <v/>
       </c>
-      <c r="E20" s="21">
+      <c r="E20" s="20">
         <f>IF(E18&gt;0,E$60,99)</f>
         <v/>
       </c>
-      <c r="F20" s="21">
+      <c r="F20" s="20">
         <f>IF(F18&gt;0,F$60,99)</f>
         <v/>
       </c>
-      <c r="G20" s="21">
+      <c r="G20" s="20">
         <f>IF(G18&gt;0,G$60,99)</f>
         <v/>
       </c>
@@ -2188,191 +2315,190 @@
       <c r="H23" s="3" t="n"/>
     </row>
     <row r="24">
-      <c r="B24" s="9" t="inlineStr"/>
-      <c r="C24" s="10" t="inlineStr">
+      <c r="C24" s="8" t="inlineStr">
         <is>
           <t>Y1</t>
         </is>
       </c>
-      <c r="D24" s="10" t="inlineStr">
+      <c r="D24" s="8" t="inlineStr">
         <is>
           <t>Y2</t>
         </is>
       </c>
-      <c r="E24" s="10" t="inlineStr">
+      <c r="E24" s="8" t="inlineStr">
         <is>
           <t>Y3</t>
         </is>
       </c>
-      <c r="F24" s="10" t="inlineStr">
+      <c r="F24" s="8" t="inlineStr">
         <is>
           <t>Y4</t>
         </is>
       </c>
-      <c r="G24" s="10" t="inlineStr">
+      <c r="G24" s="8" t="inlineStr">
         <is>
           <t>Y5</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="20" t="inlineStr">
+      <c r="B25" s="19" t="inlineStr">
         <is>
           <t>Revenue</t>
         </is>
       </c>
-      <c r="C25" s="25">
-        <f>Assumptions!C27*Assumptions!C21*Assumptions!$C$32/1000000</f>
-        <v/>
-      </c>
-      <c r="D25" s="25">
-        <f>Assumptions!D27*Assumptions!D21*Assumptions!$C$32/1000000</f>
-        <v/>
-      </c>
-      <c r="E25" s="25">
-        <f>Assumptions!E27*Assumptions!E21*Assumptions!$C$32/1000000</f>
-        <v/>
-      </c>
-      <c r="F25" s="25">
-        <f>Assumptions!F27*Assumptions!F21*Assumptions!$C$32/1000000</f>
-        <v/>
-      </c>
-      <c r="G25" s="25">
-        <f>Assumptions!G27*Assumptions!G21*Assumptions!$C$32/1000000</f>
+      <c r="C25" s="24">
+        <f>Assumptions!C29*Assumptions!C23*Assumptions!$C$34/1000000</f>
+        <v/>
+      </c>
+      <c r="D25" s="24">
+        <f>Assumptions!D29*Assumptions!D23*Assumptions!$C$34/1000000</f>
+        <v/>
+      </c>
+      <c r="E25" s="24">
+        <f>Assumptions!E29*Assumptions!E23*Assumptions!$C$34/1000000</f>
+        <v/>
+      </c>
+      <c r="F25" s="24">
+        <f>Assumptions!F29*Assumptions!F23*Assumptions!$C$34/1000000</f>
+        <v/>
+      </c>
+      <c r="G25" s="24">
+        <f>Assumptions!G29*Assumptions!G23*Assumptions!$C$34/1000000</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="20" t="inlineStr">
+      <c r="B26" s="19" t="inlineStr">
         <is>
           <t>Gross profit</t>
         </is>
       </c>
-      <c r="C26" s="25">
-        <f>C25*Assumptions!$C$6</f>
-        <v/>
-      </c>
-      <c r="D26" s="25">
-        <f>D25*Assumptions!$C$6</f>
-        <v/>
-      </c>
-      <c r="E26" s="25">
-        <f>E25*Assumptions!$C$6</f>
-        <v/>
-      </c>
-      <c r="F26" s="25">
-        <f>F25*Assumptions!$C$6</f>
-        <v/>
-      </c>
-      <c r="G26" s="25">
-        <f>G25*Assumptions!$C$6</f>
+      <c r="C26" s="24">
+        <f>C25*Assumptions!$C$7</f>
+        <v/>
+      </c>
+      <c r="D26" s="24">
+        <f>D25*Assumptions!$C$7</f>
+        <v/>
+      </c>
+      <c r="E26" s="24">
+        <f>E25*Assumptions!$C$7</f>
+        <v/>
+      </c>
+      <c r="F26" s="24">
+        <f>F25*Assumptions!$C$7</f>
+        <v/>
+      </c>
+      <c r="G26" s="24">
+        <f>G25*Assumptions!$C$7</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="20" t="inlineStr">
+      <c r="B27" s="19" t="inlineStr">
         <is>
           <t>Operating expenses</t>
         </is>
       </c>
-      <c r="C27" s="25">
-        <f>Assumptions!C43*Assumptions!$C$48</f>
-        <v/>
-      </c>
-      <c r="D27" s="25">
-        <f>Assumptions!D43*Assumptions!$C$48</f>
-        <v/>
-      </c>
-      <c r="E27" s="25">
-        <f>Assumptions!E43*Assumptions!$C$48</f>
-        <v/>
-      </c>
-      <c r="F27" s="25">
-        <f>Assumptions!F43*Assumptions!$C$48</f>
-        <v/>
-      </c>
-      <c r="G27" s="25">
-        <f>Assumptions!G43*Assumptions!$C$48</f>
+      <c r="C27" s="24">
+        <f>Assumptions!C49*Assumptions!$C$54</f>
+        <v/>
+      </c>
+      <c r="D27" s="24">
+        <f>Assumptions!D49*Assumptions!$C$54</f>
+        <v/>
+      </c>
+      <c r="E27" s="24">
+        <f>Assumptions!E49*Assumptions!$C$54</f>
+        <v/>
+      </c>
+      <c r="F27" s="24">
+        <f>Assumptions!F49*Assumptions!$C$54</f>
+        <v/>
+      </c>
+      <c r="G27" s="24">
+        <f>Assumptions!G49*Assumptions!$C$54</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="26" t="inlineStr">
+      <c r="B28" s="25" t="inlineStr">
         <is>
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="C28" s="27">
+      <c r="C28" s="26">
         <f>C26-C27</f>
         <v/>
       </c>
-      <c r="D28" s="27">
+      <c r="D28" s="26">
         <f>D26-D27</f>
         <v/>
       </c>
-      <c r="E28" s="27">
+      <c r="E28" s="26">
         <f>E26-E27</f>
         <v/>
       </c>
-      <c r="F28" s="27">
+      <c r="F28" s="26">
         <f>F26-F27</f>
         <v/>
       </c>
-      <c r="G28" s="27">
+      <c r="G28" s="26">
         <f>G26-G27</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="20" t="inlineStr">
+      <c r="B29" s="19" t="inlineStr">
         <is>
           <t>Cumulative EBITDA</t>
         </is>
       </c>
-      <c r="C29" s="25">
+      <c r="C29" s="24">
         <f>C28</f>
         <v/>
       </c>
-      <c r="D29" s="25">
+      <c r="D29" s="24">
         <f>C29+D28</f>
         <v/>
       </c>
-      <c r="E29" s="25">
+      <c r="E29" s="24">
         <f>D29+E28</f>
         <v/>
       </c>
-      <c r="F29" s="25">
+      <c r="F29" s="24">
         <f>E29+F28</f>
         <v/>
       </c>
-      <c r="G29" s="25">
+      <c r="G29" s="24">
         <f>F29+G28</f>
         <v/>
       </c>
     </row>
     <row r="30" hidden="1">
-      <c r="B30" s="20" t="inlineStr">
-        <is>
-          <t>First EBITDA+ helper</t>
-        </is>
-      </c>
-      <c r="C30" s="21">
+      <c r="B30" s="19" t="inlineStr">
+        <is>
+          <t>profit-year helper</t>
+        </is>
+      </c>
+      <c r="C30" s="20">
         <f>IF(C28&gt;0,C$60,99)</f>
         <v/>
       </c>
-      <c r="D30" s="21">
+      <c r="D30" s="20">
         <f>IF(D28&gt;0,D$60,99)</f>
         <v/>
       </c>
-      <c r="E30" s="21">
+      <c r="E30" s="20">
         <f>IF(E28&gt;0,E$60,99)</f>
         <v/>
       </c>
-      <c r="F30" s="21">
+      <c r="F30" s="20">
         <f>IF(F28&gt;0,F$60,99)</f>
         <v/>
       </c>
-      <c r="G30" s="21">
+      <c r="G30" s="20">
         <f>IF(G28&gt;0,G$60,99)</f>
         <v/>
       </c>
@@ -2391,133 +2517,132 @@
       <c r="H34" s="3" t="n"/>
     </row>
     <row r="35">
-      <c r="B35" s="9" t="inlineStr"/>
-      <c r="C35" s="10" t="inlineStr">
+      <c r="C35" s="8" t="inlineStr">
         <is>
           <t>Conservative</t>
         </is>
       </c>
-      <c r="D35" s="10" t="inlineStr">
+      <c r="D35" s="8" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="E35" s="10" t="inlineStr">
+      <c r="E35" s="8" t="inlineStr">
         <is>
           <t>Aggressive</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="B36" s="26" t="inlineStr">
+      <c r="B36" s="25" t="inlineStr">
         <is>
           <t>Y5 revenue</t>
         </is>
       </c>
-      <c r="C36" s="27">
+      <c r="C36" s="26">
         <f>G5</f>
         <v/>
       </c>
-      <c r="D36" s="27">
+      <c r="D36" s="26">
         <f>G15</f>
         <v/>
       </c>
-      <c r="E36" s="27">
+      <c r="E36" s="26">
         <f>G25</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="B37" s="26" t="inlineStr">
+      <c r="B37" s="25" t="inlineStr">
         <is>
           <t>Y5 EBITDA</t>
         </is>
       </c>
-      <c r="C37" s="27">
+      <c r="C37" s="26">
         <f>G8</f>
         <v/>
       </c>
-      <c r="D37" s="27">
+      <c r="D37" s="26">
         <f>G18</f>
         <v/>
       </c>
-      <c r="E37" s="27">
+      <c r="E37" s="26">
         <f>G28</f>
         <v/>
       </c>
     </row>
     <row r="38">
-      <c r="B38" s="20" t="inlineStr">
+      <c r="B38" s="19" t="inlineStr">
         <is>
           <t>Y5 EBITDA margin</t>
         </is>
       </c>
-      <c r="C38" s="28">
+      <c r="C38" s="27">
         <f>IF(G5=0,"",G8/G5)</f>
         <v/>
       </c>
-      <c r="D38" s="28">
+      <c r="D38" s="27">
         <f>IF(G15=0,"",G18/G15)</f>
         <v/>
       </c>
-      <c r="E38" s="28">
+      <c r="E38" s="27">
         <f>IF(G25=0,"",G28/G25)</f>
         <v/>
       </c>
     </row>
     <row r="39">
-      <c r="B39" s="20" t="inlineStr">
+      <c r="B39" s="19" t="inlineStr">
         <is>
           <t>Cumulative cash low-point</t>
         </is>
       </c>
-      <c r="C39" s="25">
+      <c r="C39" s="24">
         <f>MIN(C9:G9)</f>
         <v/>
       </c>
-      <c r="D39" s="25">
+      <c r="D39" s="24">
         <f>MIN(C19:G19)</f>
         <v/>
       </c>
-      <c r="E39" s="25">
+      <c r="E39" s="24">
         <f>MIN(C29:G29)</f>
         <v/>
       </c>
     </row>
     <row r="40">
-      <c r="B40" s="26" t="inlineStr">
+      <c r="B40" s="25" t="inlineStr">
         <is>
           <t>Capital need incl. buffer</t>
         </is>
       </c>
-      <c r="C40" s="27">
-        <f>-MIN(C9:G9)+Assumptions!$C$10</f>
-        <v/>
-      </c>
-      <c r="D40" s="27">
-        <f>-MIN(C19:G19)+Assumptions!$C$10</f>
-        <v/>
-      </c>
-      <c r="E40" s="27">
-        <f>-MIN(C29:G29)+Assumptions!$C$10</f>
+      <c r="C40" s="26">
+        <f>-MIN(C9:G9)+Assumptions!$C$11</f>
+        <v/>
+      </c>
+      <c r="D40" s="26">
+        <f>-MIN(C19:G19)+Assumptions!$C$11</f>
+        <v/>
+      </c>
+      <c r="E40" s="26">
+        <f>-MIN(C29:G29)+Assumptions!$C$11</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="B41" s="20" t="inlineStr">
+      <c r="B41" s="19" t="inlineStr">
         <is>
           <t>First EBITDA-positive year</t>
         </is>
       </c>
-      <c r="C41" s="29">
+      <c r="C41" s="28">
         <f>"Y"&amp;MIN(C10:G10)</f>
         <v/>
       </c>
-      <c r="D41" s="29">
+      <c r="D41" s="28">
         <f>"Y"&amp;MIN(C20:G20)</f>
         <v/>
       </c>
-      <c r="E41" s="29">
+      <c r="E41" s="28">
         <f>"Y"&amp;MIN(C30:G30)</f>
         <v/>
       </c>
@@ -2551,7 +2676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:E29"/>
+  <dimension ref="B1:E27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="2" max="2"/>
@@ -2578,64 +2703,64 @@
       <c r="E3" s="3" t="n"/>
     </row>
     <row r="4">
-      <c r="C4" s="9" t="inlineStr">
+      <c r="C4" s="29" t="inlineStr">
         <is>
           <t>Conservative</t>
         </is>
       </c>
-      <c r="D4" s="9" t="inlineStr">
+      <c r="D4" s="29" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="E4" s="9" t="inlineStr">
+      <c r="E4" s="29" t="inlineStr">
         <is>
           <t>Aggressive</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="26" t="inlineStr">
+      <c r="B5" s="25" t="inlineStr">
         <is>
           <t>Total capital to breakeven (Rm)</t>
         </is>
       </c>
-      <c r="C5" s="27">
+      <c r="C5" s="26">
         <f>Scenarios!C40</f>
         <v/>
       </c>
-      <c r="D5" s="27">
+      <c r="D5" s="26">
         <f>Scenarios!D40</f>
         <v/>
       </c>
-      <c r="E5" s="27">
+      <c r="E5" s="26">
         <f>Scenarios!E40</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="20" t="inlineStr">
+      <c r="B6" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">  in USD (m, approx)</t>
         </is>
       </c>
-      <c r="C6" s="25">
-        <f>C5/Assumptions!$C$7</f>
-        <v/>
-      </c>
-      <c r="D6" s="25">
-        <f>D5/Assumptions!$C$7</f>
-        <v/>
-      </c>
-      <c r="E6" s="25">
-        <f>E5/Assumptions!$C$7</f>
+      <c r="C6" s="24">
+        <f>C5/Assumptions!$C$8</f>
+        <v/>
+      </c>
+      <c r="D6" s="24">
+        <f>D5/Assumptions!$C$8</f>
+        <v/>
+      </c>
+      <c r="E6" s="24">
+        <f>E5/Assumptions!$C$8</f>
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>RECOMMENDED RAISE (single seed — base)</t>
+          <t>RECOMMENDED RAISE</t>
         </is>
       </c>
       <c r="C8" s="3" t="n"/>
@@ -2645,205 +2770,188 @@
     <row r="9">
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Seed round (Rm)</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="n">
-        <v>22</v>
+          <t>Seed round (Rm) — growth buffer above need</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="20" t="inlineStr">
+      <c r="B10" s="19" t="inlineStr">
         <is>
           <t>Seed round (USD m approx)</t>
         </is>
       </c>
-      <c r="C10" s="25">
-        <f>C9/Assumptions!$C$7</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>Series A — optional (Rm)</t>
-        </is>
-      </c>
-      <c r="C11" s="8" t="n">
-        <v>40</v>
+      <c r="C10" s="24">
+        <f>C9/Assumptions!$C$8</f>
+        <v/>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>Series A only if accelerating national-prime faster than cash allows</t>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>VALUATION — REVENUE MULTIPLE (Base, Y5)</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="n"/>
+      <c r="D12" s="3" t="n"/>
+      <c r="E12" s="3" t="n"/>
+    </row>
+    <row r="13">
+      <c r="C13" s="29" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D13" s="29" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>VALUATION — REVENUE MULTIPLE (Base, Y5)</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="n"/>
-      <c r="D14" s="3" t="n"/>
-      <c r="E14" s="3" t="n"/>
+      <c r="B14" s="19" t="inlineStr">
+        <is>
+          <t>Y5 revenue (Rm)</t>
+        </is>
+      </c>
+      <c r="C14" s="24">
+        <f>Scenarios!D36</f>
+        <v/>
+      </c>
+      <c r="D14" s="24">
+        <f>Scenarios!D36</f>
+        <v/>
+      </c>
     </row>
     <row r="15">
-      <c r="C15" s="9" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="D15" s="9" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
+      <c r="B15" s="19" t="inlineStr">
+        <is>
+          <t>Revenue multiple</t>
+        </is>
+      </c>
+      <c r="C15" s="30">
+        <f>Assumptions!C9</f>
+        <v/>
+      </c>
+      <c r="D15" s="30">
+        <f>Assumptions!C10</f>
+        <v/>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="20" t="inlineStr">
+      <c r="B16" s="25" t="inlineStr">
+        <is>
+          <t>Enterprise value (Rm)</t>
+        </is>
+      </c>
+      <c r="C16" s="26">
+        <f>C14*C15</f>
+        <v/>
+      </c>
+      <c r="D16" s="26">
+        <f>D14*D15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="19" t="inlineStr">
+        <is>
+          <t>Enterprise value (USD m)</t>
+        </is>
+      </c>
+      <c r="C17" s="30">
+        <f>C16/Assumptions!$C$8</f>
+        <v/>
+      </c>
+      <c r="D17" s="30">
+        <f>D16/Assumptions!$C$8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>SEED ROUND FRAMING (illustrative)</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="n"/>
+      <c r="D19" s="3" t="n"/>
+      <c r="E19" s="3" t="n"/>
+    </row>
+    <row r="20">
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>Seed pre-money (Rm)</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="19" t="inlineStr">
+        <is>
+          <t>Seed raise (Rm)</t>
+        </is>
+      </c>
+      <c r="C21" s="24">
+        <f>C9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="25" t="inlineStr">
+        <is>
+          <t>Seed post-money (Rm)</t>
+        </is>
+      </c>
+      <c r="C22" s="26">
+        <f>C20+C21</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="19" t="inlineStr">
+        <is>
+          <t>New-investor stake</t>
+        </is>
+      </c>
+      <c r="C23" s="27">
+        <f>C21/C22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>AGGRESSIVE UPSIDE</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="n"/>
+      <c r="D25" s="3" t="n"/>
+      <c r="E25" s="3" t="n"/>
+    </row>
+    <row r="26">
+      <c r="B26" s="19" t="inlineStr">
         <is>
           <t>Y5 revenue (Rm)</t>
         </is>
       </c>
-      <c r="C16" s="25">
-        <f>Scenarios!D36</f>
-        <v/>
-      </c>
-      <c r="D16" s="25">
-        <f>Scenarios!D36</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" s="20" t="inlineStr">
-        <is>
-          <t>Revenue multiple</t>
-        </is>
-      </c>
-      <c r="C17" s="30">
-        <f>Assumptions!C8</f>
-        <v/>
-      </c>
-      <c r="D17" s="30">
-        <f>Assumptions!C9</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="26" t="inlineStr">
-        <is>
-          <t>Enterprise value (Rm)</t>
-        </is>
-      </c>
-      <c r="C18" s="27">
-        <f>C16*C17</f>
-        <v/>
-      </c>
-      <c r="D18" s="27">
-        <f>D16*D17</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" s="20" t="inlineStr">
-        <is>
-          <t>Enterprise value (USD m)</t>
-        </is>
-      </c>
-      <c r="C19" s="31">
-        <f>C18/Assumptions!$C$7</f>
-        <v/>
-      </c>
-      <c r="D19" s="31">
-        <f>D18/Assumptions!$C$7</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>SEED ROUND FRAMING (illustrative)</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="n"/>
-      <c r="D21" s="3" t="n"/>
-      <c r="E21" s="3" t="n"/>
-    </row>
-    <row r="22">
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>Seed pre-money (Rm)</t>
-        </is>
-      </c>
-      <c r="C22" s="8" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="20" t="inlineStr">
-        <is>
-          <t>Seed raise (Rm)</t>
-        </is>
-      </c>
-      <c r="C23" s="25">
-        <f>C9</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="26" t="inlineStr">
-        <is>
-          <t>Seed post-money (Rm)</t>
-        </is>
-      </c>
-      <c r="C24" s="27">
-        <f>C22+C23</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="B25" s="20" t="inlineStr">
-        <is>
-          <t>New-investor stake</t>
-        </is>
-      </c>
-      <c r="C25" s="28">
-        <f>C23/C24</f>
+      <c r="C26" s="24">
+        <f>Scenarios!E36</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>AGGRESSIVE UPSIDE</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="n"/>
-      <c r="D27" s="3" t="n"/>
-      <c r="E27" s="3" t="n"/>
-    </row>
-    <row r="28">
-      <c r="B28" s="20" t="inlineStr">
-        <is>
-          <t>Y5 revenue (Rm)</t>
-        </is>
-      </c>
-      <c r="C28" s="25">
-        <f>Scenarios!E36</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="26" t="inlineStr">
+      <c r="B27" s="25" t="inlineStr">
         <is>
           <t>EV @ 5x (Rm)</t>
         </is>
       </c>
-      <c r="C29" s="27">
-        <f>C28*5</f>
+      <c r="C27" s="26">
+        <f>C26*5</f>
         <v/>
       </c>
     </row>
@@ -2859,150 +2967,153 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:B23"/>
+  <dimension ref="B1:B24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="110" customWidth="1" min="2" max="2"/>
+    <col width="115" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="B1" s="32" t="inlineStr">
+      <c r="B1" s="31" t="inlineStr">
         <is>
           <t>Sold Direct — model notes &amp; sources</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="B2" s="33" t="inlineStr"/>
+      <c r="B2" s="32" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="B3" s="34" t="inlineStr">
+      <c r="B3" s="33" t="inlineStr">
         <is>
           <t>Strategy: prime / upper-market focus (Atlantic Seaboard, City Bowl, Southern Suburbs, Constantia; then prime JHB-north &amp; Umhlanga).</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="33" t="inlineStr">
-        <is>
-          <t>Fewer deals, larger bonds (bigger origination referral), low reputation-led CAC, lean concierge team.</t>
-        </is>
-      </c>
+      <c r="B4" s="32" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="B5" s="33" t="inlineStr"/>
+      <c r="B5" s="34" t="inlineStr">
+        <is>
+          <t>MONETISATION (every deal pays a take-rate of value):</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="B6" s="34" t="inlineStr">
-        <is>
-          <t>MONETISATION POLICY (every deal pays ~0.5% of value): the free 0% tier requires a qualifying bond (&gt;=80% LTV) so we earn the</t>
+      <c r="B6" s="32" t="inlineStr">
+        <is>
+          <t>• Free 0% tier REQUIRES a &gt;=80% bond placed with our partner bank (e.g. Nedbank) + our panel conveyancer -&gt; we earn the Nedbank kickback (% of bond).</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="33" t="inlineStr">
-        <is>
-          <t>bank-paid origination referral. Cash buyers / sub-80% bonds instead pay a 0.5% facilitation fee on the price — still ~10-14x</t>
+      <c r="B7" s="32" t="inlineStr">
+        <is>
+          <t>• Otherwise a 1% facilitation fee applies on the price (cash buyers / sub-80% bonds / not using our partners) - still ~6x cheaper than 5-7% agent commission.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="33" t="inlineStr">
-        <is>
-          <t>cheaper than 5-7% agent commission. This removes the cash-deal revenue gap; bonded-share becomes a minor mix assumption, not a cliff.</t>
+      <c r="B8" s="32" t="inlineStr">
+        <is>
+          <t>• Bonded-share is now a MINOR assumption: both paths monetise. Kickback rate is to be NEGOTIATED with the bank (a direct deal may exceed the ~0.5% originator sub-share).</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="33" t="inlineStr"/>
+      <c r="B9" s="32" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="B10" s="35" t="inlineStr">
-        <is>
-          <t>KEY SOURCED ANCHORS (see docs/dataroom/00-assumptions.md for full citations &amp; reliability flags):</t>
+      <c r="B10" s="34" t="inlineStr">
+        <is>
+          <t>AI-LEAN OPERATING MODEL:</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="33" t="inlineStr">
-        <is>
-          <t>• Cape Town: median ~R3.4m, average ~R2.1m; R6m+ = prime freehold band (Lightstone / Property24, 2024–26).</t>
+      <c r="B11" s="32" t="inlineStr">
+        <is>
+          <t>• 50% of headcount are AI agents (concierge/coordination/ops), costed at ~R0.15m/yr each (LLM API + tooling + human oversight) vs ~R0.70-0.78m/yr fully-loaded human.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="33" t="inlineStr">
-        <is>
-          <t>• ~50% of SA transfers are bonded; prime skews more cash — model uses 40% bonded (Lightstone 2024).</t>
+      <c r="B12" s="32" t="inlineStr">
+        <is>
+          <t>• This roughly halves people-cost. Flex the AI share, AI run-cost and human cost on the Assumptions tab.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="33" t="inlineStr">
-        <is>
-          <t>• Bond origination commission paid by banks 1.0–1.9% of loan; referral-partner share ~0.5% (ooba / IOL).</t>
-        </is>
-      </c>
+      <c r="B13" s="32" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="B14" s="33" t="inlineStr">
-        <is>
-          <t>• Estate-agency commission 5–7% + 15% VAT — the consumer saving Sold Direct displaces (Private Property).</t>
+      <c r="B14" s="34" t="inlineStr">
+        <is>
+          <t>KEY SOURCED ANCHORS (full citations &amp; reliability in docs/dataroom/00-assumptions.md):</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="33" t="inlineStr">
-        <is>
-          <t>• WhatsApp service/utility within 24h = free; marketing templates the main paid line (Meta, Jul 2025).</t>
+      <c r="B15" s="32" t="inlineStr">
+        <is>
+          <t>• Cape Town: median ~R3.4m, average ~R2.1m; R6m+ = prime freehold band (Lightstone/Property24 2024-26).</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="33" t="inlineStr">
-        <is>
-          <t>• Proptech ~8.8x EV/revenue globally — discounted to 4–6x for SA early stage (Finro 2025).</t>
+      <c r="B16" s="32" t="inlineStr">
+        <is>
+          <t>• Bond origination commission banks pay 1.0-1.9% of loan; originator referral share ~0.5% (ooba/IOL) - direct bank kickback to be negotiated.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="33" t="inlineStr">
-        <is>
-          <t>• Salaries: eng intermediate ~R48k/mo, senior ~R100k/mo; +~30% load for 13th cheque/benefits (OfferZen 2025).</t>
+      <c r="B17" s="32" t="inlineStr">
+        <is>
+          <t>• Estate-agency commission 5-7% + 15% VAT (Private Property). WhatsApp service/utility within 24h = free (Meta Jul 2025).</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="33" t="inlineStr">
-        <is>
-          <t>• Cautionary comp: Purplebricks (IPO £240m → peak &gt;£1bn → sold for £1, 2023) — CAC discipline is rule #1.</t>
+      <c r="B18" s="32" t="inlineStr">
+        <is>
+          <t>• Proptech ~8.8x EV/revenue globally; discount to 4-6x for SA early stage (Finro 2025). Purplebricks: IPO GBP240m -&gt; sold for GBP1 (CAC discipline).</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="33" t="inlineStr"/>
+      <c r="B19" s="32" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="B20" s="35" t="inlineStr">
-        <is>
-          <t>CONFIRM BEFORE INVESTOR CIRCULATION (model-grade, not audit-grade):</t>
+      <c r="B20" s="34" t="inlineStr">
+        <is>
+          <t>WATCH-OUTS (flag to investors before they do):</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="33" t="inlineStr">
-        <is>
-          <t>1. 0.5% bond referral share (ooba)   2. conveyancing panel %   3. prime transfer counts   4. bonded share in prime.</t>
+      <c r="B21" s="32" t="inlineStr">
+        <is>
+          <t>1. High margins (AI-lean + 1% take) - consider a 'reinvest for growth' case. 2. Tying 0% to one bank (Nedbank) has consumer-choice / PPRA / competition angles - get the agreement + legal sign-off.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="33" t="inlineStr"/>
+      <c r="B22" s="32" t="inlineStr">
+        <is>
+          <t>3. AI agents replacing 50% of roles in Y1 is operationally aggressive - validate with a pilot.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="B23" s="34" t="inlineStr">
-        <is>
-          <t>HOW TO USE: edit amber cells on the Assumptions tab. P&amp;L, Scenarios and Valuation recalculate automatically.</t>
+      <c r="B23" s="32" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="B24" s="33" t="inlineStr">
+        <is>
+          <t>HOW TO USE: edit amber cells on Assumptions. P&amp;L, Scenarios and Valuation recalculate automatically.</t>
         </is>
       </c>
     </row>

--- a/docs/dataroom/sold-direct-model.xlsx
+++ b/docs/dataroom/sold-direct-model.xlsx
@@ -130,9 +130,9 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="7" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -517,10 +517,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:H54"/>
+  <dimension ref="B1:H58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
@@ -532,7 +532,7 @@
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Sold Direct — Model Assumptions (Prime · Nedbank-0% · AI-lean)</t>
+          <t>Sold Direct — Model Assumptions (Prime · 1% fee · AI-lean · bank sponsor)</t>
         </is>
       </c>
     </row>
@@ -559,7 +559,7 @@
     <row r="5">
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Nedbank partner kickback (% of bond)</t>
+          <t>Bond origination referral (% of bond, via ooba)</t>
         </is>
       </c>
       <c r="C5" s="5" t="n">
@@ -691,7 +691,7 @@
     <row r="16">
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Bonded-with-Nedbank share (&gt;=80% -&gt; free)</t>
+          <t>Bonded share (qualifying &gt;=80% bond, any bank)</t>
         </is>
       </c>
       <c r="C16" s="5" t="n">
@@ -740,7 +740,7 @@
     <row r="18">
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>Nedbank kickback / qualifying deal (R)</t>
+          <t>Origination referral / qualifying deal (R)</t>
         </is>
       </c>
       <c r="C18" s="11">
@@ -794,7 +794,7 @@
     <row r="20">
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>Kickback OR fee / deal, blended (R)</t>
+          <t>Referral OR fee / deal, blended (R)</t>
         </is>
       </c>
       <c r="C20" s="11">
@@ -892,7 +892,7 @@
     <row r="25">
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>REGISTERED DEALS BY SCENARIO</t>
+          <t>OTHER REVENUE</t>
         </is>
       </c>
       <c r="C25" s="3" t="n"/>
@@ -932,476 +932,538 @@
     <row r="27">
       <c r="B27" s="4" t="inlineStr">
         <is>
+          <t>Bank headline sponsorship (Rm/yr)</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D27" s="7" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E27" s="7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F27" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G27" s="7" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>REGISTERED DEALS BY SCENARIO</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="n"/>
+      <c r="D29" s="3" t="n"/>
+      <c r="E29" s="3" t="n"/>
+      <c r="F29" s="3" t="n"/>
+      <c r="G29" s="3" t="n"/>
+      <c r="H29" s="3" t="n"/>
+    </row>
+    <row r="30">
+      <c r="C30" s="8" t="inlineStr">
+        <is>
+          <t>Y1</t>
+        </is>
+      </c>
+      <c r="D30" s="8" t="inlineStr">
+        <is>
+          <t>Y2</t>
+        </is>
+      </c>
+      <c r="E30" s="8" t="inlineStr">
+        <is>
+          <t>Y3</t>
+        </is>
+      </c>
+      <c r="F30" s="8" t="inlineStr">
+        <is>
+          <t>Y4</t>
+        </is>
+      </c>
+      <c r="G30" s="8" t="inlineStr">
+        <is>
+          <t>Y5</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="4" t="inlineStr">
+        <is>
           <t>Conservative</t>
         </is>
       </c>
-      <c r="C27" s="15" t="n">
+      <c r="C31" s="15" t="n">
         <v>25</v>
       </c>
-      <c r="D27" s="15" t="n">
+      <c r="D31" s="15" t="n">
         <v>100</v>
       </c>
-      <c r="E27" s="15" t="n">
+      <c r="E31" s="15" t="n">
         <v>280</v>
       </c>
-      <c r="F27" s="15" t="n">
+      <c r="F31" s="15" t="n">
         <v>550</v>
       </c>
-      <c r="G27" s="15" t="n">
+      <c r="G31" s="15" t="n">
         <v>1000</v>
       </c>
-    </row>
-    <row r="28">
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>Base</t>
-        </is>
-      </c>
-      <c r="C28" s="15" t="n">
-        <v>40</v>
-      </c>
-      <c r="D28" s="15" t="n">
-        <v>160</v>
-      </c>
-      <c r="E28" s="15" t="n">
-        <v>450</v>
-      </c>
-      <c r="F28" s="15" t="n">
-        <v>900</v>
-      </c>
-      <c r="G28" s="15" t="n">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>Aggressive</t>
-        </is>
-      </c>
-      <c r="C29" s="15" t="n">
-        <v>60</v>
-      </c>
-      <c r="D29" s="15" t="n">
-        <v>250</v>
-      </c>
-      <c r="E29" s="15" t="n">
-        <v>700</v>
-      </c>
-      <c r="F29" s="15" t="n">
-        <v>1400</v>
-      </c>
-      <c r="G29" s="15" t="n">
-        <v>2600</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t>REVENUE/DEAL MULTIPLIER BY SCENARIO</t>
-        </is>
-      </c>
-      <c r="C31" s="3" t="n"/>
-      <c r="D31" s="3" t="n"/>
-      <c r="E31" s="3" t="n"/>
-      <c r="F31" s="3" t="n"/>
-      <c r="G31" s="3" t="n"/>
-      <c r="H31" s="3" t="n"/>
     </row>
     <row r="32">
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>Conservative</t>
-        </is>
-      </c>
-      <c r="C32" s="16" t="n">
-        <v>0.92</v>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="C32" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="D32" s="15" t="n">
+        <v>160</v>
+      </c>
+      <c r="E32" s="15" t="n">
+        <v>450</v>
+      </c>
+      <c r="F32" s="15" t="n">
+        <v>900</v>
+      </c>
+      <c r="G32" s="15" t="n">
+        <v>1600</v>
       </c>
     </row>
     <row r="33">
       <c r="B33" s="4" t="inlineStr">
         <is>
+          <t>Aggressive</t>
+        </is>
+      </c>
+      <c r="C33" s="15" t="n">
+        <v>60</v>
+      </c>
+      <c r="D33" s="15" t="n">
+        <v>250</v>
+      </c>
+      <c r="E33" s="15" t="n">
+        <v>700</v>
+      </c>
+      <c r="F33" s="15" t="n">
+        <v>1400</v>
+      </c>
+      <c r="G33" s="15" t="n">
+        <v>2600</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>REVENUE/DEAL MULTIPLIER BY SCENARIO</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="n"/>
+      <c r="D35" s="3" t="n"/>
+      <c r="E35" s="3" t="n"/>
+      <c r="F35" s="3" t="n"/>
+      <c r="G35" s="3" t="n"/>
+      <c r="H35" s="3" t="n"/>
+    </row>
+    <row r="36">
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>Conservative</t>
+        </is>
+      </c>
+      <c r="C36" s="16" t="n">
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="4" t="inlineStr">
+        <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="C33" s="16" t="n">
+      <c r="C37" s="16" t="n">
         <v>1</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t>Aggressive</t>
-        </is>
-      </c>
-      <c r="C34" s="16" t="n">
-        <v>1.1</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="3" t="inlineStr">
-        <is>
-          <t>OPERATING EXPENSE INPUTS (BASE)</t>
-        </is>
-      </c>
-      <c r="C36" s="3" t="n"/>
-      <c r="D36" s="3" t="n"/>
-      <c r="E36" s="3" t="n"/>
-      <c r="F36" s="3" t="n"/>
-      <c r="G36" s="3" t="n"/>
-      <c r="H36" s="3" t="n"/>
-    </row>
-    <row r="37">
-      <c r="C37" s="8" t="inlineStr">
-        <is>
-          <t>Y1</t>
-        </is>
-      </c>
-      <c r="D37" s="8" t="inlineStr">
-        <is>
-          <t>Y2</t>
-        </is>
-      </c>
-      <c r="E37" s="8" t="inlineStr">
-        <is>
-          <t>Y3</t>
-        </is>
-      </c>
-      <c r="F37" s="8" t="inlineStr">
-        <is>
-          <t>Y4</t>
-        </is>
-      </c>
-      <c r="G37" s="8" t="inlineStr">
-        <is>
-          <t>Y5</t>
-        </is>
       </c>
     </row>
     <row r="38">
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>Total headcount (workers)</t>
-        </is>
-      </c>
-      <c r="C38" s="15" t="n">
-        <v>6</v>
-      </c>
-      <c r="D38" s="15" t="n">
-        <v>9</v>
-      </c>
-      <c r="E38" s="15" t="n">
-        <v>13</v>
-      </c>
-      <c r="F38" s="15" t="n">
-        <v>18</v>
-      </c>
-      <c r="G38" s="15" t="n">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" s="4" t="inlineStr">
-        <is>
-          <t>AI-agent share of headcount</t>
-        </is>
-      </c>
-      <c r="C39" s="5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D39" s="5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E39" s="5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F39" s="5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G39" s="5" t="n">
-        <v>0.5</v>
+          <t>Aggressive</t>
+        </is>
+      </c>
+      <c r="C38" s="16" t="n">
+        <v>1.1</v>
       </c>
     </row>
     <row r="40">
-      <c r="B40" s="9" t="inlineStr">
-        <is>
-          <t>Human FTEs</t>
-        </is>
-      </c>
-      <c r="C40" s="17">
-        <f>C38*(1-C39)</f>
-        <v/>
-      </c>
-      <c r="D40" s="17">
-        <f>D38*(1-D39)</f>
-        <v/>
-      </c>
-      <c r="E40" s="17">
-        <f>E38*(1-E39)</f>
-        <v/>
-      </c>
-      <c r="F40" s="17">
-        <f>F38*(1-F39)</f>
-        <v/>
-      </c>
-      <c r="G40" s="17">
-        <f>G38*(1-G39)</f>
-        <v/>
-      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>OPERATING EXPENSE INPUTS (BASE)</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="n"/>
+      <c r="D40" s="3" t="n"/>
+      <c r="E40" s="3" t="n"/>
+      <c r="F40" s="3" t="n"/>
+      <c r="G40" s="3" t="n"/>
+      <c r="H40" s="3" t="n"/>
     </row>
     <row r="41">
-      <c r="B41" s="9" t="inlineStr">
-        <is>
-          <t>AI agents</t>
-        </is>
-      </c>
-      <c r="C41" s="17">
-        <f>C38*C39</f>
-        <v/>
-      </c>
-      <c r="D41" s="17">
-        <f>D38*D39</f>
-        <v/>
-      </c>
-      <c r="E41" s="17">
-        <f>E38*E39</f>
-        <v/>
-      </c>
-      <c r="F41" s="17">
-        <f>F38*F39</f>
-        <v/>
-      </c>
-      <c r="G41" s="17">
-        <f>G38*G39</f>
-        <v/>
+      <c r="C41" s="8" t="inlineStr">
+        <is>
+          <t>Y1</t>
+        </is>
+      </c>
+      <c r="D41" s="8" t="inlineStr">
+        <is>
+          <t>Y2</t>
+        </is>
+      </c>
+      <c r="E41" s="8" t="inlineStr">
+        <is>
+          <t>Y3</t>
+        </is>
+      </c>
+      <c r="F41" s="8" t="inlineStr">
+        <is>
+          <t>Y4</t>
+        </is>
+      </c>
+      <c r="G41" s="8" t="inlineStr">
+        <is>
+          <t>Y5</t>
+        </is>
       </c>
     </row>
     <row r="42">
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>Human fully-loaded cost / FTE (Rm/yr)</t>
-        </is>
-      </c>
-      <c r="C42" s="7" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="D42" s="7" t="n">
-        <v>0.722</v>
-      </c>
-      <c r="E42" s="7" t="n">
-        <v>0.738</v>
-      </c>
-      <c r="F42" s="7" t="n">
-        <v>0.761</v>
-      </c>
-      <c r="G42" s="7" t="n">
-        <v>0.779</v>
+          <t>Total headcount (workers)</t>
+        </is>
+      </c>
+      <c r="C42" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="D42" s="15" t="n">
+        <v>9</v>
+      </c>
+      <c r="E42" s="15" t="n">
+        <v>13</v>
+      </c>
+      <c r="F42" s="15" t="n">
+        <v>18</v>
+      </c>
+      <c r="G42" s="15" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="43">
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>AI-agent run cost each (Rm/yr)</t>
-        </is>
-      </c>
-      <c r="C43" s="7" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="D43" s="7" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="E43" s="7" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="F43" s="7" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="G43" s="7" t="n">
-        <v>0.15</v>
+          <t>AI-agent share of headcount</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D43" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E43" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F43" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G43" s="5" t="n">
+        <v>0.5</v>
       </c>
     </row>
     <row r="44">
-      <c r="B44" s="13" t="inlineStr">
-        <is>
-          <t>Payroll + AI agents (Rm)</t>
-        </is>
-      </c>
-      <c r="C44" s="18">
-        <f>C40*C42+C41*C43</f>
-        <v/>
-      </c>
-      <c r="D44" s="18">
-        <f>D40*D42+D41*D43</f>
-        <v/>
-      </c>
-      <c r="E44" s="18">
-        <f>E40*E42+E41*E43</f>
-        <v/>
-      </c>
-      <c r="F44" s="18">
-        <f>F40*F42+F41*F43</f>
-        <v/>
-      </c>
-      <c r="G44" s="18">
-        <f>G40*G42+G41*G43</f>
+      <c r="B44" s="9" t="inlineStr">
+        <is>
+          <t>Human FTEs</t>
+        </is>
+      </c>
+      <c r="C44" s="17">
+        <f>C42*(1-C43)</f>
+        <v/>
+      </c>
+      <c r="D44" s="17">
+        <f>D42*(1-D43)</f>
+        <v/>
+      </c>
+      <c r="E44" s="17">
+        <f>E42*(1-E43)</f>
+        <v/>
+      </c>
+      <c r="F44" s="17">
+        <f>F42*(1-F43)</f>
+        <v/>
+      </c>
+      <c r="G44" s="17">
+        <f>G42*(1-G43)</f>
         <v/>
       </c>
     </row>
     <row r="45">
-      <c r="B45" s="4" t="inlineStr">
-        <is>
-          <t>Marketing (Rm)</t>
-        </is>
-      </c>
-      <c r="C45" s="7" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D45" s="7" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="E45" s="7" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="F45" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="G45" s="7" t="n">
-        <v>5.5</v>
+      <c r="B45" s="9" t="inlineStr">
+        <is>
+          <t>AI agents</t>
+        </is>
+      </c>
+      <c r="C45" s="17">
+        <f>C42*C43</f>
+        <v/>
+      </c>
+      <c r="D45" s="17">
+        <f>D42*D43</f>
+        <v/>
+      </c>
+      <c r="E45" s="17">
+        <f>E42*E43</f>
+        <v/>
+      </c>
+      <c r="F45" s="17">
+        <f>F42*F43</f>
+        <v/>
+      </c>
+      <c r="G45" s="17">
+        <f>G42*G43</f>
+        <v/>
       </c>
     </row>
     <row r="46">
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>Tech &amp; tools (Rm)</t>
+          <t>Human fully-loaded cost / FTE (Rm/yr)</t>
         </is>
       </c>
       <c r="C46" s="7" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="D46" s="7" t="n">
-        <v>0.8</v>
+        <v>0.722</v>
       </c>
       <c r="E46" s="7" t="n">
-        <v>1.2</v>
+        <v>0.738</v>
       </c>
       <c r="F46" s="7" t="n">
-        <v>1.6</v>
+        <v>0.761</v>
       </c>
       <c r="G46" s="7" t="n">
-        <v>2.2</v>
+        <v>0.779</v>
       </c>
     </row>
     <row r="47">
       <c r="B47" s="4" t="inlineStr">
         <is>
+          <t>AI-agent run cost each (Rm/yr)</t>
+        </is>
+      </c>
+      <c r="C47" s="7" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D47" s="7" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E47" s="7" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F47" s="7" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="G47" s="7" t="n">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="13" t="inlineStr">
+        <is>
+          <t>Payroll + AI agents (Rm)</t>
+        </is>
+      </c>
+      <c r="C48" s="18">
+        <f>C44*C46+C45*C47</f>
+        <v/>
+      </c>
+      <c r="D48" s="18">
+        <f>D44*D46+D45*D47</f>
+        <v/>
+      </c>
+      <c r="E48" s="18">
+        <f>E44*E46+E45*E47</f>
+        <v/>
+      </c>
+      <c r="F48" s="18">
+        <f>F44*F46+F45*F47</f>
+        <v/>
+      </c>
+      <c r="G48" s="18">
+        <f>G44*G46+G45*G47</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>Marketing (Rm)</t>
+        </is>
+      </c>
+      <c r="C49" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D49" s="7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E49" s="7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F49" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="G49" s="7" t="n">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>Tech &amp; tools (Rm)</t>
+        </is>
+      </c>
+      <c r="C50" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D50" s="7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E50" s="7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F50" s="7" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="G50" s="7" t="n">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="4" t="inlineStr">
+        <is>
           <t>Legal / compliance / insurance (Rm)</t>
         </is>
       </c>
-      <c r="C47" s="7" t="n">
+      <c r="C51" s="7" t="n">
         <v>0.6</v>
       </c>
-      <c r="D47" s="7" t="n">
+      <c r="D51" s="7" t="n">
         <v>0.9</v>
       </c>
-      <c r="E47" s="7" t="n">
+      <c r="E51" s="7" t="n">
         <v>1.2</v>
       </c>
-      <c r="F47" s="7" t="n">
+      <c r="F51" s="7" t="n">
         <v>1.6</v>
       </c>
-      <c r="G47" s="7" t="n">
+      <c r="G51" s="7" t="n">
         <v>2</v>
       </c>
-    </row>
-    <row r="48">
-      <c r="B48" s="4" t="inlineStr">
-        <is>
-          <t>G&amp;A / office / other (Rm)</t>
-        </is>
-      </c>
-      <c r="C48" s="7" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D48" s="7" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E48" s="7" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="F48" s="7" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="G48" s="7" t="n">
-        <v>2.4</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="B49" s="13" t="inlineStr">
-        <is>
-          <t>Total opex — BASE (Rm)</t>
-        </is>
-      </c>
-      <c r="C49" s="18">
-        <f>SUM(C44:C48)</f>
-        <v/>
-      </c>
-      <c r="D49" s="18">
-        <f>SUM(D44:D48)</f>
-        <v/>
-      </c>
-      <c r="E49" s="18">
-        <f>SUM(E44:E48)</f>
-        <v/>
-      </c>
-      <c r="F49" s="18">
-        <f>SUM(F44:F48)</f>
-        <v/>
-      </c>
-      <c r="G49" s="18">
-        <f>SUM(G44:G48)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="51">
-      <c r="B51" s="3" t="inlineStr">
-        <is>
-          <t>OPEX SCALING BY SCENARIO</t>
-        </is>
-      </c>
-      <c r="C51" s="3" t="n"/>
-      <c r="D51" s="3" t="n"/>
-      <c r="E51" s="3" t="n"/>
-      <c r="F51" s="3" t="n"/>
-      <c r="G51" s="3" t="n"/>
-      <c r="H51" s="3" t="n"/>
     </row>
     <row r="52">
       <c r="B52" s="4" t="inlineStr">
         <is>
+          <t>G&amp;A / office / other (Rm)</t>
+        </is>
+      </c>
+      <c r="C52" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D52" s="7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E52" s="7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F52" s="7" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G52" s="7" t="n">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="13" t="inlineStr">
+        <is>
+          <t>Total opex — BASE (Rm)</t>
+        </is>
+      </c>
+      <c r="C53" s="18">
+        <f>SUM(C48:C52)</f>
+        <v/>
+      </c>
+      <c r="D53" s="18">
+        <f>SUM(D48:D52)</f>
+        <v/>
+      </c>
+      <c r="E53" s="18">
+        <f>SUM(E48:E52)</f>
+        <v/>
+      </c>
+      <c r="F53" s="18">
+        <f>SUM(F48:F52)</f>
+        <v/>
+      </c>
+      <c r="G53" s="18">
+        <f>SUM(G48:G52)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>OPEX SCALING BY SCENARIO</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="n"/>
+      <c r="D55" s="3" t="n"/>
+      <c r="E55" s="3" t="n"/>
+      <c r="F55" s="3" t="n"/>
+      <c r="G55" s="3" t="n"/>
+      <c r="H55" s="3" t="n"/>
+    </row>
+    <row r="56">
+      <c r="B56" s="4" t="inlineStr">
+        <is>
           <t>Conservative</t>
         </is>
       </c>
-      <c r="C52" s="16" t="n">
+      <c r="C56" s="16" t="n">
         <v>0.72</v>
       </c>
     </row>
-    <row r="53">
-      <c r="B53" s="4" t="inlineStr">
+    <row r="57">
+      <c r="B57" s="4" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="C53" s="16" t="n">
+      <c r="C57" s="16" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="54">
-      <c r="B54" s="4" t="inlineStr">
+    <row r="58">
+      <c r="B58" s="4" t="inlineStr">
         <is>
           <t>Aggressive</t>
         </is>
       </c>
-      <c r="C54" s="16" t="n">
+      <c r="C58" s="16" t="n">
         <v>1.3</v>
       </c>
     </row>
@@ -1417,7 +1479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:G18"/>
+  <dimension ref="B1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="2" max="2"/>
@@ -1469,23 +1531,23 @@
         </is>
       </c>
       <c r="C4" s="20">
-        <f>Assumptions!C28</f>
+        <f>Assumptions!C32</f>
         <v/>
       </c>
       <c r="D4" s="20">
-        <f>Assumptions!D28</f>
+        <f>Assumptions!D32</f>
         <v/>
       </c>
       <c r="E4" s="20">
-        <f>Assumptions!E28</f>
+        <f>Assumptions!E32</f>
         <v/>
       </c>
       <c r="F4" s="20">
-        <f>Assumptions!F28</f>
+        <f>Assumptions!F32</f>
         <v/>
       </c>
       <c r="G4" s="20">
-        <f>Assumptions!G28</f>
+        <f>Assumptions!G32</f>
         <v/>
       </c>
     </row>
@@ -1496,49 +1558,49 @@
         </is>
       </c>
       <c r="C5" s="21">
-        <f>Assumptions!C23*Assumptions!$C$33</f>
+        <f>Assumptions!C23*Assumptions!$C$37</f>
         <v/>
       </c>
       <c r="D5" s="21">
-        <f>Assumptions!D23*Assumptions!$C$33</f>
+        <f>Assumptions!D23*Assumptions!$C$37</f>
         <v/>
       </c>
       <c r="E5" s="21">
-        <f>Assumptions!E23*Assumptions!$C$33</f>
+        <f>Assumptions!E23*Assumptions!$C$37</f>
         <v/>
       </c>
       <c r="F5" s="21">
-        <f>Assumptions!F23*Assumptions!$C$33</f>
+        <f>Assumptions!F23*Assumptions!$C$37</f>
         <v/>
       </c>
       <c r="G5" s="21">
-        <f>Assumptions!G23*Assumptions!$C$33</f>
+        <f>Assumptions!G23*Assumptions!$C$37</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="22" t="inlineStr">
-        <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="C6" s="23">
+      <c r="B6" s="19" t="inlineStr">
+        <is>
+          <t>Transactional revenue</t>
+        </is>
+      </c>
+      <c r="C6" s="22">
         <f>C4*C5/1000000</f>
         <v/>
       </c>
-      <c r="D6" s="23">
+      <c r="D6" s="22">
         <f>D4*D5/1000000</f>
         <v/>
       </c>
-      <c r="E6" s="23">
+      <c r="E6" s="22">
         <f>E4*E5/1000000</f>
         <v/>
       </c>
-      <c r="F6" s="23">
+      <c r="F6" s="22">
         <f>F4*F5/1000000</f>
         <v/>
       </c>
-      <c r="G6" s="23">
+      <c r="G6" s="22">
         <f>G4*G5/1000000</f>
         <v/>
       </c>
@@ -1546,324 +1608,378 @@
     <row r="7">
       <c r="B7" s="19" t="inlineStr">
         <is>
-          <t>COGS</t>
-        </is>
-      </c>
-      <c r="C7" s="24">
-        <f>-C6*(1-Assumptions!$C$7)</f>
-        <v/>
-      </c>
-      <c r="D7" s="24">
-        <f>-D6*(1-Assumptions!$C$7)</f>
-        <v/>
-      </c>
-      <c r="E7" s="24">
-        <f>-E6*(1-Assumptions!$C$7)</f>
-        <v/>
-      </c>
-      <c r="F7" s="24">
-        <f>-F6*(1-Assumptions!$C$7)</f>
-        <v/>
-      </c>
-      <c r="G7" s="24">
-        <f>-G6*(1-Assumptions!$C$7)</f>
+          <t>Bank sponsorship</t>
+        </is>
+      </c>
+      <c r="C7" s="22">
+        <f>Assumptions!C27</f>
+        <v/>
+      </c>
+      <c r="D7" s="22">
+        <f>Assumptions!D27</f>
+        <v/>
+      </c>
+      <c r="E7" s="22">
+        <f>Assumptions!E27</f>
+        <v/>
+      </c>
+      <c r="F7" s="22">
+        <f>Assumptions!F27</f>
+        <v/>
+      </c>
+      <c r="G7" s="22">
+        <f>Assumptions!G27</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="25" t="inlineStr">
-        <is>
-          <t>Gross profit</t>
-        </is>
-      </c>
-      <c r="C8" s="26">
-        <f>C6*Assumptions!$C$7</f>
-        <v/>
-      </c>
-      <c r="D8" s="26">
-        <f>D6*Assumptions!$C$7</f>
-        <v/>
-      </c>
-      <c r="E8" s="26">
-        <f>E6*Assumptions!$C$7</f>
-        <v/>
-      </c>
-      <c r="F8" s="26">
-        <f>F6*Assumptions!$C$7</f>
-        <v/>
-      </c>
-      <c r="G8" s="26">
-        <f>G6*Assumptions!$C$7</f>
+      <c r="B8" s="23" t="inlineStr">
+        <is>
+          <t>Total revenue</t>
+        </is>
+      </c>
+      <c r="C8" s="24">
+        <f>C6+C7</f>
+        <v/>
+      </c>
+      <c r="D8" s="24">
+        <f>D6+D7</f>
+        <v/>
+      </c>
+      <c r="E8" s="24">
+        <f>E6+E7</f>
+        <v/>
+      </c>
+      <c r="F8" s="24">
+        <f>F6+F7</f>
+        <v/>
+      </c>
+      <c r="G8" s="24">
+        <f>G6+G7</f>
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="B9" s="19" t="inlineStr">
         <is>
-          <t>Gross margin</t>
-        </is>
-      </c>
-      <c r="C9" s="27">
-        <f>IF(C6=0,"",C8/C6)</f>
-        <v/>
-      </c>
-      <c r="D9" s="27">
-        <f>IF(D6=0,"",D8/D6)</f>
-        <v/>
-      </c>
-      <c r="E9" s="27">
-        <f>IF(E6=0,"",E8/E6)</f>
-        <v/>
-      </c>
-      <c r="F9" s="27">
-        <f>IF(F6=0,"",F8/F6)</f>
-        <v/>
-      </c>
-      <c r="G9" s="27">
-        <f>IF(G6=0,"",G8/G6)</f>
+          <t>COGS</t>
+        </is>
+      </c>
+      <c r="C9" s="22">
+        <f>-C8*(1-Assumptions!$C$7)</f>
+        <v/>
+      </c>
+      <c r="D9" s="22">
+        <f>-D8*(1-Assumptions!$C$7)</f>
+        <v/>
+      </c>
+      <c r="E9" s="22">
+        <f>-E8*(1-Assumptions!$C$7)</f>
+        <v/>
+      </c>
+      <c r="F9" s="22">
+        <f>-F8*(1-Assumptions!$C$7)</f>
+        <v/>
+      </c>
+      <c r="G9" s="22">
+        <f>-G8*(1-Assumptions!$C$7)</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="19" t="inlineStr">
-        <is>
-          <t>Payroll + AI agents</t>
-        </is>
-      </c>
-      <c r="C10" s="24">
-        <f>Assumptions!C44</f>
-        <v/>
-      </c>
-      <c r="D10" s="24">
-        <f>Assumptions!D44</f>
-        <v/>
-      </c>
-      <c r="E10" s="24">
-        <f>Assumptions!E44</f>
-        <v/>
-      </c>
-      <c r="F10" s="24">
-        <f>Assumptions!F44</f>
-        <v/>
-      </c>
-      <c r="G10" s="24">
-        <f>Assumptions!G44</f>
+      <c r="B10" s="25" t="inlineStr">
+        <is>
+          <t>Gross profit</t>
+        </is>
+      </c>
+      <c r="C10" s="26">
+        <f>C8*Assumptions!$C$7</f>
+        <v/>
+      </c>
+      <c r="D10" s="26">
+        <f>D8*Assumptions!$C$7</f>
+        <v/>
+      </c>
+      <c r="E10" s="26">
+        <f>E8*Assumptions!$C$7</f>
+        <v/>
+      </c>
+      <c r="F10" s="26">
+        <f>F8*Assumptions!$C$7</f>
+        <v/>
+      </c>
+      <c r="G10" s="26">
+        <f>G8*Assumptions!$C$7</f>
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="19" t="inlineStr">
         <is>
-          <t>Marketing</t>
-        </is>
-      </c>
-      <c r="C11" s="24">
-        <f>Assumptions!C45</f>
-        <v/>
-      </c>
-      <c r="D11" s="24">
-        <f>Assumptions!D45</f>
-        <v/>
-      </c>
-      <c r="E11" s="24">
-        <f>Assumptions!E45</f>
-        <v/>
-      </c>
-      <c r="F11" s="24">
-        <f>Assumptions!F45</f>
-        <v/>
-      </c>
-      <c r="G11" s="24">
-        <f>Assumptions!G45</f>
+          <t>Gross margin</t>
+        </is>
+      </c>
+      <c r="C11" s="27">
+        <f>IF(C8=0,"",C10/C8)</f>
+        <v/>
+      </c>
+      <c r="D11" s="27">
+        <f>IF(D8=0,"",D10/D8)</f>
+        <v/>
+      </c>
+      <c r="E11" s="27">
+        <f>IF(E8=0,"",E10/E8)</f>
+        <v/>
+      </c>
+      <c r="F11" s="27">
+        <f>IF(F8=0,"",F10/F8)</f>
+        <v/>
+      </c>
+      <c r="G11" s="27">
+        <f>IF(G8=0,"",G10/G8)</f>
         <v/>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="19" t="inlineStr">
         <is>
-          <t>Tech &amp; tools</t>
-        </is>
-      </c>
-      <c r="C12" s="24">
-        <f>Assumptions!C46</f>
-        <v/>
-      </c>
-      <c r="D12" s="24">
-        <f>Assumptions!D46</f>
-        <v/>
-      </c>
-      <c r="E12" s="24">
-        <f>Assumptions!E46</f>
-        <v/>
-      </c>
-      <c r="F12" s="24">
-        <f>Assumptions!F46</f>
-        <v/>
-      </c>
-      <c r="G12" s="24">
-        <f>Assumptions!G46</f>
+          <t>Payroll + AI agents</t>
+        </is>
+      </c>
+      <c r="C12" s="22">
+        <f>Assumptions!C48</f>
+        <v/>
+      </c>
+      <c r="D12" s="22">
+        <f>Assumptions!D48</f>
+        <v/>
+      </c>
+      <c r="E12" s="22">
+        <f>Assumptions!E48</f>
+        <v/>
+      </c>
+      <c r="F12" s="22">
+        <f>Assumptions!F48</f>
+        <v/>
+      </c>
+      <c r="G12" s="22">
+        <f>Assumptions!G48</f>
         <v/>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="19" t="inlineStr">
         <is>
-          <t>Legal / compliance / insurance</t>
-        </is>
-      </c>
-      <c r="C13" s="24">
-        <f>Assumptions!C47</f>
-        <v/>
-      </c>
-      <c r="D13" s="24">
-        <f>Assumptions!D47</f>
-        <v/>
-      </c>
-      <c r="E13" s="24">
-        <f>Assumptions!E47</f>
-        <v/>
-      </c>
-      <c r="F13" s="24">
-        <f>Assumptions!F47</f>
-        <v/>
-      </c>
-      <c r="G13" s="24">
-        <f>Assumptions!G47</f>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="C13" s="22">
+        <f>Assumptions!C49</f>
+        <v/>
+      </c>
+      <c r="D13" s="22">
+        <f>Assumptions!D49</f>
+        <v/>
+      </c>
+      <c r="E13" s="22">
+        <f>Assumptions!E49</f>
+        <v/>
+      </c>
+      <c r="F13" s="22">
+        <f>Assumptions!F49</f>
+        <v/>
+      </c>
+      <c r="G13" s="22">
+        <f>Assumptions!G49</f>
         <v/>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="19" t="inlineStr">
         <is>
+          <t>Tech &amp; tools</t>
+        </is>
+      </c>
+      <c r="C14" s="22">
+        <f>Assumptions!C50</f>
+        <v/>
+      </c>
+      <c r="D14" s="22">
+        <f>Assumptions!D50</f>
+        <v/>
+      </c>
+      <c r="E14" s="22">
+        <f>Assumptions!E50</f>
+        <v/>
+      </c>
+      <c r="F14" s="22">
+        <f>Assumptions!F50</f>
+        <v/>
+      </c>
+      <c r="G14" s="22">
+        <f>Assumptions!G50</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="19" t="inlineStr">
+        <is>
+          <t>Legal / compliance / insurance</t>
+        </is>
+      </c>
+      <c r="C15" s="22">
+        <f>Assumptions!C51</f>
+        <v/>
+      </c>
+      <c r="D15" s="22">
+        <f>Assumptions!D51</f>
+        <v/>
+      </c>
+      <c r="E15" s="22">
+        <f>Assumptions!E51</f>
+        <v/>
+      </c>
+      <c r="F15" s="22">
+        <f>Assumptions!F51</f>
+        <v/>
+      </c>
+      <c r="G15" s="22">
+        <f>Assumptions!G51</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="19" t="inlineStr">
+        <is>
           <t>G&amp;A / office / other</t>
         </is>
       </c>
-      <c r="C14" s="24">
-        <f>Assumptions!C48</f>
-        <v/>
-      </c>
-      <c r="D14" s="24">
-        <f>Assumptions!D48</f>
-        <v/>
-      </c>
-      <c r="E14" s="24">
-        <f>Assumptions!E48</f>
-        <v/>
-      </c>
-      <c r="F14" s="24">
-        <f>Assumptions!F48</f>
-        <v/>
-      </c>
-      <c r="G14" s="24">
-        <f>Assumptions!G48</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="25" t="inlineStr">
+      <c r="C16" s="22">
+        <f>Assumptions!C52</f>
+        <v/>
+      </c>
+      <c r="D16" s="22">
+        <f>Assumptions!D52</f>
+        <v/>
+      </c>
+      <c r="E16" s="22">
+        <f>Assumptions!E52</f>
+        <v/>
+      </c>
+      <c r="F16" s="22">
+        <f>Assumptions!F52</f>
+        <v/>
+      </c>
+      <c r="G16" s="22">
+        <f>Assumptions!G52</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="25" t="inlineStr">
         <is>
           <t>Total operating expenses</t>
         </is>
       </c>
-      <c r="C15" s="26">
-        <f>SUM(C10:C14)</f>
-        <v/>
-      </c>
-      <c r="D15" s="26">
-        <f>SUM(D10:D14)</f>
-        <v/>
-      </c>
-      <c r="E15" s="26">
-        <f>SUM(E10:E14)</f>
-        <v/>
-      </c>
-      <c r="F15" s="26">
-        <f>SUM(F10:F14)</f>
-        <v/>
-      </c>
-      <c r="G15" s="26">
-        <f>SUM(G10:G14)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" s="22" t="inlineStr">
+      <c r="C17" s="26">
+        <f>SUM(C12:C16)</f>
+        <v/>
+      </c>
+      <c r="D17" s="26">
+        <f>SUM(D12:D16)</f>
+        <v/>
+      </c>
+      <c r="E17" s="26">
+        <f>SUM(E12:E16)</f>
+        <v/>
+      </c>
+      <c r="F17" s="26">
+        <f>SUM(F12:F16)</f>
+        <v/>
+      </c>
+      <c r="G17" s="26">
+        <f>SUM(G12:G16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="23" t="inlineStr">
         <is>
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="C16" s="23">
-        <f>C8-C15</f>
-        <v/>
-      </c>
-      <c r="D16" s="23">
-        <f>D8-D15</f>
-        <v/>
-      </c>
-      <c r="E16" s="23">
-        <f>E8-E15</f>
-        <v/>
-      </c>
-      <c r="F16" s="23">
-        <f>F8-F15</f>
-        <v/>
-      </c>
-      <c r="G16" s="23">
-        <f>G8-G15</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" s="19" t="inlineStr">
+      <c r="C18" s="24">
+        <f>C10-C17</f>
+        <v/>
+      </c>
+      <c r="D18" s="24">
+        <f>D10-D17</f>
+        <v/>
+      </c>
+      <c r="E18" s="24">
+        <f>E10-E17</f>
+        <v/>
+      </c>
+      <c r="F18" s="24">
+        <f>F10-F17</f>
+        <v/>
+      </c>
+      <c r="G18" s="24">
+        <f>G10-G17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="19" t="inlineStr">
         <is>
           <t>EBITDA margin</t>
         </is>
       </c>
-      <c r="C17" s="27">
-        <f>IF(C6=0,"",C16/C6)</f>
-        <v/>
-      </c>
-      <c r="D17" s="27">
-        <f>IF(D6=0,"",D16/D6)</f>
-        <v/>
-      </c>
-      <c r="E17" s="27">
-        <f>IF(E6=0,"",E16/E6)</f>
-        <v/>
-      </c>
-      <c r="F17" s="27">
-        <f>IF(F6=0,"",F16/F6)</f>
-        <v/>
-      </c>
-      <c r="G17" s="27">
-        <f>IF(G6=0,"",G16/G6)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="25" t="inlineStr">
+      <c r="C19" s="27">
+        <f>IF(C8=0,"",C18/C8)</f>
+        <v/>
+      </c>
+      <c r="D19" s="27">
+        <f>IF(D8=0,"",D18/D8)</f>
+        <v/>
+      </c>
+      <c r="E19" s="27">
+        <f>IF(E8=0,"",E18/E8)</f>
+        <v/>
+      </c>
+      <c r="F19" s="27">
+        <f>IF(F8=0,"",F18/F8)</f>
+        <v/>
+      </c>
+      <c r="G19" s="27">
+        <f>IF(G8=0,"",G18/G8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="25" t="inlineStr">
         <is>
           <t>Cumulative EBITDA (cash proxy)</t>
         </is>
       </c>
-      <c r="C18" s="26">
-        <f>C16</f>
-        <v/>
-      </c>
-      <c r="D18" s="26">
-        <f>C18+D16</f>
-        <v/>
-      </c>
-      <c r="E18" s="26">
-        <f>D18+E16</f>
-        <v/>
-      </c>
-      <c r="F18" s="26">
-        <f>E18+F16</f>
-        <v/>
-      </c>
-      <c r="G18" s="26">
-        <f>F18+G16</f>
+      <c r="C20" s="26">
+        <f>C18</f>
+        <v/>
+      </c>
+      <c r="D20" s="26">
+        <f>C20+D18</f>
+        <v/>
+      </c>
+      <c r="E20" s="26">
+        <f>D20+E18</f>
+        <v/>
+      </c>
+      <c r="F20" s="26">
+        <f>E20+F18</f>
+        <v/>
+      </c>
+      <c r="G20" s="26">
+        <f>F20+G18</f>
         <v/>
       </c>
     </row>
@@ -1943,24 +2059,24 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="C5" s="24">
-        <f>Assumptions!C27*Assumptions!C23*Assumptions!$C$32/1000000</f>
-        <v/>
-      </c>
-      <c r="D5" s="24">
-        <f>Assumptions!D27*Assumptions!D23*Assumptions!$C$32/1000000</f>
-        <v/>
-      </c>
-      <c r="E5" s="24">
-        <f>Assumptions!E27*Assumptions!E23*Assumptions!$C$32/1000000</f>
-        <v/>
-      </c>
-      <c r="F5" s="24">
-        <f>Assumptions!F27*Assumptions!F23*Assumptions!$C$32/1000000</f>
-        <v/>
-      </c>
-      <c r="G5" s="24">
-        <f>Assumptions!G27*Assumptions!G23*Assumptions!$C$32/1000000</f>
+      <c r="C5" s="22">
+        <f>Assumptions!C31*Assumptions!C23*Assumptions!$C$36/1000000+Assumptions!C27</f>
+        <v/>
+      </c>
+      <c r="D5" s="22">
+        <f>Assumptions!D31*Assumptions!D23*Assumptions!$C$36/1000000+Assumptions!D27</f>
+        <v/>
+      </c>
+      <c r="E5" s="22">
+        <f>Assumptions!E31*Assumptions!E23*Assumptions!$C$36/1000000+Assumptions!E27</f>
+        <v/>
+      </c>
+      <c r="F5" s="22">
+        <f>Assumptions!F31*Assumptions!F23*Assumptions!$C$36/1000000+Assumptions!F27</f>
+        <v/>
+      </c>
+      <c r="G5" s="22">
+        <f>Assumptions!G31*Assumptions!G23*Assumptions!$C$36/1000000+Assumptions!G27</f>
         <v/>
       </c>
     </row>
@@ -1970,23 +2086,23 @@
           <t>Gross profit</t>
         </is>
       </c>
-      <c r="C6" s="24">
+      <c r="C6" s="22">
         <f>C5*Assumptions!$C$7</f>
         <v/>
       </c>
-      <c r="D6" s="24">
+      <c r="D6" s="22">
         <f>D5*Assumptions!$C$7</f>
         <v/>
       </c>
-      <c r="E6" s="24">
+      <c r="E6" s="22">
         <f>E5*Assumptions!$C$7</f>
         <v/>
       </c>
-      <c r="F6" s="24">
+      <c r="F6" s="22">
         <f>F5*Assumptions!$C$7</f>
         <v/>
       </c>
-      <c r="G6" s="24">
+      <c r="G6" s="22">
         <f>G5*Assumptions!$C$7</f>
         <v/>
       </c>
@@ -1997,24 +2113,24 @@
           <t>Operating expenses</t>
         </is>
       </c>
-      <c r="C7" s="24">
-        <f>Assumptions!C49*Assumptions!$C$52</f>
-        <v/>
-      </c>
-      <c r="D7" s="24">
-        <f>Assumptions!D49*Assumptions!$C$52</f>
-        <v/>
-      </c>
-      <c r="E7" s="24">
-        <f>Assumptions!E49*Assumptions!$C$52</f>
-        <v/>
-      </c>
-      <c r="F7" s="24">
-        <f>Assumptions!F49*Assumptions!$C$52</f>
-        <v/>
-      </c>
-      <c r="G7" s="24">
-        <f>Assumptions!G49*Assumptions!$C$52</f>
+      <c r="C7" s="22">
+        <f>Assumptions!C53*Assumptions!$C$56</f>
+        <v/>
+      </c>
+      <c r="D7" s="22">
+        <f>Assumptions!D53*Assumptions!$C$56</f>
+        <v/>
+      </c>
+      <c r="E7" s="22">
+        <f>Assumptions!E53*Assumptions!$C$56</f>
+        <v/>
+      </c>
+      <c r="F7" s="22">
+        <f>Assumptions!F53*Assumptions!$C$56</f>
+        <v/>
+      </c>
+      <c r="G7" s="22">
+        <f>Assumptions!G53*Assumptions!$C$56</f>
         <v/>
       </c>
     </row>
@@ -2051,23 +2167,23 @@
           <t>Cumulative EBITDA</t>
         </is>
       </c>
-      <c r="C9" s="24">
+      <c r="C9" s="22">
         <f>C8</f>
         <v/>
       </c>
-      <c r="D9" s="24">
+      <c r="D9" s="22">
         <f>C9+D8</f>
         <v/>
       </c>
-      <c r="E9" s="24">
+      <c r="E9" s="22">
         <f>D9+E8</f>
         <v/>
       </c>
-      <c r="F9" s="24">
+      <c r="F9" s="22">
         <f>E9+F8</f>
         <v/>
       </c>
-      <c r="G9" s="24">
+      <c r="G9" s="22">
         <f>F9+G8</f>
         <v/>
       </c>
@@ -2145,24 +2261,24 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="C15" s="24">
-        <f>Assumptions!C28*Assumptions!C23*Assumptions!$C$33/1000000</f>
-        <v/>
-      </c>
-      <c r="D15" s="24">
-        <f>Assumptions!D28*Assumptions!D23*Assumptions!$C$33/1000000</f>
-        <v/>
-      </c>
-      <c r="E15" s="24">
-        <f>Assumptions!E28*Assumptions!E23*Assumptions!$C$33/1000000</f>
-        <v/>
-      </c>
-      <c r="F15" s="24">
-        <f>Assumptions!F28*Assumptions!F23*Assumptions!$C$33/1000000</f>
-        <v/>
-      </c>
-      <c r="G15" s="24">
-        <f>Assumptions!G28*Assumptions!G23*Assumptions!$C$33/1000000</f>
+      <c r="C15" s="22">
+        <f>Assumptions!C32*Assumptions!C23*Assumptions!$C$37/1000000+Assumptions!C27</f>
+        <v/>
+      </c>
+      <c r="D15" s="22">
+        <f>Assumptions!D32*Assumptions!D23*Assumptions!$C$37/1000000+Assumptions!D27</f>
+        <v/>
+      </c>
+      <c r="E15" s="22">
+        <f>Assumptions!E32*Assumptions!E23*Assumptions!$C$37/1000000+Assumptions!E27</f>
+        <v/>
+      </c>
+      <c r="F15" s="22">
+        <f>Assumptions!F32*Assumptions!F23*Assumptions!$C$37/1000000+Assumptions!F27</f>
+        <v/>
+      </c>
+      <c r="G15" s="22">
+        <f>Assumptions!G32*Assumptions!G23*Assumptions!$C$37/1000000+Assumptions!G27</f>
         <v/>
       </c>
     </row>
@@ -2172,23 +2288,23 @@
           <t>Gross profit</t>
         </is>
       </c>
-      <c r="C16" s="24">
+      <c r="C16" s="22">
         <f>C15*Assumptions!$C$7</f>
         <v/>
       </c>
-      <c r="D16" s="24">
+      <c r="D16" s="22">
         <f>D15*Assumptions!$C$7</f>
         <v/>
       </c>
-      <c r="E16" s="24">
+      <c r="E16" s="22">
         <f>E15*Assumptions!$C$7</f>
         <v/>
       </c>
-      <c r="F16" s="24">
+      <c r="F16" s="22">
         <f>F15*Assumptions!$C$7</f>
         <v/>
       </c>
-      <c r="G16" s="24">
+      <c r="G16" s="22">
         <f>G15*Assumptions!$C$7</f>
         <v/>
       </c>
@@ -2199,24 +2315,24 @@
           <t>Operating expenses</t>
         </is>
       </c>
-      <c r="C17" s="24">
-        <f>Assumptions!C49*Assumptions!$C$53</f>
-        <v/>
-      </c>
-      <c r="D17" s="24">
-        <f>Assumptions!D49*Assumptions!$C$53</f>
-        <v/>
-      </c>
-      <c r="E17" s="24">
-        <f>Assumptions!E49*Assumptions!$C$53</f>
-        <v/>
-      </c>
-      <c r="F17" s="24">
-        <f>Assumptions!F49*Assumptions!$C$53</f>
-        <v/>
-      </c>
-      <c r="G17" s="24">
-        <f>Assumptions!G49*Assumptions!$C$53</f>
+      <c r="C17" s="22">
+        <f>Assumptions!C53*Assumptions!$C$57</f>
+        <v/>
+      </c>
+      <c r="D17" s="22">
+        <f>Assumptions!D53*Assumptions!$C$57</f>
+        <v/>
+      </c>
+      <c r="E17" s="22">
+        <f>Assumptions!E53*Assumptions!$C$57</f>
+        <v/>
+      </c>
+      <c r="F17" s="22">
+        <f>Assumptions!F53*Assumptions!$C$57</f>
+        <v/>
+      </c>
+      <c r="G17" s="22">
+        <f>Assumptions!G53*Assumptions!$C$57</f>
         <v/>
       </c>
     </row>
@@ -2253,23 +2369,23 @@
           <t>Cumulative EBITDA</t>
         </is>
       </c>
-      <c r="C19" s="24">
+      <c r="C19" s="22">
         <f>C18</f>
         <v/>
       </c>
-      <c r="D19" s="24">
+      <c r="D19" s="22">
         <f>C19+D18</f>
         <v/>
       </c>
-      <c r="E19" s="24">
+      <c r="E19" s="22">
         <f>D19+E18</f>
         <v/>
       </c>
-      <c r="F19" s="24">
+      <c r="F19" s="22">
         <f>E19+F18</f>
         <v/>
       </c>
-      <c r="G19" s="24">
+      <c r="G19" s="22">
         <f>F19+G18</f>
         <v/>
       </c>
@@ -2347,24 +2463,24 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="C25" s="24">
-        <f>Assumptions!C29*Assumptions!C23*Assumptions!$C$34/1000000</f>
-        <v/>
-      </c>
-      <c r="D25" s="24">
-        <f>Assumptions!D29*Assumptions!D23*Assumptions!$C$34/1000000</f>
-        <v/>
-      </c>
-      <c r="E25" s="24">
-        <f>Assumptions!E29*Assumptions!E23*Assumptions!$C$34/1000000</f>
-        <v/>
-      </c>
-      <c r="F25" s="24">
-        <f>Assumptions!F29*Assumptions!F23*Assumptions!$C$34/1000000</f>
-        <v/>
-      </c>
-      <c r="G25" s="24">
-        <f>Assumptions!G29*Assumptions!G23*Assumptions!$C$34/1000000</f>
+      <c r="C25" s="22">
+        <f>Assumptions!C33*Assumptions!C23*Assumptions!$C$38/1000000+Assumptions!C27</f>
+        <v/>
+      </c>
+      <c r="D25" s="22">
+        <f>Assumptions!D33*Assumptions!D23*Assumptions!$C$38/1000000+Assumptions!D27</f>
+        <v/>
+      </c>
+      <c r="E25" s="22">
+        <f>Assumptions!E33*Assumptions!E23*Assumptions!$C$38/1000000+Assumptions!E27</f>
+        <v/>
+      </c>
+      <c r="F25" s="22">
+        <f>Assumptions!F33*Assumptions!F23*Assumptions!$C$38/1000000+Assumptions!F27</f>
+        <v/>
+      </c>
+      <c r="G25" s="22">
+        <f>Assumptions!G33*Assumptions!G23*Assumptions!$C$38/1000000+Assumptions!G27</f>
         <v/>
       </c>
     </row>
@@ -2374,23 +2490,23 @@
           <t>Gross profit</t>
         </is>
       </c>
-      <c r="C26" s="24">
+      <c r="C26" s="22">
         <f>C25*Assumptions!$C$7</f>
         <v/>
       </c>
-      <c r="D26" s="24">
+      <c r="D26" s="22">
         <f>D25*Assumptions!$C$7</f>
         <v/>
       </c>
-      <c r="E26" s="24">
+      <c r="E26" s="22">
         <f>E25*Assumptions!$C$7</f>
         <v/>
       </c>
-      <c r="F26" s="24">
+      <c r="F26" s="22">
         <f>F25*Assumptions!$C$7</f>
         <v/>
       </c>
-      <c r="G26" s="24">
+      <c r="G26" s="22">
         <f>G25*Assumptions!$C$7</f>
         <v/>
       </c>
@@ -2401,24 +2517,24 @@
           <t>Operating expenses</t>
         </is>
       </c>
-      <c r="C27" s="24">
-        <f>Assumptions!C49*Assumptions!$C$54</f>
-        <v/>
-      </c>
-      <c r="D27" s="24">
-        <f>Assumptions!D49*Assumptions!$C$54</f>
-        <v/>
-      </c>
-      <c r="E27" s="24">
-        <f>Assumptions!E49*Assumptions!$C$54</f>
-        <v/>
-      </c>
-      <c r="F27" s="24">
-        <f>Assumptions!F49*Assumptions!$C$54</f>
-        <v/>
-      </c>
-      <c r="G27" s="24">
-        <f>Assumptions!G49*Assumptions!$C$54</f>
+      <c r="C27" s="22">
+        <f>Assumptions!C53*Assumptions!$C$58</f>
+        <v/>
+      </c>
+      <c r="D27" s="22">
+        <f>Assumptions!D53*Assumptions!$C$58</f>
+        <v/>
+      </c>
+      <c r="E27" s="22">
+        <f>Assumptions!E53*Assumptions!$C$58</f>
+        <v/>
+      </c>
+      <c r="F27" s="22">
+        <f>Assumptions!F53*Assumptions!$C$58</f>
+        <v/>
+      </c>
+      <c r="G27" s="22">
+        <f>Assumptions!G53*Assumptions!$C$58</f>
         <v/>
       </c>
     </row>
@@ -2455,23 +2571,23 @@
           <t>Cumulative EBITDA</t>
         </is>
       </c>
-      <c r="C29" s="24">
+      <c r="C29" s="22">
         <f>C28</f>
         <v/>
       </c>
-      <c r="D29" s="24">
+      <c r="D29" s="22">
         <f>C29+D28</f>
         <v/>
       </c>
-      <c r="E29" s="24">
+      <c r="E29" s="22">
         <f>D29+E28</f>
         <v/>
       </c>
-      <c r="F29" s="24">
+      <c r="F29" s="22">
         <f>E29+F28</f>
         <v/>
       </c>
-      <c r="G29" s="24">
+      <c r="G29" s="22">
         <f>F29+G28</f>
         <v/>
       </c>
@@ -2596,15 +2712,15 @@
           <t>Cumulative cash low-point</t>
         </is>
       </c>
-      <c r="C39" s="24">
+      <c r="C39" s="22">
         <f>MIN(C9:G9)</f>
         <v/>
       </c>
-      <c r="D39" s="24">
+      <c r="D39" s="22">
         <f>MIN(C19:G19)</f>
         <v/>
       </c>
-      <c r="E39" s="24">
+      <c r="E39" s="22">
         <f>MIN(C29:G29)</f>
         <v/>
       </c>
@@ -2744,15 +2860,15 @@
           <t xml:space="preserve">  in USD (m, approx)</t>
         </is>
       </c>
-      <c r="C6" s="24">
+      <c r="C6" s="22">
         <f>C5/Assumptions!$C$8</f>
         <v/>
       </c>
-      <c r="D6" s="24">
+      <c r="D6" s="22">
         <f>D5/Assumptions!$C$8</f>
         <v/>
       </c>
-      <c r="E6" s="24">
+      <c r="E6" s="22">
         <f>E5/Assumptions!$C$8</f>
         <v/>
       </c>
@@ -2783,7 +2899,7 @@
           <t>Seed round (USD m approx)</t>
         </is>
       </c>
-      <c r="C10" s="24">
+      <c r="C10" s="22">
         <f>C9/Assumptions!$C$8</f>
         <v/>
       </c>
@@ -2816,11 +2932,11 @@
           <t>Y5 revenue (Rm)</t>
         </is>
       </c>
-      <c r="C14" s="24">
+      <c r="C14" s="22">
         <f>Scenarios!D36</f>
         <v/>
       </c>
-      <c r="D14" s="24">
+      <c r="D14" s="22">
         <f>Scenarios!D36</f>
         <v/>
       </c>
@@ -2896,7 +3012,7 @@
           <t>Seed raise (Rm)</t>
         </is>
       </c>
-      <c r="C21" s="24">
+      <c r="C21" s="22">
         <f>C9</f>
         <v/>
       </c>
@@ -2939,7 +3055,7 @@
           <t>Y5 revenue (Rm)</t>
         </is>
       </c>
-      <c r="C26" s="24">
+      <c r="C26" s="22">
         <f>Scenarios!E36</f>
         <v/>
       </c>
@@ -2967,10 +3083,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:B24"/>
+  <dimension ref="B1:B23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="115" customWidth="1" min="2" max="2"/>
+    <col width="118" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2996,52 +3112,52 @@
     <row r="5">
       <c r="B5" s="34" t="inlineStr">
         <is>
-          <t>MONETISATION (every deal pays a take-rate of value):</t>
+          <t>MONETISATION (legally clean - no bank exclusivity):</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="B6" s="32" t="inlineStr">
         <is>
-          <t>• Free 0% tier REQUIRES a &gt;=80% bond placed with our partner bank (e.g. Nedbank) + our panel conveyancer -&gt; we earn the Nedbank kickback (% of bond).</t>
+          <t>• Free 0% requires a qualifying &gt;=80% bond via our MULTI-BANK originator (ooba) + our conveyancer. Buyer keeps full rate choice; we earn the origination referral (~0.5% of bond).</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="32" t="inlineStr">
         <is>
-          <t>• Otherwise a 1% facilitation fee applies on the price (cash buyers / sub-80% bonds / not using our partners) - still ~6x cheaper than 5-7% agent commission.</t>
+          <t>• Otherwise a 1% facilitation fee on the price (cash / sub-80% / not using our partners) - still ~6x cheaper than 5-7% agent commission.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="32" t="inlineStr">
         <is>
-          <t>• Bonded-share is now a MINOR assumption: both paths monetise. Kickback rate is to be NEGOTIATED with the bank (a direct deal may exceed the ~0.5% originator sub-share).</t>
+          <t>• Bank HEADLINE SPONSORSHIP: a bank pays an annual fee to be the featured sponsor / brand on the platform (advertising, not steering) - high-margin, grows with audience.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="32" t="inlineStr"/>
+      <c r="B9" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  NOTE: making a specific bank a prerequisite for 0% is legally grey (consumer-steering / competition / PPRA) - replaced by the bank-agnostic referral + sponsorship above.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="B10" s="34" t="inlineStr">
+      <c r="B10" s="32" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="B11" s="34" t="inlineStr">
         <is>
           <t>AI-LEAN OPERATING MODEL:</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" s="32" t="inlineStr">
-        <is>
-          <t>• 50% of headcount are AI agents (concierge/coordination/ops), costed at ~R0.15m/yr each (LLM API + tooling + human oversight) vs ~R0.70-0.78m/yr fully-loaded human.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="32" t="inlineStr">
         <is>
-          <t>• This roughly halves people-cost. Flex the AI share, AI run-cost and human cost on the Assumptions tab.</t>
+          <t>• 50% of headcount are AI agents (concierge/coordination/ops) at ~R0.15m/yr each vs ~R0.70-0.78m/yr fully-loaded human - roughly halves people-cost.</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3167,7 @@
     <row r="14">
       <c r="B14" s="34" t="inlineStr">
         <is>
-          <t>KEY SOURCED ANCHORS (full citations &amp; reliability in docs/dataroom/00-assumptions.md):</t>
+          <t>KEY SOURCED ANCHORS (full citations in docs/dataroom/00-assumptions.md):</t>
         </is>
       </c>
     </row>
@@ -3065,53 +3181,46 @@
     <row r="16">
       <c r="B16" s="32" t="inlineStr">
         <is>
-          <t>• Bond origination commission banks pay 1.0-1.9% of loan; originator referral share ~0.5% (ooba/IOL) - direct bank kickback to be negotiated.</t>
+          <t>• Bond origination commission 1.0-1.9% of loan; originator referral share ~0.5% (ooba/IOL). Estate agency 5-7% + 15% VAT (Private Property).</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="32" t="inlineStr">
         <is>
-          <t>• Estate-agency commission 5-7% + 15% VAT (Private Property). WhatsApp service/utility within 24h = free (Meta Jul 2025).</t>
+          <t>• Proptech ~8.8x EV/revenue globally; discount to 4-6x for SA early stage (Finro 2025). Purplebricks: IPO GBP240m -&gt; sold for GBP1 (CAC discipline).</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="32" t="inlineStr">
-        <is>
-          <t>• Proptech ~8.8x EV/revenue globally; discount to 4-6x for SA early stage (Finro 2025). Purplebricks: IPO GBP240m -&gt; sold for GBP1 (CAC discipline).</t>
-        </is>
-      </c>
+      <c r="B18" s="32" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="B19" s="32" t="inlineStr"/>
+      <c r="B19" s="34" t="inlineStr">
+        <is>
+          <t>WATCH-OUTS:</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="B20" s="34" t="inlineStr">
-        <is>
-          <t>WATCH-OUTS (flag to investors before they do):</t>
+      <c r="B20" s="32" t="inlineStr">
+        <is>
+          <t>1. High margins (AI-lean + 1% take + sponsorship) - present a 'reinvest for growth' case. 2. AI agents at 50% of roles in Y1 is aggressive - validate with a pilot.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="32" t="inlineStr">
         <is>
-          <t>1. High margins (AI-lean + 1% take) - consider a 'reinvest for growth' case. 2. Tying 0% to one bank (Nedbank) has consumer-choice / PPRA / competition angles - get the agreement + legal sign-off.</t>
+          <t>3. Sponsorship value scales with real audience/traffic - keep Y1 conservative until reach is proven.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="32" t="inlineStr">
-        <is>
-          <t>3. AI agents replacing 50% of roles in Y1 is operationally aggressive - validate with a pilot.</t>
-        </is>
-      </c>
+      <c r="B22" s="32" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="B23" s="32" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="B24" s="33" t="inlineStr">
+      <c r="B23" s="33" t="inlineStr">
         <is>
           <t>HOW TO USE: edit amber cells on Assumptions. P&amp;L, Scenarios and Valuation recalculate automatically.</t>
         </is>

--- a/docs/dataroom/sold-direct-model.xlsx
+++ b/docs/dataroom/sold-direct-model.xlsx
@@ -11,7 +11,8 @@
     <sheet name="P&amp;L (Base)" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Scenarios" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Capital &amp; Valuation" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Notes &amp; Sources" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Ancillary Revenue" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Notes &amp; Sources" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -25,7 +26,7 @@
     <numFmt numFmtId="165" formatCode="#,##0.0"/>
     <numFmt numFmtId="166" formatCode="R#,##0"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -63,6 +64,10 @@
     <font>
       <b val="1"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <color rgb="00334155"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="6">
@@ -105,7 +110,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -139,6 +144,11 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="7" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
@@ -517,7 +527,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:H58"/>
+  <dimension ref="B1:H63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="2" max="2"/>
@@ -936,25 +946,25 @@
         </is>
       </c>
       <c r="C27" s="7" t="n">
-        <v>0.3</v>
+        <v>3</v>
       </c>
       <c r="D27" s="7" t="n">
-        <v>0.75</v>
+        <v>4</v>
       </c>
       <c r="E27" s="7" t="n">
-        <v>1.5</v>
+        <v>5</v>
       </c>
       <c r="F27" s="7" t="n">
-        <v>3</v>
+        <v>6.5</v>
       </c>
       <c r="G27" s="7" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="29">
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>REGISTERED DEALS BY SCENARIO</t>
+          <t>REGISTERED DEALS BY SCENARIO (reinvest-for-growth)</t>
         </is>
       </c>
       <c r="C29" s="3" t="n"/>
@@ -998,19 +1008,19 @@
         </is>
       </c>
       <c r="C31" s="15" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D31" s="15" t="n">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="E31" s="15" t="n">
-        <v>280</v>
+        <v>400</v>
       </c>
       <c r="F31" s="15" t="n">
-        <v>550</v>
+        <v>950</v>
       </c>
       <c r="G31" s="15" t="n">
-        <v>1000</v>
+        <v>1900</v>
       </c>
     </row>
     <row r="32">
@@ -1020,19 +1030,19 @@
         </is>
       </c>
       <c r="C32" s="15" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="D32" s="15" t="n">
-        <v>160</v>
+        <v>220</v>
       </c>
       <c r="E32" s="15" t="n">
-        <v>450</v>
+        <v>650</v>
       </c>
       <c r="F32" s="15" t="n">
-        <v>900</v>
+        <v>1500</v>
       </c>
       <c r="G32" s="15" t="n">
-        <v>1600</v>
+        <v>2900</v>
       </c>
     </row>
     <row r="33">
@@ -1042,19 +1052,19 @@
         </is>
       </c>
       <c r="C33" s="15" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="D33" s="15" t="n">
-        <v>250</v>
+        <v>350</v>
       </c>
       <c r="E33" s="15" t="n">
-        <v>700</v>
+        <v>1000</v>
       </c>
       <c r="F33" s="15" t="n">
-        <v>1400</v>
+        <v>2400</v>
       </c>
       <c r="G33" s="15" t="n">
-        <v>2600</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="35">
@@ -1147,19 +1157,19 @@
         </is>
       </c>
       <c r="C42" s="15" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D42" s="15" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E42" s="15" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="F42" s="15" t="n">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="G42" s="15" t="n">
-        <v>24</v>
+        <v>48</v>
       </c>
     </row>
     <row r="43">
@@ -1312,23 +1322,23 @@
     <row r="49">
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Marketing (Rm)</t>
+          <t>Marketing — above-the-line (Rm)</t>
         </is>
       </c>
       <c r="C49" s="7" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="D49" s="7" t="n">
-        <v>1.2</v>
+        <v>8</v>
       </c>
       <c r="E49" s="7" t="n">
-        <v>2.5</v>
+        <v>18</v>
       </c>
       <c r="F49" s="7" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="G49" s="7" t="n">
-        <v>5.5</v>
+        <v>50</v>
       </c>
     </row>
     <row r="50">
@@ -1338,19 +1348,19 @@
         </is>
       </c>
       <c r="C50" s="7" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="D50" s="7" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E50" s="7" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="F50" s="7" t="n">
-        <v>1.6</v>
+        <v>2.8</v>
       </c>
       <c r="G50" s="7" t="n">
-        <v>2.2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="51">
@@ -1360,19 +1370,19 @@
         </is>
       </c>
       <c r="C51" s="7" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="D51" s="7" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="E51" s="7" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="F51" s="7" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="G51" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="52">
@@ -1382,19 +1392,19 @@
         </is>
       </c>
       <c r="C52" s="7" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="D52" s="7" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E52" s="7" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="F52" s="7" t="n">
-        <v>1.8</v>
+        <v>3.2</v>
       </c>
       <c r="G52" s="7" t="n">
-        <v>2.4</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="53">
@@ -1465,6 +1475,51 @@
       </c>
       <c r="C58" s="16" t="n">
         <v>1.3</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>ANCILLARY / ECOSYSTEM REVENUE (optional — see Ancillary Revenue tab)</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="n"/>
+      <c r="D60" s="3" t="n"/>
+      <c r="E60" s="3" t="n"/>
+      <c r="F60" s="3" t="n"/>
+      <c r="G60" s="3" t="n"/>
+      <c r="H60" s="3" t="n"/>
+    </row>
+    <row r="61">
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>Include ancillary in P&amp;L?  (1 = yes, 0 = no)</t>
+        </is>
+      </c>
+      <c r="C61" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" s="9" t="inlineStr">
+        <is>
+          <t>Realistic additional captured / deal (R)</t>
+        </is>
+      </c>
+      <c r="C62" s="11">
+        <f>'Ancillary Revenue'!G22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" s="9" t="inlineStr">
+        <is>
+          <t>Ancillary added / deal (R)  = toggle x captured</t>
+        </is>
+      </c>
+      <c r="C63" s="11">
+        <f>C61*C62</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -1554,27 +1609,27 @@
     <row r="5">
       <c r="B5" s="19" t="inlineStr">
         <is>
-          <t>Revenue per deal (R)</t>
+          <t>Revenue per deal (R, incl. ancillary if on)</t>
         </is>
       </c>
       <c r="C5" s="21">
-        <f>Assumptions!C23*Assumptions!$C$37</f>
+        <f>Assumptions!C23*Assumptions!$C$37+Assumptions!$C$63</f>
         <v/>
       </c>
       <c r="D5" s="21">
-        <f>Assumptions!D23*Assumptions!$C$37</f>
+        <f>Assumptions!D23*Assumptions!$C$37+Assumptions!$C$63</f>
         <v/>
       </c>
       <c r="E5" s="21">
-        <f>Assumptions!E23*Assumptions!$C$37</f>
+        <f>Assumptions!E23*Assumptions!$C$37+Assumptions!$C$63</f>
         <v/>
       </c>
       <c r="F5" s="21">
-        <f>Assumptions!F23*Assumptions!$C$37</f>
+        <f>Assumptions!F23*Assumptions!$C$37+Assumptions!$C$63</f>
         <v/>
       </c>
       <c r="G5" s="21">
-        <f>Assumptions!G23*Assumptions!$C$37</f>
+        <f>Assumptions!G23*Assumptions!$C$37+Assumptions!$C$63</f>
         <v/>
       </c>
     </row>
@@ -2060,23 +2115,23 @@
         </is>
       </c>
       <c r="C5" s="22">
-        <f>Assumptions!C31*Assumptions!C23*Assumptions!$C$36/1000000+Assumptions!C27</f>
+        <f>Assumptions!C31*(Assumptions!C23*Assumptions!$C$36+Assumptions!$C$63)/1000000+Assumptions!C27</f>
         <v/>
       </c>
       <c r="D5" s="22">
-        <f>Assumptions!D31*Assumptions!D23*Assumptions!$C$36/1000000+Assumptions!D27</f>
+        <f>Assumptions!D31*(Assumptions!D23*Assumptions!$C$36+Assumptions!$C$63)/1000000+Assumptions!D27</f>
         <v/>
       </c>
       <c r="E5" s="22">
-        <f>Assumptions!E31*Assumptions!E23*Assumptions!$C$36/1000000+Assumptions!E27</f>
+        <f>Assumptions!E31*(Assumptions!E23*Assumptions!$C$36+Assumptions!$C$63)/1000000+Assumptions!E27</f>
         <v/>
       </c>
       <c r="F5" s="22">
-        <f>Assumptions!F31*Assumptions!F23*Assumptions!$C$36/1000000+Assumptions!F27</f>
+        <f>Assumptions!F31*(Assumptions!F23*Assumptions!$C$36+Assumptions!$C$63)/1000000+Assumptions!F27</f>
         <v/>
       </c>
       <c r="G5" s="22">
-        <f>Assumptions!G31*Assumptions!G23*Assumptions!$C$36/1000000+Assumptions!G27</f>
+        <f>Assumptions!G31*(Assumptions!G23*Assumptions!$C$36+Assumptions!$C$63)/1000000+Assumptions!G27</f>
         <v/>
       </c>
     </row>
@@ -2262,23 +2317,23 @@
         </is>
       </c>
       <c r="C15" s="22">
-        <f>Assumptions!C32*Assumptions!C23*Assumptions!$C$37/1000000+Assumptions!C27</f>
+        <f>Assumptions!C32*(Assumptions!C23*Assumptions!$C$37+Assumptions!$C$63)/1000000+Assumptions!C27</f>
         <v/>
       </c>
       <c r="D15" s="22">
-        <f>Assumptions!D32*Assumptions!D23*Assumptions!$C$37/1000000+Assumptions!D27</f>
+        <f>Assumptions!D32*(Assumptions!D23*Assumptions!$C$37+Assumptions!$C$63)/1000000+Assumptions!D27</f>
         <v/>
       </c>
       <c r="E15" s="22">
-        <f>Assumptions!E32*Assumptions!E23*Assumptions!$C$37/1000000+Assumptions!E27</f>
+        <f>Assumptions!E32*(Assumptions!E23*Assumptions!$C$37+Assumptions!$C$63)/1000000+Assumptions!E27</f>
         <v/>
       </c>
       <c r="F15" s="22">
-        <f>Assumptions!F32*Assumptions!F23*Assumptions!$C$37/1000000+Assumptions!F27</f>
+        <f>Assumptions!F32*(Assumptions!F23*Assumptions!$C$37+Assumptions!$C$63)/1000000+Assumptions!F27</f>
         <v/>
       </c>
       <c r="G15" s="22">
-        <f>Assumptions!G32*Assumptions!G23*Assumptions!$C$37/1000000+Assumptions!G27</f>
+        <f>Assumptions!G32*(Assumptions!G23*Assumptions!$C$37+Assumptions!$C$63)/1000000+Assumptions!G27</f>
         <v/>
       </c>
     </row>
@@ -2464,23 +2519,23 @@
         </is>
       </c>
       <c r="C25" s="22">
-        <f>Assumptions!C33*Assumptions!C23*Assumptions!$C$38/1000000+Assumptions!C27</f>
+        <f>Assumptions!C33*(Assumptions!C23*Assumptions!$C$38+Assumptions!$C$63)/1000000+Assumptions!C27</f>
         <v/>
       </c>
       <c r="D25" s="22">
-        <f>Assumptions!D33*Assumptions!D23*Assumptions!$C$38/1000000+Assumptions!D27</f>
+        <f>Assumptions!D33*(Assumptions!D23*Assumptions!$C$38+Assumptions!$C$63)/1000000+Assumptions!D27</f>
         <v/>
       </c>
       <c r="E25" s="22">
-        <f>Assumptions!E33*Assumptions!E23*Assumptions!$C$38/1000000+Assumptions!E27</f>
+        <f>Assumptions!E33*(Assumptions!E23*Assumptions!$C$38+Assumptions!$C$63)/1000000+Assumptions!E27</f>
         <v/>
       </c>
       <c r="F25" s="22">
-        <f>Assumptions!F33*Assumptions!F23*Assumptions!$C$38/1000000+Assumptions!F27</f>
+        <f>Assumptions!F33*(Assumptions!F23*Assumptions!$C$38+Assumptions!$C$63)/1000000+Assumptions!F27</f>
         <v/>
       </c>
       <c r="G25" s="22">
-        <f>Assumptions!G33*Assumptions!G23*Assumptions!$C$38/1000000+Assumptions!G27</f>
+        <f>Assumptions!G33*(Assumptions!G23*Assumptions!$C$38+Assumptions!$C$63)/1000000+Assumptions!G27</f>
         <v/>
       </c>
     </row>
@@ -3079,148 +3134,644 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="000EA5E9"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B1:G25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Ancillary / Ecosystem Revenue — the value of the database</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Referral &amp; commission streams unlocked by owning the homeowner relationship + data. Optional: toggle into the P&amp;L on Assumptions!C61.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="29" t="inlineStr">
+        <is>
+          <t>Revenue stream</t>
+        </is>
+      </c>
+      <c r="C4" s="29" t="inlineStr">
+        <is>
+          <t>Low (R)</t>
+        </is>
+      </c>
+      <c r="D4" s="29" t="inlineStr">
+        <is>
+          <t>High (R)</t>
+        </is>
+      </c>
+      <c r="E4" s="29" t="inlineStr">
+        <is>
+          <t>Midpoint (R)</t>
+        </is>
+      </c>
+      <c r="F4" s="29" t="inlineStr">
+        <is>
+          <t>Attach %</t>
+        </is>
+      </c>
+      <c r="G4" s="29" t="inlineStr">
+        <is>
+          <t>Captured/deal (R)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="19" t="inlineStr">
+        <is>
+          <t>Homeowners insurance commission</t>
+        </is>
+      </c>
+      <c r="C5" s="31" t="n">
+        <v>1500</v>
+      </c>
+      <c r="D5" s="31" t="n">
+        <v>4000</v>
+      </c>
+      <c r="E5" s="32">
+        <f>AVERAGE(C5:D5)</f>
+        <v/>
+      </c>
+      <c r="F5" s="33" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G5" s="32">
+        <f>E5*F5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="19" t="inlineStr">
+        <is>
+          <t>Household contents insurance</t>
+        </is>
+      </c>
+      <c r="C6" s="31" t="n">
+        <v>500</v>
+      </c>
+      <c r="D6" s="31" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E6" s="32">
+        <f>AVERAGE(C6:D6)</f>
+        <v/>
+      </c>
+      <c r="F6" s="33" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G6" s="32">
+        <f>E6*F6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="19" t="inlineStr">
+        <is>
+          <t>Conveyancing referral/marketing fee (already in core)</t>
+        </is>
+      </c>
+      <c r="C7" s="31" t="n">
+        <v>3000</v>
+      </c>
+      <c r="D7" s="31" t="n">
+        <v>8000</v>
+      </c>
+      <c r="E7" s="32">
+        <f>AVERAGE(C7:D7)</f>
+        <v/>
+      </c>
+      <c r="F7" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="32">
+        <f>E7*F7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="19" t="inlineStr">
+        <is>
+          <t>Moving company referral</t>
+        </is>
+      </c>
+      <c r="C8" s="31" t="n">
+        <v>500</v>
+      </c>
+      <c r="D8" s="31" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E8" s="32">
+        <f>AVERAGE(C8:D8)</f>
+        <v/>
+      </c>
+      <c r="F8" s="33" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G8" s="32">
+        <f>E8*F8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="19" t="inlineStr">
+        <is>
+          <t>Fibre / internet installation</t>
+        </is>
+      </c>
+      <c r="C9" s="31" t="n">
+        <v>500</v>
+      </c>
+      <c r="D9" s="31" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E9" s="32">
+        <f>AVERAGE(C9:D9)</f>
+        <v/>
+      </c>
+      <c r="F9" s="33" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G9" s="32">
+        <f>E9*F9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="19" t="inlineStr">
+        <is>
+          <t>Security system installation</t>
+        </is>
+      </c>
+      <c r="C10" s="31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D10" s="31" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E10" s="32">
+        <f>AVERAGE(C10:D10)</f>
+        <v/>
+      </c>
+      <c r="F10" s="33" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="G10" s="32">
+        <f>E10*F10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="19" t="inlineStr">
+        <is>
+          <t>Utility connection service</t>
+        </is>
+      </c>
+      <c r="C11" s="31" t="n">
+        <v>250</v>
+      </c>
+      <c r="D11" s="31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E11" s="32">
+        <f>AVERAGE(C11:D11)</f>
+        <v/>
+      </c>
+      <c r="F11" s="33" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G11" s="32">
+        <f>E11*F11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="19" t="inlineStr">
+        <is>
+          <t>Home warranty / product upsell</t>
+        </is>
+      </c>
+      <c r="C12" s="31" t="n">
+        <v>500</v>
+      </c>
+      <c r="D12" s="31" t="n">
+        <v>2500</v>
+      </c>
+      <c r="E12" s="32">
+        <f>AVERAGE(C12:D12)</f>
+        <v/>
+      </c>
+      <c r="F12" s="33" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G12" s="32">
+        <f>E12*F12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="19" t="inlineStr">
+        <is>
+          <t>Compliance certificates (already in core add-ons)</t>
+        </is>
+      </c>
+      <c r="C13" s="31" t="n">
+        <v>500</v>
+      </c>
+      <c r="D13" s="31" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E13" s="32">
+        <f>AVERAGE(C13:D13)</f>
+        <v/>
+      </c>
+      <c r="F13" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="32">
+        <f>E13*F13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="19" t="inlineStr">
+        <is>
+          <t>Solar installation referral</t>
+        </is>
+      </c>
+      <c r="C14" s="31" t="n">
+        <v>5000</v>
+      </c>
+      <c r="D14" s="31" t="n">
+        <v>20000</v>
+      </c>
+      <c r="E14" s="32">
+        <f>AVERAGE(C14:D14)</f>
+        <v/>
+      </c>
+      <c r="F14" s="33" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G14" s="32">
+        <f>E14*F14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="19" t="inlineStr">
+        <is>
+          <t>Home improvement / renovation referrals</t>
+        </is>
+      </c>
+      <c r="C15" s="31" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D15" s="31" t="n">
+        <v>15000</v>
+      </c>
+      <c r="E15" s="32">
+        <f>AVERAGE(C15:D15)</f>
+        <v/>
+      </c>
+      <c r="F15" s="33" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="G15" s="32">
+        <f>E15*F15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="19" t="inlineStr">
+        <is>
+          <t>Storage solutions referral</t>
+        </is>
+      </c>
+      <c r="C16" s="31" t="n">
+        <v>500</v>
+      </c>
+      <c r="D16" s="31" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E16" s="32">
+        <f>AVERAGE(C16:D16)</f>
+        <v/>
+      </c>
+      <c r="F16" s="33" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G16" s="32">
+        <f>E16*F16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="19" t="inlineStr">
+        <is>
+          <t>Short-term insurance cross-sell (car/business)</t>
+        </is>
+      </c>
+      <c r="C17" s="31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D17" s="31" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E17" s="32">
+        <f>AVERAGE(C17:D17)</f>
+        <v/>
+      </c>
+      <c r="F17" s="33" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G17" s="32">
+        <f>E17*F17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="19" t="inlineStr">
+        <is>
+          <t>Life cover linked to the bond</t>
+        </is>
+      </c>
+      <c r="C18" s="31" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D18" s="31" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E18" s="32">
+        <f>AVERAGE(C18:D18)</f>
+        <v/>
+      </c>
+      <c r="F18" s="33" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="G18" s="32">
+        <f>E18*F18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="19" t="inlineStr">
+        <is>
+          <t>Estate planning / will services</t>
+        </is>
+      </c>
+      <c r="C19" s="31" t="n">
+        <v>500</v>
+      </c>
+      <c r="D19" s="31" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E19" s="32">
+        <f>AVERAGE(C19:D19)</f>
+        <v/>
+      </c>
+      <c r="F19" s="33" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G19" s="32">
+        <f>E19*F19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="23" t="inlineStr">
+        <is>
+          <t>FULL ecosystem potential / customer (sum of midpoints)</t>
+        </is>
+      </c>
+      <c r="E21" s="34">
+        <f>SUM(E5:E19)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="23" t="inlineStr">
+        <is>
+          <t>Realistic ADDITIONAL captured / deal (sum of captured)</t>
+        </is>
+      </c>
+      <c r="G22" s="34">
+        <f>SUM(G5:G19)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Conveyancing &amp; compliance certs are already counted in the core model (attach set to 0 here to avoid double-counting).</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="35" t="inlineStr">
+        <is>
+          <t>Strategic point: each registered customer is worth up to ~R50k of ecosystem referral revenue. Even ~10% capture ≈ R5k/deal — the database is the moat.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
     <tabColor rgb="0064748B"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:B23"/>
+  <dimension ref="B1:B28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="118" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="B1" s="31" t="inlineStr">
+      <c r="B1" s="36" t="inlineStr">
         <is>
           <t>Sold Direct — model notes &amp; sources</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="B2" s="32" t="inlineStr"/>
+      <c r="B2" s="37" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="B3" s="33" t="inlineStr">
+      <c r="B3" s="38" t="inlineStr">
         <is>
           <t>Strategy: prime / upper-market focus (Atlantic Seaboard, City Bowl, Southern Suburbs, Constantia; then prime JHB-north &amp; Umhlanga).</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="32" t="inlineStr"/>
+      <c r="B4" s="37" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="B5" s="34" t="inlineStr">
+      <c r="B5" s="39" t="inlineStr">
         <is>
           <t>MONETISATION (legally clean - no bank exclusivity):</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="32" t="inlineStr">
+      <c r="B6" s="37" t="inlineStr">
         <is>
           <t>• Free 0% requires a qualifying &gt;=80% bond via our MULTI-BANK originator (ooba) + our conveyancer. Buyer keeps full rate choice; we earn the origination referral (~0.5% of bond).</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="32" t="inlineStr">
+      <c r="B7" s="37" t="inlineStr">
         <is>
           <t>• Otherwise a 1% facilitation fee on the price (cash / sub-80% / not using our partners) - still ~6x cheaper than 5-7% agent commission.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="32" t="inlineStr">
+      <c r="B8" s="37" t="inlineStr">
         <is>
           <t>• Bank HEADLINE SPONSORSHIP: a bank pays an annual fee to be the featured sponsor / brand on the platform (advertising, not steering) - high-margin, grows with audience.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="32" t="inlineStr">
+      <c r="B9" s="37" t="inlineStr">
         <is>
           <t xml:space="preserve">  NOTE: making a specific bank a prerequisite for 0% is legally grey (consumer-steering / competition / PPRA) - replaced by the bank-agnostic referral + sponsorship above.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="32" t="inlineStr"/>
+      <c r="B10" s="37" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="B11" s="34" t="inlineStr">
+      <c r="B11" s="39" t="inlineStr">
+        <is>
+          <t>THE DATABASE / ECOSYSTEM (see Ancillary Revenue tab):</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="37" t="inlineStr">
+        <is>
+          <t>• Owning the homeowner relationship unlocks a referral menu worth ~R50k of ecosystem revenue per customer (insurance, solar, moving, fibre, security, life cover, etc.).</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="37" t="inlineStr">
+        <is>
+          <t>• Modelled conservatively as OPTIONAL: ~R5k additional captured per deal (~10% blended capture). Toggle into the P&amp;L on Assumptions!C61 (default off).</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="37" t="inlineStr">
+        <is>
+          <t>• This is the moat and the expansion-revenue story - default off keeps the headline P&amp;L conservative; turning it on adds ~R14m to Y5 base revenue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="37" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="B16" s="39" t="inlineStr">
         <is>
           <t>AI-LEAN OPERATING MODEL:</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="B12" s="32" t="inlineStr">
+    <row r="17">
+      <c r="B17" s="37" t="inlineStr">
         <is>
           <t>• 50% of headcount are AI agents (concierge/coordination/ops) at ~R0.15m/yr each vs ~R0.70-0.78m/yr fully-loaded human - roughly halves people-cost.</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="B13" s="32" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="B14" s="34" t="inlineStr">
+    <row r="18">
+      <c r="B18" s="37" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="B19" s="39" t="inlineStr">
         <is>
           <t>KEY SOURCED ANCHORS (full citations in docs/dataroom/00-assumptions.md):</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="B15" s="32" t="inlineStr">
+    <row r="20">
+      <c r="B20" s="37" t="inlineStr">
         <is>
           <t>• Cape Town: median ~R3.4m, average ~R2.1m; R6m+ = prime freehold band (Lightstone/Property24 2024-26).</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="B16" s="32" t="inlineStr">
+    <row r="21">
+      <c r="B21" s="37" t="inlineStr">
         <is>
           <t>• Bond origination commission 1.0-1.9% of loan; originator referral share ~0.5% (ooba/IOL). Estate agency 5-7% + 15% VAT (Private Property).</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="B17" s="32" t="inlineStr">
+    <row r="22">
+      <c r="B22" s="37" t="inlineStr">
         <is>
           <t>• Proptech ~8.8x EV/revenue globally; discount to 4-6x for SA early stage (Finro 2025). Purplebricks: IPO GBP240m -&gt; sold for GBP1 (CAC discipline).</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="B18" s="32" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="B19" s="34" t="inlineStr">
+    <row r="23">
+      <c r="B23" s="37" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="B24" s="39" t="inlineStr">
         <is>
           <t>WATCH-OUTS:</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="B20" s="32" t="inlineStr">
+    <row r="25">
+      <c r="B25" s="37" t="inlineStr">
         <is>
           <t>1. High margins (AI-lean + 1% take + sponsorship) - present a 'reinvest for growth' case. 2. AI agents at 50% of roles in Y1 is aggressive - validate with a pilot.</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="B21" s="32" t="inlineStr">
+    <row r="26">
+      <c r="B26" s="37" t="inlineStr">
         <is>
           <t>3. Sponsorship value scales with real audience/traffic - keep Y1 conservative until reach is proven.</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="B22" s="32" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="B23" s="33" t="inlineStr">
+    <row r="27">
+      <c r="B27" s="37" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="B28" s="38" t="inlineStr">
         <is>
           <t>HOW TO USE: edit amber cells on Assumptions. P&amp;L, Scenarios and Valuation recalculate automatically.</t>
         </is>

--- a/docs/dataroom/sold-direct-model.xlsx
+++ b/docs/dataroom/sold-direct-model.xlsx
@@ -11,8 +11,11 @@
     <sheet name="Scenarios" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Market Sizing" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Capital &amp; Valuation" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Ancillary Revenue" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Notes &amp; Sources" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Use of Funds" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Competitive Landscape" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Risk Register" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Ancillary Revenue" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Notes &amp; Sources" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1" iterateDelta="0.0001"/>
@@ -29,7 +32,7 @@
     <numFmt numFmtId="168" formatCode="[$$-409]#,##0;\([$$-409]#,##0\);&quot;-&quot;"/>
     <numFmt numFmtId="169" formatCode="R#,##0"/>
   </numFmts>
-  <fonts count="31">
+  <fonts count="32">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -220,8 +223,13 @@
       <color rgb="00334155"/>
       <sz val="9"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="14">
+  <fills count="16">
     <fill>
       <patternFill/>
     </fill>
@@ -293,6 +301,16 @@
         <fgColor rgb="00FEF3C7"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FECACA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FDE68A"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -324,7 +342,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="97">
+  <cellXfs count="109">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -440,6 +458,38 @@
     <xf numFmtId="167" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="0" fillId="13" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1803,6 +1853,189 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="FF64748B"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B1:B28"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <cols>
+    <col width="1" customWidth="1" min="1" max="1"/>
+    <col width="183.33203125" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="21" customHeight="1">
+      <c r="B1" s="52" t="inlineStr">
+        <is>
+          <t>Sold Direct — model notes &amp; sources</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="B2" s="7" t="n"/>
+    </row>
+    <row r="3">
+      <c r="B3" s="56" t="inlineStr">
+        <is>
+          <t>Strategy: prime / upper-market focus (Atlantic Seaboard, City Bowl, Southern Suburbs, Constantia; then prime JHB-north &amp; Umhlanga).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="7" t="n"/>
+    </row>
+    <row r="5">
+      <c r="B5" s="53" t="inlineStr">
+        <is>
+          <t>MONETISATION (legally clean - no bank exclusivity):</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="55" t="inlineStr">
+        <is>
+          <t>• Free 0% requires a qualifying &gt;=80% bond via our MULTI-BANK originator (ooba) + our conveyancer. Buyer keeps full rate choice; we earn the origination referral (~0.5% of bond).</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="55" t="inlineStr">
+        <is>
+          <t>• Otherwise a 1% facilitation fee on the price (cash / sub-80% / not using our partners) - still ~6x cheaper than 5-7% agent commission.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="55" t="inlineStr">
+        <is>
+          <t>• Bank HEADLINE SPONSORSHIP: a bank pays an annual fee to be the featured sponsor / brand on the platform (advertising, not steering) - high-margin, grows with audience.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="55" t="n"/>
+    </row>
+    <row r="10">
+      <c r="B10" s="54" t="inlineStr">
+        <is>
+          <t>THE DATABASE / ECOSYSTEM (see Ancillary Revenue tab):</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="53" t="inlineStr">
+        <is>
+          <t>• Owning the homeowner relationship unlocks a referral menu worth ~R50k of ecosystem revenue per customer (insurance, solar, moving, fibre, security, life cover, etc.).</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="55" t="inlineStr">
+        <is>
+          <t>• Modelled conservatively as OPTIONAL: ~R5k additional captured per deal (~10% blended capture). Toggle into the P&amp;L on Assumptions!C61 (default off).</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="55" t="inlineStr">
+        <is>
+          <t>• This is the moat and the expansion-revenue story - default off keeps the headline P&amp;L conservative; turning it on adds ~R14m to Y5 base revenue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="55" t="n"/>
+    </row>
+    <row r="15">
+      <c r="B15" s="54" t="inlineStr">
+        <is>
+          <t>AI-LEAN OPERATING MODEL:</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="53" t="inlineStr">
+        <is>
+          <t>• 50% of headcount are AI agents (concierge/coordination/ops) at ~R0.15m/yr each vs ~R0.70-0.78m/yr fully-loaded human - roughly halves people-cost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="55" t="n"/>
+    </row>
+    <row r="18">
+      <c r="B18" s="54" t="inlineStr">
+        <is>
+          <t>KEY SOURCED ANCHORS (full citations in docs/dataroom/00-assumptions.md):</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="53" t="inlineStr">
+        <is>
+          <t>• Cape Town: median ~R3.4m, average ~R2.1m; R6m+ = prime freehold band (Lightstone/Property24 2024-26).</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="55" t="inlineStr">
+        <is>
+          <t>• Bond origination commission 1.0-1.9% of loan; originator referral share ~0.5% (ooba/IOL). Estate agency 5-7% + 15% VAT (Private Property).</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="55" t="inlineStr">
+        <is>
+          <t>• Proptech ~8.8x EV/revenue globally; discount to 4-6x for SA early stage (Finro 2025). Purplebricks: IPO GBP240m -&gt; sold for GBP1 (CAC discipline).</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="55" t="n"/>
+    </row>
+    <row r="23">
+      <c r="B23" s="54" t="inlineStr">
+        <is>
+          <t>WATCH-OUTS:</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="53" t="inlineStr">
+        <is>
+          <t>1. High margins (AI-lean + 1% take + sponsorship) - present a 'reinvest for growth' case. 2. AI agents at 50% of roles in Y1 is aggressive - validate with a pilot.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="55" t="inlineStr">
+        <is>
+          <t>3. Sponsorship value scales with real audience/traffic - keep Y1 conservative until reach is proven.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="55" t="n"/>
+    </row>
+    <row r="27">
+      <c r="B27" s="54" t="inlineStr">
+        <is>
+          <t>HOW TO USE: edit amber cells on Assumptions. P&amp;L, Scenarios and Valuation recalculate automatically.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="57" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -4192,6 +4425,993 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="007C3AED"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B1:E15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="69" t="inlineStr">
+        <is>
+          <t>Use of Funds — seed round</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="B2" s="70" t="inlineStr">
+        <is>
+          <t>Amber = editable allocation. % and totals calculated. Seed amount linked from Capital &amp; Valuation!C9.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="97" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="C4" s="97" t="inlineStr">
+        <is>
+          <t>Amount (R)</t>
+        </is>
+      </c>
+      <c r="D4" s="97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">% </t>
+        </is>
+      </c>
+      <c r="E4" s="97" t="inlineStr">
+        <is>
+          <t>What it buys / milestone</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="75" t="inlineStr">
+        <is>
+          <t>Above-the-line / brand marketing</t>
+        </is>
+      </c>
+      <c r="C5" s="98" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="D5" s="85">
+        <f>C5/$C$11</f>
+        <v/>
+      </c>
+      <c r="E5" s="99" t="inlineStr">
+        <is>
+          <t>First brand campaign in prime CT — the deal-ramp engine; prove ATL→deals conversion</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="75" t="inlineStr">
+        <is>
+          <t>Team (AI-augmented, ~8 people)</t>
+        </is>
+      </c>
+      <c r="C6" s="98" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="D6" s="85">
+        <f>C6/$C$11</f>
+        <v/>
+      </c>
+      <c r="E6" s="99" t="inlineStr">
+        <is>
+          <t>Founders + small human core (product, ops/concierge, partnerships); 12–18mo runway</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="75" t="inlineStr">
+        <is>
+          <t>Product &amp; technology</t>
+        </is>
+      </c>
+      <c r="C7" s="98" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="D7" s="85">
+        <f>C7/$C$11</f>
+        <v/>
+      </c>
+      <c r="E7" s="99" t="inlineStr">
+        <is>
+          <t>WhatsApp Cloud API/BSP, AI agents, deal tracker, dashboard, security</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="75" t="inlineStr">
+        <is>
+          <t>Partnerships &amp; go-to-market</t>
+        </is>
+      </c>
+      <c r="C8" s="98" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="D8" s="85">
+        <f>C8/$C$11</f>
+        <v/>
+      </c>
+      <c r="E8" s="99" t="inlineStr">
+        <is>
+          <t>ooba + panel conveyancers live; secure the bank headline sponsor; onboarding</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="75" t="inlineStr">
+        <is>
+          <t>Legal / compliance / licensing</t>
+        </is>
+      </c>
+      <c r="C9" s="98" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="D9" s="85">
+        <f>C9/$C$11</f>
+        <v/>
+      </c>
+      <c r="E9" s="99" t="inlineStr">
+        <is>
+          <t>PPRA practitioner + FFC, POPIA programme, contracts, mandate templates</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="75" t="inlineStr">
+        <is>
+          <t>Working capital / contingency</t>
+        </is>
+      </c>
+      <c r="C10" s="98" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="D10" s="85">
+        <f>C10/$C$11</f>
+        <v/>
+      </c>
+      <c r="E10" s="99" t="inlineStr">
+        <is>
+          <t>Buffer above the ~R6m modelled cash low-point</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="72" t="inlineStr">
+        <is>
+          <t>Total allocated</t>
+        </is>
+      </c>
+      <c r="C11" s="74">
+        <f>SUM(C5:C10)</f>
+        <v/>
+      </c>
+      <c r="D11" s="85">
+        <f>C11/$C$11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="75" t="inlineStr">
+        <is>
+          <t>Seed raise (linked)</t>
+        </is>
+      </c>
+      <c r="C12" s="83">
+        <f>'Capital &amp; Valuation'!C9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="70" t="inlineStr">
+        <is>
+          <t>Check (allocated − seed; should be 0)</t>
+        </is>
+      </c>
+      <c r="C13" s="83">
+        <f>C11-C12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="70" t="inlineStr">
+        <is>
+          <t>Note: survival need is only ~R6m; the rest is growth capital (brand + team) to drive the deal ramp.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="000EA5E9"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B1:H12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="69" t="inlineStr">
+        <is>
+          <t>Competitive Landscape</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="B2" s="70" t="inlineStr">
+        <is>
+          <t>Sold Direct is the only 0%-to-consumer player that monetises the financial ecosystem around the deal via WhatsApp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="100" t="inlineStr">
+        <is>
+          <t>Player</t>
+        </is>
+      </c>
+      <c r="C4" s="100" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="D4" s="100" t="inlineStr">
+        <is>
+          <t>Cost to seller</t>
+        </is>
+      </c>
+      <c r="E4" s="100" t="inlineStr">
+        <is>
+          <t>Channel</t>
+        </is>
+      </c>
+      <c r="F4" s="100" t="inlineStr">
+        <is>
+          <t>Bond / finance</t>
+        </is>
+      </c>
+      <c r="G4" s="100" t="inlineStr">
+        <is>
+          <t>Ecosystem revenue</t>
+        </is>
+      </c>
+      <c r="H4" s="100" t="inlineStr">
+        <is>
+          <t>Segment / status</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="101" t="inlineStr">
+        <is>
+          <t>Sold Direct</t>
+        </is>
+      </c>
+      <c r="C5" s="102" t="inlineStr">
+        <is>
+          <t>0% marketplace + concierge</t>
+        </is>
+      </c>
+      <c r="D5" s="102" t="inlineStr">
+        <is>
+          <t>0% (1% non-partner)</t>
+        </is>
+      </c>
+      <c r="E5" s="102" t="inlineStr">
+        <is>
+          <t>WhatsApp-native</t>
+        </is>
+      </c>
+      <c r="F5" s="102" t="inlineStr">
+        <is>
+          <t>Multi-bank origination referral (core)</t>
+        </is>
+      </c>
+      <c r="G5" s="102" t="inlineStr">
+        <is>
+          <t>Yes — insurance, solar, moving, life cover…</t>
+        </is>
+      </c>
+      <c r="H5" s="102" t="inlineStr">
+        <is>
+          <t>Prime first; launching</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="103" t="inlineStr">
+        <is>
+          <t>Traditional agencies
+(Pam Golding, Seeff, RE/MAX, Rawson)</t>
+        </is>
+      </c>
+      <c r="C6" s="99" t="inlineStr">
+        <is>
+          <t>Full-service agency</t>
+        </is>
+      </c>
+      <c r="D6" s="99" t="inlineStr">
+        <is>
+          <t>5–7% + VAT</t>
+        </is>
+      </c>
+      <c r="E6" s="99" t="inlineStr">
+        <is>
+          <t>Agents + portals</t>
+        </is>
+      </c>
+      <c r="F6" s="99" t="inlineStr">
+        <is>
+          <t>Refer to originators</t>
+        </is>
+      </c>
+      <c r="G6" s="99" t="inlineStr">
+        <is>
+          <t>Limited (referrals)</t>
+        </is>
+      </c>
+      <c r="H6" s="99" t="inlineStr">
+        <is>
+          <t>All; incumbent, high cost</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="103" t="inlineStr">
+        <is>
+          <t>Property24</t>
+        </is>
+      </c>
+      <c r="C7" s="99" t="inlineStr">
+        <is>
+          <t>Listings portal</t>
+        </is>
+      </c>
+      <c r="D7" s="99" t="inlineStr">
+        <is>
+          <t>Portal fees (to agents)</t>
+        </is>
+      </c>
+      <c r="E7" s="99" t="inlineStr">
+        <is>
+          <t>Web / app portal</t>
+        </is>
+      </c>
+      <c r="F7" s="99" t="inlineStr">
+        <is>
+          <t>Bond calculators &amp; leads</t>
+        </is>
+      </c>
+      <c r="G7" s="99" t="inlineStr">
+        <is>
+          <t>Ad / lead revenue</t>
+        </is>
+      </c>
+      <c r="H7" s="99" t="inlineStr">
+        <is>
+          <t>All; dominant portal (Prosus)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="103" t="inlineStr">
+        <is>
+          <t>Private Property</t>
+        </is>
+      </c>
+      <c r="C8" s="99" t="inlineStr">
+        <is>
+          <t>Listings portal</t>
+        </is>
+      </c>
+      <c r="D8" s="99" t="inlineStr">
+        <is>
+          <t>Listing / portal fees</t>
+        </is>
+      </c>
+      <c r="E8" s="99" t="inlineStr">
+        <is>
+          <t>Web portal</t>
+        </is>
+      </c>
+      <c r="F8" s="99" t="inlineStr">
+        <is>
+          <t>Bond referral</t>
+        </is>
+      </c>
+      <c r="G8" s="99" t="inlineStr">
+        <is>
+          <t>Ad / lead revenue</t>
+        </is>
+      </c>
+      <c r="H8" s="99" t="inlineStr">
+        <is>
+          <t>All; #2 portal</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="103" t="inlineStr">
+        <is>
+          <t>PropertyFox</t>
+        </is>
+      </c>
+      <c r="C9" s="99" t="inlineStr">
+        <is>
+          <t>Low-commission hybrid</t>
+        </is>
+      </c>
+      <c r="D9" s="99" t="inlineStr">
+        <is>
+          <t>~1.5% flat</t>
+        </is>
+      </c>
+      <c r="E9" s="99" t="inlineStr">
+        <is>
+          <t>Online + agents</t>
+        </is>
+      </c>
+      <c r="F9" s="99" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G9" s="99" t="inlineStr">
+        <is>
+          <t>Limited</t>
+        </is>
+      </c>
+      <c r="H9" s="99" t="inlineStr">
+        <is>
+          <t>Mid; struggled / sold — cautionary</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="103" t="inlineStr">
+        <is>
+          <t>Leadhome</t>
+        </is>
+      </c>
+      <c r="C10" s="99" t="inlineStr">
+        <is>
+          <t>Fixed-fee online agency</t>
+        </is>
+      </c>
+      <c r="D10" s="99" t="inlineStr">
+        <is>
+          <t>Low fixed fee</t>
+        </is>
+      </c>
+      <c r="E10" s="99" t="inlineStr">
+        <is>
+          <t>Online + agents</t>
+        </is>
+      </c>
+      <c r="F10" s="99" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="99" t="inlineStr">
+        <is>
+          <t>Limited</t>
+        </is>
+      </c>
+      <c r="H10" s="99" t="inlineStr">
+        <is>
+          <t>Mid; wound down — cautionary</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="103" t="inlineStr">
+        <is>
+          <t>ooba / BetterBond</t>
+        </is>
+      </c>
+      <c r="C11" s="99" t="inlineStr">
+        <is>
+          <t>Bond originators</t>
+        </is>
+      </c>
+      <c r="D11" s="99" t="inlineStr">
+        <is>
+          <t>Free to consumer</t>
+        </is>
+      </c>
+      <c r="E11" s="99" t="inlineStr">
+        <is>
+          <t>Web / agents</t>
+        </is>
+      </c>
+      <c r="F11" s="99" t="inlineStr">
+        <is>
+          <t>Core business</t>
+        </is>
+      </c>
+      <c r="G11" s="99" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H11" s="99" t="inlineStr">
+        <is>
+          <t>Bonded buyers — PARTNERS, not rivals</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="103" t="inlineStr">
+        <is>
+          <t>Purplebricks (UK)</t>
+        </is>
+      </c>
+      <c r="C12" s="99" t="inlineStr">
+        <is>
+          <t>Fixed-fee online agency</t>
+        </is>
+      </c>
+      <c r="D12" s="99" t="inlineStr">
+        <is>
+          <t>Fixed fee</t>
+        </is>
+      </c>
+      <c r="E12" s="99" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="F12" s="99" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="99" t="inlineStr">
+        <is>
+          <t>Limited</t>
+        </is>
+      </c>
+      <c r="H12" s="99" t="inlineStr">
+        <is>
+          <t>Defunct: £240m IPO → £1 — CAC warning</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00EF4444"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B1:G18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="5" customWidth="1" min="4" max="4"/>
+    <col width="5" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="6" max="6"/>
+    <col width="52" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="69" t="inlineStr">
+        <is>
+          <t>Risk Register</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="B2" s="70" t="inlineStr">
+        <is>
+          <t>Likelihood (L) &amp; Impact (I): 1=Low, 2=Med, 3=High. Severity = L×I (green ≤2, amber 3–4, red ≥6).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="100" t="inlineStr">
+        <is>
+          <t>Risk</t>
+        </is>
+      </c>
+      <c r="C4" s="100" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D4" s="104" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E4" s="104" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F4" s="104" t="inlineStr">
+        <is>
+          <t>Sev</t>
+        </is>
+      </c>
+      <c r="G4" s="100" t="inlineStr">
+        <is>
+          <t>Mitigation</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="99" t="inlineStr">
+        <is>
+          <t>ATL marketing doesn't convert to deals (CAC blows out)</t>
+        </is>
+      </c>
+      <c r="C5" s="88" t="inlineStr">
+        <is>
+          <t>Growth</t>
+        </is>
+      </c>
+      <c r="D5" s="105" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" s="105" t="n">
+        <v>3</v>
+      </c>
+      <c r="F5" s="106">
+        <f>D5*E5</f>
+        <v/>
+      </c>
+      <c r="G5" s="99" t="inlineStr">
+        <is>
+          <t>Pilot ATL in CT before scaling; track CAC payback; throttle spend to cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="99" t="inlineStr">
+        <is>
+          <t>Prime pool smaller / ~20% share too ambitious</t>
+        </is>
+      </c>
+      <c r="C6" s="88" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="D6" s="105" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" s="105" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" s="106">
+        <f>D6*E6</f>
+        <v/>
+      </c>
+      <c r="G6" s="99" t="inlineStr">
+        <is>
+          <t>Confirm prime-pool data; conservative case ≈14% share; widen to upper-mid segment</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="99" t="inlineStr">
+        <is>
+          <t>Regulatory — PPRA/FFC, bond-steering, NCA if originating</t>
+        </is>
+      </c>
+      <c r="C7" s="88" t="inlineStr">
+        <is>
+          <t>Regulatory</t>
+        </is>
+      </c>
+      <c r="D7" s="105" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" s="105" t="n">
+        <v>3</v>
+      </c>
+      <c r="F7" s="106">
+        <f>D7*E7</f>
+        <v/>
+      </c>
+      <c r="G7" s="99" t="inlineStr">
+        <is>
+          <t>Registered practitioner + FFC; multi-bank (no steering); legal sign-off before launch</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="99" t="inlineStr">
+        <is>
+          <t>POPIA / data breach (IDs, payslips, bank data)</t>
+        </is>
+      </c>
+      <c r="C8" s="88" t="inlineStr">
+        <is>
+          <t>Compliance</t>
+        </is>
+      </c>
+      <c r="D8" s="105" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" s="105" t="n">
+        <v>3</v>
+      </c>
+      <c r="F8" s="106">
+        <f>D8*E8</f>
+        <v/>
+      </c>
+      <c r="G8" s="99" t="inlineStr">
+        <is>
+          <t>Encrypt at rest, minimise PII, consent logging, DPAs, security review (already in build)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="99" t="inlineStr">
+        <is>
+          <t>Trust/adoption — sellers wary of a new brand for R6m+ sale</t>
+        </is>
+      </c>
+      <c r="C9" s="88" t="inlineStr">
+        <is>
+          <t>Adoption</t>
+        </is>
+      </c>
+      <c r="D9" s="105" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" s="105" t="n">
+        <v>3</v>
+      </c>
+      <c r="F9" s="106">
+        <f>D9*E9</f>
+        <v/>
+      </c>
+      <c r="G9" s="99" t="inlineStr">
+        <is>
+          <t>Concierge model, panel conveyancers (funds in trust), testimonials, bank-sponsor halo</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="99" t="inlineStr">
+        <is>
+          <t>Partner concentration (ooba, sponsor, conveyancers)</t>
+        </is>
+      </c>
+      <c r="C10" s="88" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="D10" s="105" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" s="105" t="n">
+        <v>2</v>
+      </c>
+      <c r="F10" s="107">
+        <f>D10*E10</f>
+        <v/>
+      </c>
+      <c r="G10" s="99" t="inlineStr">
+        <is>
+          <t>Multi-bank via ooba; multiple conveyancers; non-exclusive sponsor</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="99" t="inlineStr">
+        <is>
+          <t>Incumbent retaliation (portals / agencies cut fees or copy)</t>
+        </is>
+      </c>
+      <c r="C11" s="88" t="inlineStr">
+        <is>
+          <t>Competitive</t>
+        </is>
+      </c>
+      <c r="D11" s="105" t="n">
+        <v>2</v>
+      </c>
+      <c r="E11" s="105" t="n">
+        <v>2</v>
+      </c>
+      <c r="F11" s="107">
+        <f>D11*E11</f>
+        <v/>
+      </c>
+      <c r="G11" s="99" t="inlineStr">
+        <is>
+          <t>Speed + brand + WhatsApp UX + ecosystem lock-in + data advantage</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="99" t="inlineStr">
+        <is>
+          <t>AI agents underperform for high-touch prime clients</t>
+        </is>
+      </c>
+      <c r="C12" s="88" t="inlineStr">
+        <is>
+          <t>Operational</t>
+        </is>
+      </c>
+      <c r="D12" s="105" t="n">
+        <v>2</v>
+      </c>
+      <c r="E12" s="105" t="n">
+        <v>2</v>
+      </c>
+      <c r="F12" s="107">
+        <f>D12*E12</f>
+        <v/>
+      </c>
+      <c r="G12" s="99" t="inlineStr">
+        <is>
+          <t>Human-in-the-loop on prime; AI for coordination not advice; QA + escalation</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="99" t="inlineStr">
+        <is>
+          <t>Property downturn / rates → fewer transactions</t>
+        </is>
+      </c>
+      <c r="C13" s="88" t="inlineStr">
+        <is>
+          <t>Macro</t>
+        </is>
+      </c>
+      <c r="D13" s="105" t="n">
+        <v>2</v>
+      </c>
+      <c r="E13" s="105" t="n">
+        <v>2</v>
+      </c>
+      <c r="F13" s="107">
+        <f>D13*E13</f>
+        <v/>
+      </c>
+      <c r="G13" s="99" t="inlineStr">
+        <is>
+          <t>Counter-cyclical 0% appeal; lean cost base; flex marketing spend</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="99" t="inlineStr">
+        <is>
+          <t>WhatsApp / Meta platform &amp; pricing dependency</t>
+        </is>
+      </c>
+      <c r="C14" s="88" t="inlineStr">
+        <is>
+          <t>Platform</t>
+        </is>
+      </c>
+      <c r="D14" s="105" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" s="105" t="n">
+        <v>2</v>
+      </c>
+      <c r="F14" s="108">
+        <f>D14*E14</f>
+        <v/>
+      </c>
+      <c r="G14" s="99" t="inlineStr">
+        <is>
+          <t>BSP-agnostic adapter (built); web fallback; monitor Meta pricing</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="99" t="inlineStr">
+        <is>
+          <t>Key-person / small-team dependency</t>
+        </is>
+      </c>
+      <c r="C15" s="88" t="inlineStr">
+        <is>
+          <t>Team</t>
+        </is>
+      </c>
+      <c r="D15" s="105" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" s="105" t="n">
+        <v>2</v>
+      </c>
+      <c r="F15" s="107">
+        <f>D15*E15</f>
+        <v/>
+      </c>
+      <c r="G15" s="99" t="inlineStr">
+        <is>
+          <t>Document + cross-train; AI leverage; hire on the raise</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="99" t="inlineStr">
+        <is>
+          <t>High-margin assumptions hurt the fundraise</t>
+        </is>
+      </c>
+      <c r="C16" s="88" t="inlineStr">
+        <is>
+          <t>Funding</t>
+        </is>
+      </c>
+      <c r="D16" s="105" t="n">
+        <v>2</v>
+      </c>
+      <c r="E16" s="105" t="n">
+        <v>2</v>
+      </c>
+      <c r="F16" s="107">
+        <f>D16*E16</f>
+        <v/>
+      </c>
+      <c r="G16" s="99" t="inlineStr">
+        <is>
+          <t>Lead with conservative case + traction; reinvest-for-growth framing</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="70" t="inlineStr">
+        <is>
+          <t>Top risks (Sev 6): marketing-conversion, prime-share, regulatory, POPIA, trust/adoption — each has an owner action above.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
     <tabColor rgb="FF0EA5E9"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -4657,187 +5877,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="FF64748B"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="B1:B28"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
-  <cols>
-    <col width="1" customWidth="1" min="1" max="1"/>
-    <col width="183.33203125" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="21" customHeight="1">
-      <c r="B1" s="52" t="inlineStr">
-        <is>
-          <t>Sold Direct — model notes &amp; sources</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="B2" s="7" t="n"/>
-    </row>
-    <row r="3">
-      <c r="B3" s="56" t="inlineStr">
-        <is>
-          <t>Strategy: prime / upper-market focus (Atlantic Seaboard, City Bowl, Southern Suburbs, Constantia; then prime JHB-north &amp; Umhlanga).</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="B4" s="7" t="n"/>
-    </row>
-    <row r="5">
-      <c r="B5" s="53" t="inlineStr">
-        <is>
-          <t>MONETISATION (legally clean - no bank exclusivity):</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="B6" s="55" t="inlineStr">
-        <is>
-          <t>• Free 0% requires a qualifying &gt;=80% bond via our MULTI-BANK originator (ooba) + our conveyancer. Buyer keeps full rate choice; we earn the origination referral (~0.5% of bond).</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" s="55" t="inlineStr">
-        <is>
-          <t>• Otherwise a 1% facilitation fee on the price (cash / sub-80% / not using our partners) - still ~6x cheaper than 5-7% agent commission.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" s="55" t="inlineStr">
-        <is>
-          <t>• Bank HEADLINE SPONSORSHIP: a bank pays an annual fee to be the featured sponsor / brand on the platform (advertising, not steering) - high-margin, grows with audience.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" s="55" t="n"/>
-    </row>
-    <row r="10">
-      <c r="B10" s="54" t="inlineStr">
-        <is>
-          <t>THE DATABASE / ECOSYSTEM (see Ancillary Revenue tab):</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" s="53" t="inlineStr">
-        <is>
-          <t>• Owning the homeowner relationship unlocks a referral menu worth ~R50k of ecosystem revenue per customer (insurance, solar, moving, fibre, security, life cover, etc.).</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" s="55" t="inlineStr">
-        <is>
-          <t>• Modelled conservatively as OPTIONAL: ~R5k additional captured per deal (~10% blended capture). Toggle into the P&amp;L on Assumptions!C61 (default off).</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" s="55" t="inlineStr">
-        <is>
-          <t>• This is the moat and the expansion-revenue story - default off keeps the headline P&amp;L conservative; turning it on adds ~R14m to Y5 base revenue.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" s="55" t="n"/>
-    </row>
-    <row r="15">
-      <c r="B15" s="54" t="inlineStr">
-        <is>
-          <t>AI-LEAN OPERATING MODEL:</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" s="53" t="inlineStr">
-        <is>
-          <t>• 50% of headcount are AI agents (concierge/coordination/ops) at ~R0.15m/yr each vs ~R0.70-0.78m/yr fully-loaded human - roughly halves people-cost.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" s="55" t="n"/>
-    </row>
-    <row r="18">
-      <c r="B18" s="54" t="inlineStr">
-        <is>
-          <t>KEY SOURCED ANCHORS (full citations in docs/dataroom/00-assumptions.md):</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" s="53" t="inlineStr">
-        <is>
-          <t>• Cape Town: median ~R3.4m, average ~R2.1m; R6m+ = prime freehold band (Lightstone/Property24 2024-26).</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="55" t="inlineStr">
-        <is>
-          <t>• Bond origination commission 1.0-1.9% of loan; originator referral share ~0.5% (ooba/IOL). Estate agency 5-7% + 15% VAT (Private Property).</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="55" t="inlineStr">
-        <is>
-          <t>• Proptech ~8.8x EV/revenue globally; discount to 4-6x for SA early stage (Finro 2025). Purplebricks: IPO GBP240m -&gt; sold for GBP1 (CAC discipline).</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="B22" s="55" t="n"/>
-    </row>
-    <row r="23">
-      <c r="B23" s="54" t="inlineStr">
-        <is>
-          <t>WATCH-OUTS:</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="53" t="inlineStr">
-        <is>
-          <t>1. High margins (AI-lean + 1% take + sponsorship) - present a 'reinvest for growth' case. 2. AI agents at 50% of roles in Y1 is aggressive - validate with a pilot.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="B25" s="55" t="inlineStr">
-        <is>
-          <t>3. Sponsorship value scales with real audience/traffic - keep Y1 conservative until reach is proven.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="55" t="n"/>
-    </row>
-    <row r="27">
-      <c r="B27" s="54" t="inlineStr">
-        <is>
-          <t>HOW TO USE: edit amber cells on Assumptions. P&amp;L, Scenarios and Valuation recalculate automatically.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="B28" s="57" t="n"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/docs/dataroom/sold-direct-model.xlsx
+++ b/docs/dataroom/sold-direct-model.xlsx
@@ -12,10 +12,12 @@
     <sheet name="Market Sizing" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Capital &amp; Valuation" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Use of Funds" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Competitive Landscape" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Risk Register" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Ancillary Revenue" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Notes &amp; Sources" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Cap Table" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Funder Growth" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Competitive Landscape" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Risk Register" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Ancillary Revenue" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Notes &amp; Sources" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1" iterateDelta="0.0001"/>
@@ -342,7 +344,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="109">
+  <cellXfs count="112">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -490,6 +492,9 @@
     <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="167" fontId="0" fillId="13" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="13" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -564,6 +569,179 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Stakeholder value by round (R)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Funder Growth'!D4</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Funder Growth'!$B$5:$B$10</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Funder Growth'!$D$5:$D$10</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Funder Growth'!E4</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Funder Growth'!$B$5:$B$10</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Funder Growth'!$E$5:$E$10</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Funder Growth'!F4</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Funder Growth'!$B$5:$B$10</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Funder Growth'!$F$5:$F$10</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>R (millions)</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <numFmt formatCode="#,##0,,&quot;m&quot;" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>13</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7200000" cy="3060000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1012,16 +1190,16 @@
         <v>6500000</v>
       </c>
       <c r="D15" s="60" t="n">
-        <v>6700000</v>
+        <v>5750000</v>
       </c>
       <c r="E15" s="60" t="n">
-        <v>6800000</v>
+        <v>5000000</v>
       </c>
       <c r="F15" s="60" t="n">
-        <v>6900000</v>
+        <v>4500000</v>
       </c>
       <c r="G15" s="60" t="n">
-        <v>7000000</v>
+        <v>4000000</v>
       </c>
     </row>
     <row r="16">
@@ -1854,6 +2032,876 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00EF4444"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B1:G18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="5" customWidth="1" min="4" max="4"/>
+    <col width="5" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="6" max="6"/>
+    <col width="52" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="69" t="inlineStr">
+        <is>
+          <t>Risk Register</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="B2" s="70" t="inlineStr">
+        <is>
+          <t>Likelihood (L) &amp; Impact (I): 1=Low, 2=Med, 3=High. Severity = L×I (green ≤2, amber 3–4, red ≥6).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="100" t="inlineStr">
+        <is>
+          <t>Risk</t>
+        </is>
+      </c>
+      <c r="C4" s="100" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D4" s="104" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E4" s="104" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F4" s="104" t="inlineStr">
+        <is>
+          <t>Sev</t>
+        </is>
+      </c>
+      <c r="G4" s="100" t="inlineStr">
+        <is>
+          <t>Mitigation</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="99" t="inlineStr">
+        <is>
+          <t>ATL marketing doesn't convert to deals (CAC blows out)</t>
+        </is>
+      </c>
+      <c r="C5" s="88" t="inlineStr">
+        <is>
+          <t>Growth</t>
+        </is>
+      </c>
+      <c r="D5" s="105" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" s="105" t="n">
+        <v>3</v>
+      </c>
+      <c r="F5" s="106">
+        <f>D5*E5</f>
+        <v/>
+      </c>
+      <c r="G5" s="99" t="inlineStr">
+        <is>
+          <t>Pilot ATL in CT before scaling; track CAC payback; throttle spend to cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="99" t="inlineStr">
+        <is>
+          <t>Prime pool smaller / ~20% share too ambitious</t>
+        </is>
+      </c>
+      <c r="C6" s="88" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="D6" s="105" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" s="105" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" s="106">
+        <f>D6*E6</f>
+        <v/>
+      </c>
+      <c r="G6" s="99" t="inlineStr">
+        <is>
+          <t>Confirm prime-pool data; conservative case ≈14% share; widen to upper-mid segment</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="99" t="inlineStr">
+        <is>
+          <t>Regulatory — PPRA/FFC, bond-steering, NCA if originating</t>
+        </is>
+      </c>
+      <c r="C7" s="88" t="inlineStr">
+        <is>
+          <t>Regulatory</t>
+        </is>
+      </c>
+      <c r="D7" s="105" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" s="105" t="n">
+        <v>3</v>
+      </c>
+      <c r="F7" s="106">
+        <f>D7*E7</f>
+        <v/>
+      </c>
+      <c r="G7" s="99" t="inlineStr">
+        <is>
+          <t>Registered practitioner + FFC; multi-bank (no steering); legal sign-off before launch</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="99" t="inlineStr">
+        <is>
+          <t>POPIA / data breach (IDs, payslips, bank data)</t>
+        </is>
+      </c>
+      <c r="C8" s="88" t="inlineStr">
+        <is>
+          <t>Compliance</t>
+        </is>
+      </c>
+      <c r="D8" s="105" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" s="105" t="n">
+        <v>3</v>
+      </c>
+      <c r="F8" s="106">
+        <f>D8*E8</f>
+        <v/>
+      </c>
+      <c r="G8" s="99" t="inlineStr">
+        <is>
+          <t>Encrypt at rest, minimise PII, consent logging, DPAs, security review (already in build)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="99" t="inlineStr">
+        <is>
+          <t>Trust/adoption — sellers wary of a new brand for R6m+ sale</t>
+        </is>
+      </c>
+      <c r="C9" s="88" t="inlineStr">
+        <is>
+          <t>Adoption</t>
+        </is>
+      </c>
+      <c r="D9" s="105" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" s="105" t="n">
+        <v>3</v>
+      </c>
+      <c r="F9" s="106">
+        <f>D9*E9</f>
+        <v/>
+      </c>
+      <c r="G9" s="99" t="inlineStr">
+        <is>
+          <t>Concierge model, panel conveyancers (funds in trust), testimonials, bank-sponsor halo</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="99" t="inlineStr">
+        <is>
+          <t>Partner concentration (ooba, sponsor, conveyancers)</t>
+        </is>
+      </c>
+      <c r="C10" s="88" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="D10" s="105" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" s="105" t="n">
+        <v>2</v>
+      </c>
+      <c r="F10" s="107">
+        <f>D10*E10</f>
+        <v/>
+      </c>
+      <c r="G10" s="99" t="inlineStr">
+        <is>
+          <t>Multi-bank via ooba; multiple conveyancers; non-exclusive sponsor</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="99" t="inlineStr">
+        <is>
+          <t>Incumbent retaliation (portals / agencies cut fees or copy)</t>
+        </is>
+      </c>
+      <c r="C11" s="88" t="inlineStr">
+        <is>
+          <t>Competitive</t>
+        </is>
+      </c>
+      <c r="D11" s="105" t="n">
+        <v>2</v>
+      </c>
+      <c r="E11" s="105" t="n">
+        <v>2</v>
+      </c>
+      <c r="F11" s="107">
+        <f>D11*E11</f>
+        <v/>
+      </c>
+      <c r="G11" s="99" t="inlineStr">
+        <is>
+          <t>Speed + brand + WhatsApp UX + ecosystem lock-in + data advantage</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="99" t="inlineStr">
+        <is>
+          <t>AI agents underperform for high-touch prime clients</t>
+        </is>
+      </c>
+      <c r="C12" s="88" t="inlineStr">
+        <is>
+          <t>Operational</t>
+        </is>
+      </c>
+      <c r="D12" s="105" t="n">
+        <v>2</v>
+      </c>
+      <c r="E12" s="105" t="n">
+        <v>2</v>
+      </c>
+      <c r="F12" s="107">
+        <f>D12*E12</f>
+        <v/>
+      </c>
+      <c r="G12" s="99" t="inlineStr">
+        <is>
+          <t>Human-in-the-loop on prime; AI for coordination not advice; QA + escalation</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="99" t="inlineStr">
+        <is>
+          <t>Property downturn / rates → fewer transactions</t>
+        </is>
+      </c>
+      <c r="C13" s="88" t="inlineStr">
+        <is>
+          <t>Macro</t>
+        </is>
+      </c>
+      <c r="D13" s="105" t="n">
+        <v>2</v>
+      </c>
+      <c r="E13" s="105" t="n">
+        <v>2</v>
+      </c>
+      <c r="F13" s="107">
+        <f>D13*E13</f>
+        <v/>
+      </c>
+      <c r="G13" s="99" t="inlineStr">
+        <is>
+          <t>Counter-cyclical 0% appeal; lean cost base; flex marketing spend</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="99" t="inlineStr">
+        <is>
+          <t>WhatsApp / Meta platform &amp; pricing dependency</t>
+        </is>
+      </c>
+      <c r="C14" s="88" t="inlineStr">
+        <is>
+          <t>Platform</t>
+        </is>
+      </c>
+      <c r="D14" s="105" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" s="105" t="n">
+        <v>2</v>
+      </c>
+      <c r="F14" s="108">
+        <f>D14*E14</f>
+        <v/>
+      </c>
+      <c r="G14" s="99" t="inlineStr">
+        <is>
+          <t>BSP-agnostic adapter (built); web fallback; monitor Meta pricing</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="99" t="inlineStr">
+        <is>
+          <t>Key-person / small-team dependency</t>
+        </is>
+      </c>
+      <c r="C15" s="88" t="inlineStr">
+        <is>
+          <t>Team</t>
+        </is>
+      </c>
+      <c r="D15" s="105" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" s="105" t="n">
+        <v>2</v>
+      </c>
+      <c r="F15" s="107">
+        <f>D15*E15</f>
+        <v/>
+      </c>
+      <c r="G15" s="99" t="inlineStr">
+        <is>
+          <t>Document + cross-train; AI leverage; hire on the raise</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="99" t="inlineStr">
+        <is>
+          <t>High-margin assumptions hurt the fundraise</t>
+        </is>
+      </c>
+      <c r="C16" s="88" t="inlineStr">
+        <is>
+          <t>Funding</t>
+        </is>
+      </c>
+      <c r="D16" s="105" t="n">
+        <v>2</v>
+      </c>
+      <c r="E16" s="105" t="n">
+        <v>2</v>
+      </c>
+      <c r="F16" s="107">
+        <f>D16*E16</f>
+        <v/>
+      </c>
+      <c r="G16" s="99" t="inlineStr">
+        <is>
+          <t>Lead with conservative case + traction; reinvest-for-growth framing</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="70" t="inlineStr">
+        <is>
+          <t>Top risks (Sev 6): marketing-conversion, prime-share, regulatory, POPIA, trust/adoption — each has an owner action above.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="FF0EA5E9"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B1:G25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <cols>
+    <col width="1" customWidth="1" min="1" max="1"/>
+    <col width="53.33203125" customWidth="1" min="2" max="2"/>
+    <col width="16.6640625" customWidth="1" min="3" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="21" customHeight="1">
+      <c r="B1" s="8" t="inlineStr">
+        <is>
+          <t>Ancillary / Ecosystem Revenue — the value of the database</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="B2" s="46" t="inlineStr">
+        <is>
+          <t>Referral &amp; commission streams unlocked by owning the homeowner relationship + data. Optional: toggle into the P&amp;L on Assumptions!C61.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="36" t="inlineStr">
+        <is>
+          <t>Revenue stream</t>
+        </is>
+      </c>
+      <c r="C4" s="36" t="inlineStr">
+        <is>
+          <t>Low (R)</t>
+        </is>
+      </c>
+      <c r="D4" s="36" t="inlineStr">
+        <is>
+          <t>High (R)</t>
+        </is>
+      </c>
+      <c r="E4" s="36" t="inlineStr">
+        <is>
+          <t>Midpoint (R)</t>
+        </is>
+      </c>
+      <c r="F4" s="36" t="inlineStr">
+        <is>
+          <t>Attach %</t>
+        </is>
+      </c>
+      <c r="G4" s="36" t="inlineStr">
+        <is>
+          <t>Captured/deal (R)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="24" t="inlineStr">
+        <is>
+          <t>Homeowners insurance commission</t>
+        </is>
+      </c>
+      <c r="C5" s="95" t="n">
+        <v>1500</v>
+      </c>
+      <c r="D5" s="95" t="n">
+        <v>4000</v>
+      </c>
+      <c r="E5" s="96">
+        <f>AVERAGE(C5:D5)</f>
+        <v/>
+      </c>
+      <c r="F5" s="49" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G5" s="96">
+        <f>E5*F5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="24" t="inlineStr">
+        <is>
+          <t>Household contents insurance</t>
+        </is>
+      </c>
+      <c r="C6" s="95" t="n">
+        <v>500</v>
+      </c>
+      <c r="D6" s="95" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E6" s="96">
+        <f>AVERAGE(C6:D6)</f>
+        <v/>
+      </c>
+      <c r="F6" s="49" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G6" s="96">
+        <f>E6*F6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="24" t="inlineStr">
+        <is>
+          <t>Conveyancing referral/marketing fee (already in core)</t>
+        </is>
+      </c>
+      <c r="C7" s="95" t="n">
+        <v>3000</v>
+      </c>
+      <c r="D7" s="95" t="n">
+        <v>8000</v>
+      </c>
+      <c r="E7" s="96">
+        <f>AVERAGE(C7:D7)</f>
+        <v/>
+      </c>
+      <c r="F7" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="96">
+        <f>E7*F7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="24" t="inlineStr">
+        <is>
+          <t>Moving company referral</t>
+        </is>
+      </c>
+      <c r="C8" s="95" t="n">
+        <v>500</v>
+      </c>
+      <c r="D8" s="95" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E8" s="96">
+        <f>AVERAGE(C8:D8)</f>
+        <v/>
+      </c>
+      <c r="F8" s="49" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G8" s="96">
+        <f>E8*F8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="24" t="inlineStr">
+        <is>
+          <t>Fibre / internet installation</t>
+        </is>
+      </c>
+      <c r="C9" s="95" t="n">
+        <v>500</v>
+      </c>
+      <c r="D9" s="95" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E9" s="96">
+        <f>AVERAGE(C9:D9)</f>
+        <v/>
+      </c>
+      <c r="F9" s="49" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G9" s="96">
+        <f>E9*F9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="24" t="inlineStr">
+        <is>
+          <t>Security system installation</t>
+        </is>
+      </c>
+      <c r="C10" s="95" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D10" s="95" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E10" s="96">
+        <f>AVERAGE(C10:D10)</f>
+        <v/>
+      </c>
+      <c r="F10" s="49" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="G10" s="96">
+        <f>E10*F10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="24" t="inlineStr">
+        <is>
+          <t>Utility connection service</t>
+        </is>
+      </c>
+      <c r="C11" s="95" t="n">
+        <v>250</v>
+      </c>
+      <c r="D11" s="95" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E11" s="96">
+        <f>AVERAGE(C11:D11)</f>
+        <v/>
+      </c>
+      <c r="F11" s="49" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G11" s="96">
+        <f>E11*F11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="24" t="inlineStr">
+        <is>
+          <t>Home warranty / product upsell</t>
+        </is>
+      </c>
+      <c r="C12" s="95" t="n">
+        <v>500</v>
+      </c>
+      <c r="D12" s="95" t="n">
+        <v>2500</v>
+      </c>
+      <c r="E12" s="96">
+        <f>AVERAGE(C12:D12)</f>
+        <v/>
+      </c>
+      <c r="F12" s="49" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G12" s="96">
+        <f>E12*F12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="24" t="inlineStr">
+        <is>
+          <t>Compliance certificates (already in core add-ons)</t>
+        </is>
+      </c>
+      <c r="C13" s="95" t="n">
+        <v>500</v>
+      </c>
+      <c r="D13" s="95" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E13" s="96">
+        <f>AVERAGE(C13:D13)</f>
+        <v/>
+      </c>
+      <c r="F13" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="96">
+        <f>E13*F13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="24" t="inlineStr">
+        <is>
+          <t>Solar installation referral</t>
+        </is>
+      </c>
+      <c r="C14" s="95" t="n">
+        <v>5000</v>
+      </c>
+      <c r="D14" s="95" t="n">
+        <v>20000</v>
+      </c>
+      <c r="E14" s="96">
+        <f>AVERAGE(C14:D14)</f>
+        <v/>
+      </c>
+      <c r="F14" s="49" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G14" s="96">
+        <f>E14*F14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="24" t="inlineStr">
+        <is>
+          <t>Home improvement / renovation referrals</t>
+        </is>
+      </c>
+      <c r="C15" s="95" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D15" s="95" t="n">
+        <v>15000</v>
+      </c>
+      <c r="E15" s="96">
+        <f>AVERAGE(C15:D15)</f>
+        <v/>
+      </c>
+      <c r="F15" s="49" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="G15" s="96">
+        <f>E15*F15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="24" t="inlineStr">
+        <is>
+          <t>Storage solutions referral</t>
+        </is>
+      </c>
+      <c r="C16" s="95" t="n">
+        <v>500</v>
+      </c>
+      <c r="D16" s="95" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E16" s="96">
+        <f>AVERAGE(C16:D16)</f>
+        <v/>
+      </c>
+      <c r="F16" s="49" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G16" s="96">
+        <f>E16*F16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="24" t="inlineStr">
+        <is>
+          <t>Short-term insurance cross-sell (car/business)</t>
+        </is>
+      </c>
+      <c r="C17" s="95" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D17" s="95" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E17" s="96">
+        <f>AVERAGE(C17:D17)</f>
+        <v/>
+      </c>
+      <c r="F17" s="49" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G17" s="96">
+        <f>E17*F17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="24" t="inlineStr">
+        <is>
+          <t>Life cover linked to the bond</t>
+        </is>
+      </c>
+      <c r="C18" s="95" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D18" s="95" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E18" s="96">
+        <f>AVERAGE(C18:D18)</f>
+        <v/>
+      </c>
+      <c r="F18" s="49" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="G18" s="96">
+        <f>E18*F18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="24" t="inlineStr">
+        <is>
+          <t>Estate planning / will services</t>
+        </is>
+      </c>
+      <c r="C19" s="95" t="n">
+        <v>500</v>
+      </c>
+      <c r="D19" s="95" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E19" s="96">
+        <f>AVERAGE(C19:D19)</f>
+        <v/>
+      </c>
+      <c r="F19" s="49" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G19" s="96">
+        <f>E19*F19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="50" t="inlineStr">
+        <is>
+          <t>FULL ecosystem potential / customer (sum of midpoints)</t>
+        </is>
+      </c>
+      <c r="C21" s="51" t="n"/>
+      <c r="D21" s="51" t="n"/>
+      <c r="E21" s="67">
+        <f>SUM(E5:E19)</f>
+        <v/>
+      </c>
+      <c r="F21" s="51" t="n"/>
+      <c r="G21" s="51" t="n"/>
+    </row>
+    <row r="22">
+      <c r="B22" s="50" t="inlineStr">
+        <is>
+          <t>Realistic ADDITIONAL captured / deal (sum of captured)</t>
+        </is>
+      </c>
+      <c r="C22" s="51" t="n"/>
+      <c r="D22" s="51" t="n"/>
+      <c r="E22" s="51" t="n"/>
+      <c r="F22" s="51" t="n"/>
+      <c r="G22" s="67">
+        <f>SUM(G5:G19)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="46" t="inlineStr">
+        <is>
+          <t>Conveyancing &amp; compliance certs are already counted in the core model (attach set to 0 here to avoid double-counting).</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="46" t="inlineStr">
+        <is>
+          <t>Strategic point: each registered customer is worth up to ~R50k of ecosystem referral revenue. Even ~10% capture ≈ R5k/deal — the database is the moat.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FF64748B"/>
@@ -3425,7 +4473,7 @@
     <row r="7">
       <c r="B7" s="72" t="inlineStr">
         <is>
-          <t>SAM — prime (&gt;R5m), national</t>
+          <t>SAM — upper-market (&gt;~R4m), national</t>
         </is>
       </c>
       <c r="C7" s="73">
@@ -3590,7 +4638,7 @@
     <row r="22">
       <c r="B22" s="71" t="inlineStr">
         <is>
-          <t>3. SAM - serviceable: PRIME (&gt;R5m), national</t>
+          <t>3. SAM - serviceable: UPPER-MARKET (&gt;~R4m), national</t>
         </is>
       </c>
       <c r="C22" s="71" t="n"/>
@@ -3602,15 +4650,15 @@
     <row r="23">
       <c r="B23" s="75" t="inlineStr">
         <is>
-          <t>Prime (&gt;R5m) transfers / yr</t>
+          <t>Upper-market (&gt;~R4m) transfers / yr</t>
         </is>
       </c>
       <c r="C23" s="76" t="n">
-        <v>14000</v>
+        <v>35000</v>
       </c>
       <c r="D23" s="70" t="inlineStr">
         <is>
-          <t>ESTIMATE - CT ~4k + JHB-north/Umhlanga; confirm</t>
+          <t>ESTIMATE — broadens as avg price tapers; confirm</t>
         </is>
       </c>
     </row>
@@ -3748,7 +4796,7 @@
     <row r="33">
       <c r="B33" s="72" t="inlineStr">
         <is>
-          <t>SOM = % of PRIME transactions</t>
+          <t>SOM = % of upper-market transactions</t>
         </is>
       </c>
       <c r="C33" s="84">
@@ -3817,7 +4865,7 @@
     <row r="38">
       <c r="B38" s="72" t="inlineStr">
         <is>
-          <t>Base case implies this share of national PRIME by Y5</t>
+          <t>Base implies this share of the upper-market by Y5</t>
         </is>
       </c>
       <c r="C38" s="86">
@@ -3835,47 +4883,47 @@
     <row r="40">
       <c r="B40" s="75" t="inlineStr">
         <is>
-          <t>If prime pool = 10,000 -&gt; base Y5 share</t>
+          <t>If pool = 25,000 -&gt; base Y5 share</t>
         </is>
       </c>
       <c r="C40" s="87">
-        <f>D31/10000</f>
+        <f>D31/25000</f>
         <v/>
       </c>
     </row>
     <row r="41">
       <c r="B41" s="75" t="inlineStr">
         <is>
-          <t>If prime pool = 14,000 (base) -&gt; base Y5 share</t>
+          <t>If pool = 35,000 (base) -&gt; base Y5 share</t>
         </is>
       </c>
       <c r="C41" s="87">
-        <f>D31/14000</f>
+        <f>D31/35000</f>
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="B42" s="75" t="inlineStr">
         <is>
-          <t>If prime pool = 20,000 -&gt; base Y5 share</t>
+          <t>If pool = 50,000 -&gt; base Y5 share</t>
         </is>
       </c>
       <c r="C42" s="87">
-        <f>D31/20000</f>
+        <f>D31/50000</f>
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="B44" s="88" t="inlineStr">
         <is>
-          <t>POSITIONING: ~20% of national prime is ambitious - works only as the category-defining prime channel</t>
+          <t>POSITIONING: tapering price broadens the addressable pool, cutting the implied share from ~21% (prime-only) to ~8%.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="B45" s="70" t="inlineStr">
         <is>
-          <t>(only 0%-commission, WhatsApp-native, concierge + ecosystem). As % of ALL SA transfers the same plan is ~1.2%.</t>
+          <t>Land at prime (biggest rand savings + bond), expand down to upper-mid as the brand scales. As % of ALL SA transfers: ~1.2%.</t>
         </is>
       </c>
     </row>
@@ -4640,6 +5688,698 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="007C3AED"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B1:E32"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="69" t="inlineStr">
+        <is>
+          <t>Cap Table — ownership &amp; dilution</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="B2" s="70" t="inlineStr">
+        <is>
+          <t>Founders 4 x 25%. Amber = editable round inputs; seed linked from Capital &amp; Valuation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="97" t="inlineStr">
+        <is>
+          <t>ROUND INPUTS</t>
+        </is>
+      </c>
+      <c r="C4" s="97" t="n"/>
+      <c r="D4" s="97" t="n"/>
+      <c r="E4" s="97" t="n"/>
+    </row>
+    <row r="5">
+      <c r="B5" s="75" t="inlineStr">
+        <is>
+          <t>Seed pre-money (R)</t>
+        </is>
+      </c>
+      <c r="C5" s="83">
+        <f>'Capital &amp; Valuation'!C20</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="75" t="inlineStr">
+        <is>
+          <t>Seed raise (R)</t>
+        </is>
+      </c>
+      <c r="C6" s="83">
+        <f>'Capital &amp; Valuation'!C9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="72" t="inlineStr">
+        <is>
+          <t>Seed post-money (R)</t>
+        </is>
+      </c>
+      <c r="C7" s="74">
+        <f>C5+C6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="75" t="inlineStr">
+        <is>
+          <t>Series A pre-money (R)</t>
+        </is>
+      </c>
+      <c r="C8" s="98" t="n">
+        <v>250000000</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="75" t="inlineStr">
+        <is>
+          <t>Series A raise (R)</t>
+        </is>
+      </c>
+      <c r="C9" s="98" t="n">
+        <v>50000000</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="72" t="inlineStr">
+        <is>
+          <t>Series A post-money (R)</t>
+        </is>
+      </c>
+      <c r="C10" s="74">
+        <f>C8+C9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="75" t="inlineStr">
+        <is>
+          <t>Exit multiple (x Y5 revenue)</t>
+        </is>
+      </c>
+      <c r="C11" s="109" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="72" t="inlineStr">
+        <is>
+          <t>Exit enterprise value — base Y5 (R)</t>
+        </is>
+      </c>
+      <c r="C12" s="74">
+        <f>Scenarios!D36*C11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="97" t="inlineStr">
+        <is>
+          <t>OWNERSHIP (%)</t>
+        </is>
+      </c>
+      <c r="C14" s="97" t="n"/>
+      <c r="D14" s="97" t="n"/>
+      <c r="E14" s="97" t="n"/>
+    </row>
+    <row r="15">
+      <c r="B15" s="81" t="inlineStr">
+        <is>
+          <t>Holder</t>
+        </is>
+      </c>
+      <c r="C15" s="81" t="inlineStr">
+        <is>
+          <t>Founding</t>
+        </is>
+      </c>
+      <c r="D15" s="81" t="inlineStr">
+        <is>
+          <t>Post-Seed</t>
+        </is>
+      </c>
+      <c r="E15" s="81" t="inlineStr">
+        <is>
+          <t>Post-Series A</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="75" t="inlineStr">
+        <is>
+          <t>Johannes — Commercial Director</t>
+        </is>
+      </c>
+      <c r="C16" s="110" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D16" s="85">
+        <f>C16*($C$5/$C$7)</f>
+        <v/>
+      </c>
+      <c r="E16" s="85">
+        <f>D16*($C$8/$C$10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="75" t="inlineStr">
+        <is>
+          <t>Wilhelm — CTO</t>
+        </is>
+      </c>
+      <c r="C17" s="110" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D17" s="85">
+        <f>C17*($C$5/$C$7)</f>
+        <v/>
+      </c>
+      <c r="E17" s="85">
+        <f>D17*($C$8/$C$10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="75" t="inlineStr">
+        <is>
+          <t>Dean — COO</t>
+        </is>
+      </c>
+      <c r="C18" s="110" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D18" s="85">
+        <f>C18*($C$5/$C$7)</f>
+        <v/>
+      </c>
+      <c r="E18" s="85">
+        <f>D18*($C$8/$C$10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="75" t="inlineStr">
+        <is>
+          <t>Strategic Funder</t>
+        </is>
+      </c>
+      <c r="C19" s="110" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D19" s="85">
+        <f>C19*($C$5/$C$7)</f>
+        <v/>
+      </c>
+      <c r="E19" s="85">
+        <f>D19*($C$8/$C$10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="75" t="inlineStr">
+        <is>
+          <t>Seed Investor</t>
+        </is>
+      </c>
+      <c r="C20" s="110" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="85">
+        <f>$C$6/$C$7</f>
+        <v/>
+      </c>
+      <c r="E20" s="85">
+        <f>D20*($C$8/$C$10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="75" t="inlineStr">
+        <is>
+          <t>Series A Investor</t>
+        </is>
+      </c>
+      <c r="C21" s="110" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="85" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="85">
+        <f>$C$9/$C$10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="72" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C22" s="84">
+        <f>SUM(C16:C21)</f>
+        <v/>
+      </c>
+      <c r="D22" s="84">
+        <f>SUM(D16:D21)</f>
+        <v/>
+      </c>
+      <c r="E22" s="84">
+        <f>SUM(E16:E21)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="97" t="inlineStr">
+        <is>
+          <t>VALUE OF STAKE (R)</t>
+        </is>
+      </c>
+      <c r="C24" s="97" t="n"/>
+      <c r="D24" s="97" t="n"/>
+      <c r="E24" s="97" t="n"/>
+    </row>
+    <row r="25">
+      <c r="B25" s="81" t="inlineStr">
+        <is>
+          <t>Holder</t>
+        </is>
+      </c>
+      <c r="C25" s="81" t="inlineStr">
+        <is>
+          <t>At Seed (R65m)</t>
+        </is>
+      </c>
+      <c r="D25" s="81" t="inlineStr">
+        <is>
+          <t>At Series A</t>
+        </is>
+      </c>
+      <c r="E25" s="81" t="inlineStr">
+        <is>
+          <t>At Exit</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="75" t="inlineStr">
+        <is>
+          <t>Johannes — Commercial Director</t>
+        </is>
+      </c>
+      <c r="C26" s="83">
+        <f>D16*$C$7</f>
+        <v/>
+      </c>
+      <c r="D26" s="83">
+        <f>E16*$C$10</f>
+        <v/>
+      </c>
+      <c r="E26" s="74">
+        <f>E16*$C$12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="75" t="inlineStr">
+        <is>
+          <t>Wilhelm — CTO</t>
+        </is>
+      </c>
+      <c r="C27" s="83">
+        <f>D17*$C$7</f>
+        <v/>
+      </c>
+      <c r="D27" s="83">
+        <f>E17*$C$10</f>
+        <v/>
+      </c>
+      <c r="E27" s="74">
+        <f>E17*$C$12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="75" t="inlineStr">
+        <is>
+          <t>Dean — COO</t>
+        </is>
+      </c>
+      <c r="C28" s="83">
+        <f>D18*$C$7</f>
+        <v/>
+      </c>
+      <c r="D28" s="83">
+        <f>E18*$C$10</f>
+        <v/>
+      </c>
+      <c r="E28" s="74">
+        <f>E18*$C$12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="75" t="inlineStr">
+        <is>
+          <t>Strategic Funder</t>
+        </is>
+      </c>
+      <c r="C29" s="83">
+        <f>D19*$C$7</f>
+        <v/>
+      </c>
+      <c r="D29" s="83">
+        <f>E19*$C$10</f>
+        <v/>
+      </c>
+      <c r="E29" s="74">
+        <f>E19*$C$12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="75" t="inlineStr">
+        <is>
+          <t>Seed Investor</t>
+        </is>
+      </c>
+      <c r="C30" s="83">
+        <f>D20*$C$7</f>
+        <v/>
+      </c>
+      <c r="D30" s="83">
+        <f>E20*$C$10</f>
+        <v/>
+      </c>
+      <c r="E30" s="74">
+        <f>E20*$C$12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="75" t="inlineStr">
+        <is>
+          <t>Series A Investor</t>
+        </is>
+      </c>
+      <c r="C31" s="83">
+        <f>D21*$C$7</f>
+        <v/>
+      </c>
+      <c r="D31" s="83">
+        <f>E21*$C$10</f>
+        <v/>
+      </c>
+      <c r="E31" s="74">
+        <f>E21*$C$12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="72" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C32" s="90">
+        <f>SUM(C26:C31)</f>
+        <v/>
+      </c>
+      <c r="D32" s="90">
+        <f>SUM(D26:D31)</f>
+        <v/>
+      </c>
+      <c r="E32" s="90">
+        <f>SUM(E26:E31)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00F59E0B"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B1:G12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="69" t="inlineStr">
+        <is>
+          <t>Funder Growth — value of each stake by round</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="B2" s="70" t="inlineStr">
+        <is>
+          <t>Value of each holder's equity at Seed, Series A and Exit (base Y5 EV). MoM = exit value / cash invested.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="97" t="inlineStr">
+        <is>
+          <t>Holder</t>
+        </is>
+      </c>
+      <c r="C4" s="97" t="inlineStr">
+        <is>
+          <t>Invested (R)</t>
+        </is>
+      </c>
+      <c r="D4" s="97" t="inlineStr">
+        <is>
+          <t>Value @ Seed</t>
+        </is>
+      </c>
+      <c r="E4" s="97" t="inlineStr">
+        <is>
+          <t>Value @ Series A</t>
+        </is>
+      </c>
+      <c r="F4" s="97" t="inlineStr">
+        <is>
+          <t>Value @ Exit</t>
+        </is>
+      </c>
+      <c r="G4" s="97" t="inlineStr">
+        <is>
+          <t>Exit MoM</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="75" t="inlineStr">
+        <is>
+          <t>Johannes — Commercial Director</t>
+        </is>
+      </c>
+      <c r="C5" s="83" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="83">
+        <f>'Cap Table'!C26</f>
+        <v/>
+      </c>
+      <c r="E5" s="83">
+        <f>'Cap Table'!D26</f>
+        <v/>
+      </c>
+      <c r="F5" s="74">
+        <f>'Cap Table'!E26</f>
+        <v/>
+      </c>
+      <c r="G5" s="70" t="inlineStr">
+        <is>
+          <t>sweat</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="75" t="inlineStr">
+        <is>
+          <t>Wilhelm — CTO</t>
+        </is>
+      </c>
+      <c r="C6" s="83" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="83">
+        <f>'Cap Table'!C27</f>
+        <v/>
+      </c>
+      <c r="E6" s="83">
+        <f>'Cap Table'!D27</f>
+        <v/>
+      </c>
+      <c r="F6" s="74">
+        <f>'Cap Table'!E27</f>
+        <v/>
+      </c>
+      <c r="G6" s="70" t="inlineStr">
+        <is>
+          <t>sweat</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="75" t="inlineStr">
+        <is>
+          <t>Dean — COO</t>
+        </is>
+      </c>
+      <c r="C7" s="83" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="83">
+        <f>'Cap Table'!C28</f>
+        <v/>
+      </c>
+      <c r="E7" s="83">
+        <f>'Cap Table'!D28</f>
+        <v/>
+      </c>
+      <c r="F7" s="74">
+        <f>'Cap Table'!E28</f>
+        <v/>
+      </c>
+      <c r="G7" s="70" t="inlineStr">
+        <is>
+          <t>sweat</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="75" t="inlineStr">
+        <is>
+          <t>Strategic Funder</t>
+        </is>
+      </c>
+      <c r="C8" s="83" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="83">
+        <f>'Cap Table'!C29</f>
+        <v/>
+      </c>
+      <c r="E8" s="83">
+        <f>'Cap Table'!D29</f>
+        <v/>
+      </c>
+      <c r="F8" s="74">
+        <f>'Cap Table'!E29</f>
+        <v/>
+      </c>
+      <c r="G8" s="70" t="inlineStr">
+        <is>
+          <t>sweat</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="75" t="inlineStr">
+        <is>
+          <t>Seed Investor</t>
+        </is>
+      </c>
+      <c r="C9" s="83">
+        <f>'Cap Table'!C6</f>
+        <v/>
+      </c>
+      <c r="D9" s="83">
+        <f>'Cap Table'!C30</f>
+        <v/>
+      </c>
+      <c r="E9" s="83">
+        <f>'Cap Table'!D30</f>
+        <v/>
+      </c>
+      <c r="F9" s="74">
+        <f>'Cap Table'!E30</f>
+        <v/>
+      </c>
+      <c r="G9" s="111">
+        <f>F9/C9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="75" t="inlineStr">
+        <is>
+          <t>Series A Investor</t>
+        </is>
+      </c>
+      <c r="C10" s="83">
+        <f>'Cap Table'!C9</f>
+        <v/>
+      </c>
+      <c r="D10" s="83">
+        <f>'Cap Table'!C31</f>
+        <v/>
+      </c>
+      <c r="E10" s="83">
+        <f>'Cap Table'!D31</f>
+        <v/>
+      </c>
+      <c r="F10" s="74">
+        <f>'Cap Table'!E31</f>
+        <v/>
+      </c>
+      <c r="G10" s="111">
+        <f>F10/C10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="70" t="inlineStr">
+        <is>
+          <t>Founders hold 25% each for sweat; the Strategic Funder is an existing 25% holder. Exit uses the base-case Y5 EV (editable on Cap Table).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
     <tabColor rgb="000EA5E9"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -5007,874 +6747,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00EF4444"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="B1:G18"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="5" customWidth="1" min="4" max="4"/>
-    <col width="5" customWidth="1" min="5" max="5"/>
-    <col width="6" customWidth="1" min="6" max="6"/>
-    <col width="52" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="B1" s="69" t="inlineStr">
-        <is>
-          <t>Risk Register</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="B2" s="70" t="inlineStr">
-        <is>
-          <t>Likelihood (L) &amp; Impact (I): 1=Low, 2=Med, 3=High. Severity = L×I (green ≤2, amber 3–4, red ≥6).</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="B4" s="100" t="inlineStr">
-        <is>
-          <t>Risk</t>
-        </is>
-      </c>
-      <c r="C4" s="100" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D4" s="104" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="E4" s="104" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="F4" s="104" t="inlineStr">
-        <is>
-          <t>Sev</t>
-        </is>
-      </c>
-      <c r="G4" s="100" t="inlineStr">
-        <is>
-          <t>Mitigation</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="B5" s="99" t="inlineStr">
-        <is>
-          <t>ATL marketing doesn't convert to deals (CAC blows out)</t>
-        </is>
-      </c>
-      <c r="C5" s="88" t="inlineStr">
-        <is>
-          <t>Growth</t>
-        </is>
-      </c>
-      <c r="D5" s="105" t="n">
-        <v>2</v>
-      </c>
-      <c r="E5" s="105" t="n">
-        <v>3</v>
-      </c>
-      <c r="F5" s="106">
-        <f>D5*E5</f>
-        <v/>
-      </c>
-      <c r="G5" s="99" t="inlineStr">
-        <is>
-          <t>Pilot ATL in CT before scaling; track CAC payback; throttle spend to cash</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="B6" s="99" t="inlineStr">
-        <is>
-          <t>Prime pool smaller / ~20% share too ambitious</t>
-        </is>
-      </c>
-      <c r="C6" s="88" t="inlineStr">
-        <is>
-          <t>Market</t>
-        </is>
-      </c>
-      <c r="D6" s="105" t="n">
-        <v>2</v>
-      </c>
-      <c r="E6" s="105" t="n">
-        <v>3</v>
-      </c>
-      <c r="F6" s="106">
-        <f>D6*E6</f>
-        <v/>
-      </c>
-      <c r="G6" s="99" t="inlineStr">
-        <is>
-          <t>Confirm prime-pool data; conservative case ≈14% share; widen to upper-mid segment</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" s="99" t="inlineStr">
-        <is>
-          <t>Regulatory — PPRA/FFC, bond-steering, NCA if originating</t>
-        </is>
-      </c>
-      <c r="C7" s="88" t="inlineStr">
-        <is>
-          <t>Regulatory</t>
-        </is>
-      </c>
-      <c r="D7" s="105" t="n">
-        <v>2</v>
-      </c>
-      <c r="E7" s="105" t="n">
-        <v>3</v>
-      </c>
-      <c r="F7" s="106">
-        <f>D7*E7</f>
-        <v/>
-      </c>
-      <c r="G7" s="99" t="inlineStr">
-        <is>
-          <t>Registered practitioner + FFC; multi-bank (no steering); legal sign-off before launch</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" s="99" t="inlineStr">
-        <is>
-          <t>POPIA / data breach (IDs, payslips, bank data)</t>
-        </is>
-      </c>
-      <c r="C8" s="88" t="inlineStr">
-        <is>
-          <t>Compliance</t>
-        </is>
-      </c>
-      <c r="D8" s="105" t="n">
-        <v>2</v>
-      </c>
-      <c r="E8" s="105" t="n">
-        <v>3</v>
-      </c>
-      <c r="F8" s="106">
-        <f>D8*E8</f>
-        <v/>
-      </c>
-      <c r="G8" s="99" t="inlineStr">
-        <is>
-          <t>Encrypt at rest, minimise PII, consent logging, DPAs, security review (already in build)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" s="99" t="inlineStr">
-        <is>
-          <t>Trust/adoption — sellers wary of a new brand for R6m+ sale</t>
-        </is>
-      </c>
-      <c r="C9" s="88" t="inlineStr">
-        <is>
-          <t>Adoption</t>
-        </is>
-      </c>
-      <c r="D9" s="105" t="n">
-        <v>2</v>
-      </c>
-      <c r="E9" s="105" t="n">
-        <v>3</v>
-      </c>
-      <c r="F9" s="106">
-        <f>D9*E9</f>
-        <v/>
-      </c>
-      <c r="G9" s="99" t="inlineStr">
-        <is>
-          <t>Concierge model, panel conveyancers (funds in trust), testimonials, bank-sponsor halo</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="B10" s="99" t="inlineStr">
-        <is>
-          <t>Partner concentration (ooba, sponsor, conveyancers)</t>
-        </is>
-      </c>
-      <c r="C10" s="88" t="inlineStr">
-        <is>
-          <t>Partner</t>
-        </is>
-      </c>
-      <c r="D10" s="105" t="n">
-        <v>2</v>
-      </c>
-      <c r="E10" s="105" t="n">
-        <v>2</v>
-      </c>
-      <c r="F10" s="107">
-        <f>D10*E10</f>
-        <v/>
-      </c>
-      <c r="G10" s="99" t="inlineStr">
-        <is>
-          <t>Multi-bank via ooba; multiple conveyancers; non-exclusive sponsor</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" s="99" t="inlineStr">
-        <is>
-          <t>Incumbent retaliation (portals / agencies cut fees or copy)</t>
-        </is>
-      </c>
-      <c r="C11" s="88" t="inlineStr">
-        <is>
-          <t>Competitive</t>
-        </is>
-      </c>
-      <c r="D11" s="105" t="n">
-        <v>2</v>
-      </c>
-      <c r="E11" s="105" t="n">
-        <v>2</v>
-      </c>
-      <c r="F11" s="107">
-        <f>D11*E11</f>
-        <v/>
-      </c>
-      <c r="G11" s="99" t="inlineStr">
-        <is>
-          <t>Speed + brand + WhatsApp UX + ecosystem lock-in + data advantage</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" s="99" t="inlineStr">
-        <is>
-          <t>AI agents underperform for high-touch prime clients</t>
-        </is>
-      </c>
-      <c r="C12" s="88" t="inlineStr">
-        <is>
-          <t>Operational</t>
-        </is>
-      </c>
-      <c r="D12" s="105" t="n">
-        <v>2</v>
-      </c>
-      <c r="E12" s="105" t="n">
-        <v>2</v>
-      </c>
-      <c r="F12" s="107">
-        <f>D12*E12</f>
-        <v/>
-      </c>
-      <c r="G12" s="99" t="inlineStr">
-        <is>
-          <t>Human-in-the-loop on prime; AI for coordination not advice; QA + escalation</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" s="99" t="inlineStr">
-        <is>
-          <t>Property downturn / rates → fewer transactions</t>
-        </is>
-      </c>
-      <c r="C13" s="88" t="inlineStr">
-        <is>
-          <t>Macro</t>
-        </is>
-      </c>
-      <c r="D13" s="105" t="n">
-        <v>2</v>
-      </c>
-      <c r="E13" s="105" t="n">
-        <v>2</v>
-      </c>
-      <c r="F13" s="107">
-        <f>D13*E13</f>
-        <v/>
-      </c>
-      <c r="G13" s="99" t="inlineStr">
-        <is>
-          <t>Counter-cyclical 0% appeal; lean cost base; flex marketing spend</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" s="99" t="inlineStr">
-        <is>
-          <t>WhatsApp / Meta platform &amp; pricing dependency</t>
-        </is>
-      </c>
-      <c r="C14" s="88" t="inlineStr">
-        <is>
-          <t>Platform</t>
-        </is>
-      </c>
-      <c r="D14" s="105" t="n">
-        <v>1</v>
-      </c>
-      <c r="E14" s="105" t="n">
-        <v>2</v>
-      </c>
-      <c r="F14" s="108">
-        <f>D14*E14</f>
-        <v/>
-      </c>
-      <c r="G14" s="99" t="inlineStr">
-        <is>
-          <t>BSP-agnostic adapter (built); web fallback; monitor Meta pricing</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="99" t="inlineStr">
-        <is>
-          <t>Key-person / small-team dependency</t>
-        </is>
-      </c>
-      <c r="C15" s="88" t="inlineStr">
-        <is>
-          <t>Team</t>
-        </is>
-      </c>
-      <c r="D15" s="105" t="n">
-        <v>2</v>
-      </c>
-      <c r="E15" s="105" t="n">
-        <v>2</v>
-      </c>
-      <c r="F15" s="107">
-        <f>D15*E15</f>
-        <v/>
-      </c>
-      <c r="G15" s="99" t="inlineStr">
-        <is>
-          <t>Document + cross-train; AI leverage; hire on the raise</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" s="99" t="inlineStr">
-        <is>
-          <t>High-margin assumptions hurt the fundraise</t>
-        </is>
-      </c>
-      <c r="C16" s="88" t="inlineStr">
-        <is>
-          <t>Funding</t>
-        </is>
-      </c>
-      <c r="D16" s="105" t="n">
-        <v>2</v>
-      </c>
-      <c r="E16" s="105" t="n">
-        <v>2</v>
-      </c>
-      <c r="F16" s="107">
-        <f>D16*E16</f>
-        <v/>
-      </c>
-      <c r="G16" s="99" t="inlineStr">
-        <is>
-          <t>Lead with conservative case + traction; reinvest-for-growth framing</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="70" t="inlineStr">
-        <is>
-          <t>Top risks (Sev 6): marketing-conversion, prime-share, regulatory, POPIA, trust/adoption — each has an owner action above.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="FF0EA5E9"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="B1:G25"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
-  <cols>
-    <col width="1" customWidth="1" min="1" max="1"/>
-    <col width="53.33203125" customWidth="1" min="2" max="2"/>
-    <col width="16.6640625" customWidth="1" min="3" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="21" customHeight="1">
-      <c r="B1" s="8" t="inlineStr">
-        <is>
-          <t>Ancillary / Ecosystem Revenue — the value of the database</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="B2" s="46" t="inlineStr">
-        <is>
-          <t>Referral &amp; commission streams unlocked by owning the homeowner relationship + data. Optional: toggle into the P&amp;L on Assumptions!C61.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="B4" s="36" t="inlineStr">
-        <is>
-          <t>Revenue stream</t>
-        </is>
-      </c>
-      <c r="C4" s="36" t="inlineStr">
-        <is>
-          <t>Low (R)</t>
-        </is>
-      </c>
-      <c r="D4" s="36" t="inlineStr">
-        <is>
-          <t>High (R)</t>
-        </is>
-      </c>
-      <c r="E4" s="36" t="inlineStr">
-        <is>
-          <t>Midpoint (R)</t>
-        </is>
-      </c>
-      <c r="F4" s="36" t="inlineStr">
-        <is>
-          <t>Attach %</t>
-        </is>
-      </c>
-      <c r="G4" s="36" t="inlineStr">
-        <is>
-          <t>Captured/deal (R)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="B5" s="24" t="inlineStr">
-        <is>
-          <t>Homeowners insurance commission</t>
-        </is>
-      </c>
-      <c r="C5" s="95" t="n">
-        <v>1500</v>
-      </c>
-      <c r="D5" s="95" t="n">
-        <v>4000</v>
-      </c>
-      <c r="E5" s="96">
-        <f>AVERAGE(C5:D5)</f>
-        <v/>
-      </c>
-      <c r="F5" s="49" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="G5" s="96">
-        <f>E5*F5</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="B6" s="24" t="inlineStr">
-        <is>
-          <t>Household contents insurance</t>
-        </is>
-      </c>
-      <c r="C6" s="95" t="n">
-        <v>500</v>
-      </c>
-      <c r="D6" s="95" t="n">
-        <v>2000</v>
-      </c>
-      <c r="E6" s="96">
-        <f>AVERAGE(C6:D6)</f>
-        <v/>
-      </c>
-      <c r="F6" s="49" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="G6" s="96">
-        <f>E6*F6</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" s="24" t="inlineStr">
-        <is>
-          <t>Conveyancing referral/marketing fee (already in core)</t>
-        </is>
-      </c>
-      <c r="C7" s="95" t="n">
-        <v>3000</v>
-      </c>
-      <c r="D7" s="95" t="n">
-        <v>8000</v>
-      </c>
-      <c r="E7" s="96">
-        <f>AVERAGE(C7:D7)</f>
-        <v/>
-      </c>
-      <c r="F7" s="49" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="96">
-        <f>E7*F7</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" s="24" t="inlineStr">
-        <is>
-          <t>Moving company referral</t>
-        </is>
-      </c>
-      <c r="C8" s="95" t="n">
-        <v>500</v>
-      </c>
-      <c r="D8" s="95" t="n">
-        <v>2000</v>
-      </c>
-      <c r="E8" s="96">
-        <f>AVERAGE(C8:D8)</f>
-        <v/>
-      </c>
-      <c r="F8" s="49" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="G8" s="96">
-        <f>E8*F8</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" s="24" t="inlineStr">
-        <is>
-          <t>Fibre / internet installation</t>
-        </is>
-      </c>
-      <c r="C9" s="95" t="n">
-        <v>500</v>
-      </c>
-      <c r="D9" s="95" t="n">
-        <v>1500</v>
-      </c>
-      <c r="E9" s="96">
-        <f>AVERAGE(C9:D9)</f>
-        <v/>
-      </c>
-      <c r="F9" s="49" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="G9" s="96">
-        <f>E9*F9</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="B10" s="24" t="inlineStr">
-        <is>
-          <t>Security system installation</t>
-        </is>
-      </c>
-      <c r="C10" s="95" t="n">
-        <v>1000</v>
-      </c>
-      <c r="D10" s="95" t="n">
-        <v>3000</v>
-      </c>
-      <c r="E10" s="96">
-        <f>AVERAGE(C10:D10)</f>
-        <v/>
-      </c>
-      <c r="F10" s="49" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="G10" s="96">
-        <f>E10*F10</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" s="24" t="inlineStr">
-        <is>
-          <t>Utility connection service</t>
-        </is>
-      </c>
-      <c r="C11" s="95" t="n">
-        <v>250</v>
-      </c>
-      <c r="D11" s="95" t="n">
-        <v>1000</v>
-      </c>
-      <c r="E11" s="96">
-        <f>AVERAGE(C11:D11)</f>
-        <v/>
-      </c>
-      <c r="F11" s="49" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="G11" s="96">
-        <f>E11*F11</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" s="24" t="inlineStr">
-        <is>
-          <t>Home warranty / product upsell</t>
-        </is>
-      </c>
-      <c r="C12" s="95" t="n">
-        <v>500</v>
-      </c>
-      <c r="D12" s="95" t="n">
-        <v>2500</v>
-      </c>
-      <c r="E12" s="96">
-        <f>AVERAGE(C12:D12)</f>
-        <v/>
-      </c>
-      <c r="F12" s="49" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G12" s="96">
-        <f>E12*F12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" s="24" t="inlineStr">
-        <is>
-          <t>Compliance certificates (already in core add-ons)</t>
-        </is>
-      </c>
-      <c r="C13" s="95" t="n">
-        <v>500</v>
-      </c>
-      <c r="D13" s="95" t="n">
-        <v>2000</v>
-      </c>
-      <c r="E13" s="96">
-        <f>AVERAGE(C13:D13)</f>
-        <v/>
-      </c>
-      <c r="F13" s="49" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="96">
-        <f>E13*F13</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" s="24" t="inlineStr">
-        <is>
-          <t>Solar installation referral</t>
-        </is>
-      </c>
-      <c r="C14" s="95" t="n">
-        <v>5000</v>
-      </c>
-      <c r="D14" s="95" t="n">
-        <v>20000</v>
-      </c>
-      <c r="E14" s="96">
-        <f>AVERAGE(C14:D14)</f>
-        <v/>
-      </c>
-      <c r="F14" s="49" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="G14" s="96">
-        <f>E14*F14</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="24" t="inlineStr">
-        <is>
-          <t>Home improvement / renovation referrals</t>
-        </is>
-      </c>
-      <c r="C15" s="95" t="n">
-        <v>2000</v>
-      </c>
-      <c r="D15" s="95" t="n">
-        <v>15000</v>
-      </c>
-      <c r="E15" s="96">
-        <f>AVERAGE(C15:D15)</f>
-        <v/>
-      </c>
-      <c r="F15" s="49" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="G15" s="96">
-        <f>E15*F15</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" s="24" t="inlineStr">
-        <is>
-          <t>Storage solutions referral</t>
-        </is>
-      </c>
-      <c r="C16" s="95" t="n">
-        <v>500</v>
-      </c>
-      <c r="D16" s="95" t="n">
-        <v>2000</v>
-      </c>
-      <c r="E16" s="96">
-        <f>AVERAGE(C16:D16)</f>
-        <v/>
-      </c>
-      <c r="F16" s="49" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G16" s="96">
-        <f>E16*F16</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" s="24" t="inlineStr">
-        <is>
-          <t>Short-term insurance cross-sell (car/business)</t>
-        </is>
-      </c>
-      <c r="C17" s="95" t="n">
-        <v>1000</v>
-      </c>
-      <c r="D17" s="95" t="n">
-        <v>5000</v>
-      </c>
-      <c r="E17" s="96">
-        <f>AVERAGE(C17:D17)</f>
-        <v/>
-      </c>
-      <c r="F17" s="49" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G17" s="96">
-        <f>E17*F17</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="24" t="inlineStr">
-        <is>
-          <t>Life cover linked to the bond</t>
-        </is>
-      </c>
-      <c r="C18" s="95" t="n">
-        <v>2000</v>
-      </c>
-      <c r="D18" s="95" t="n">
-        <v>10000</v>
-      </c>
-      <c r="E18" s="96">
-        <f>AVERAGE(C18:D18)</f>
-        <v/>
-      </c>
-      <c r="F18" s="49" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="G18" s="96">
-        <f>E18*F18</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" s="24" t="inlineStr">
-        <is>
-          <t>Estate planning / will services</t>
-        </is>
-      </c>
-      <c r="C19" s="95" t="n">
-        <v>500</v>
-      </c>
-      <c r="D19" s="95" t="n">
-        <v>2000</v>
-      </c>
-      <c r="E19" s="96">
-        <f>AVERAGE(C19:D19)</f>
-        <v/>
-      </c>
-      <c r="F19" s="49" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G19" s="96">
-        <f>E19*F19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="50" t="inlineStr">
-        <is>
-          <t>FULL ecosystem potential / customer (sum of midpoints)</t>
-        </is>
-      </c>
-      <c r="C21" s="51" t="n"/>
-      <c r="D21" s="51" t="n"/>
-      <c r="E21" s="67">
-        <f>SUM(E5:E19)</f>
-        <v/>
-      </c>
-      <c r="F21" s="51" t="n"/>
-      <c r="G21" s="51" t="n"/>
-    </row>
-    <row r="22">
-      <c r="B22" s="50" t="inlineStr">
-        <is>
-          <t>Realistic ADDITIONAL captured / deal (sum of captured)</t>
-        </is>
-      </c>
-      <c r="C22" s="51" t="n"/>
-      <c r="D22" s="51" t="n"/>
-      <c r="E22" s="51" t="n"/>
-      <c r="F22" s="51" t="n"/>
-      <c r="G22" s="67">
-        <f>SUM(G5:G19)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="46" t="inlineStr">
-        <is>
-          <t>Conveyancing &amp; compliance certs are already counted in the core model (attach set to 0 here to avoid double-counting).</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="B25" s="46" t="inlineStr">
-        <is>
-          <t>Strategic point: each registered customer is worth up to ~R50k of ecosystem referral revenue. Even ~10% capture ≈ R5k/deal — the database is the moat.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/docs/dataroom/sold-direct-model.xlsx
+++ b/docs/dataroom/sold-direct-model.xlsx
@@ -1034,7 +1034,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:H63"/>
+  <dimension ref="B1:H72"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="1" customWidth="1" min="1" max="1"/>
@@ -1073,7 +1073,7 @@
     <row r="5">
       <c r="B5" s="20" t="inlineStr">
         <is>
-          <t>Bond origination referral (% of bond, via ooba)</t>
+          <t>Bond origination referral (% of bond, via ooba — Y1 only)</t>
         </is>
       </c>
       <c r="C5" s="12" t="n">
@@ -1254,27 +1254,27 @@
     <row r="18">
       <c r="B18" s="21" t="inlineStr">
         <is>
-          <t>Origination referral / qualifying deal (R)</t>
+          <t>Origination income / qualifying deal (R)  (Y1 ooba → Y2+ in-house)</t>
         </is>
       </c>
       <c r="C18" s="61">
-        <f>C17*$C$5</f>
+        <f>C17*C67</f>
         <v/>
       </c>
       <c r="D18" s="61">
-        <f>D17*$C$5</f>
+        <f>D17*D67</f>
         <v/>
       </c>
       <c r="E18" s="61">
-        <f>E17*$C$5</f>
+        <f>E17*E67</f>
         <v/>
       </c>
       <c r="F18" s="61">
-        <f>F17*$C$5</f>
+        <f>F17*F67</f>
         <v/>
       </c>
       <c r="G18" s="61">
-        <f>G17*$C$5</f>
+        <f>G17*G67</f>
         <v/>
       </c>
     </row>
@@ -1918,23 +1918,23 @@
         </is>
       </c>
       <c r="C53" s="62">
-        <f>SUM(C48:C52)</f>
+        <f>SUM(C48:C52)+C72</f>
         <v/>
       </c>
       <c r="D53" s="62">
-        <f>SUM(D48:D52)</f>
+        <f>SUM(D48:D52)+D72</f>
         <v/>
       </c>
       <c r="E53" s="62">
-        <f>SUM(E48:E52)</f>
+        <f>SUM(E48:E52)+E72</f>
         <v/>
       </c>
       <c r="F53" s="62">
-        <f>SUM(F48:F52)</f>
+        <f>SUM(F48:F52)+F72</f>
         <v/>
       </c>
       <c r="G53" s="62">
-        <f>SUM(G48:G52)</f>
+        <f>SUM(G48:G52)+G72</f>
         <v/>
       </c>
     </row>
@@ -2023,6 +2023,183 @@
       </c>
       <c r="C63" s="61">
         <f>C61*C62</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" s="9" t="inlineStr">
+        <is>
+          <t>IN-HOUSE BOND ORIGINATION (from Year 2 — direct with banks)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="C66" s="10" t="inlineStr">
+        <is>
+          <t>Y1</t>
+        </is>
+      </c>
+      <c r="D66" s="10" t="inlineStr">
+        <is>
+          <t>Y2</t>
+        </is>
+      </c>
+      <c r="E66" s="10" t="inlineStr">
+        <is>
+          <t>Y3</t>
+        </is>
+      </c>
+      <c r="F66" s="10" t="inlineStr">
+        <is>
+          <t>Y4</t>
+        </is>
+      </c>
+      <c r="G66" s="10" t="inlineStr">
+        <is>
+          <t>Y5</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" s="20" t="inlineStr">
+        <is>
+          <t>Origination rate applied (Y1 ooba referral → Y2+ in-house, direct-to-bank)</t>
+        </is>
+      </c>
+      <c r="C67" s="12">
+        <f>$C$5</f>
+        <v/>
+      </c>
+      <c r="D67" s="12" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="E67" s="12" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="F67" s="12" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G67" s="12" t="n">
+        <v>0.015</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" s="20" t="inlineStr">
+        <is>
+          <t>In-house origination — cost per bonded deal (R)</t>
+        </is>
+      </c>
+      <c r="C68" s="60" t="n">
+        <v>0</v>
+      </c>
+      <c r="D68" s="60" t="n">
+        <v>6000</v>
+      </c>
+      <c r="E68" s="60" t="n">
+        <v>6000</v>
+      </c>
+      <c r="F68" s="60" t="n">
+        <v>6000</v>
+      </c>
+      <c r="G68" s="60" t="n">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" s="20" t="inlineStr">
+        <is>
+          <t>In-house origination — bank-aggregation / licensing base (R/yr)</t>
+        </is>
+      </c>
+      <c r="C69" s="60" t="n">
+        <v>0</v>
+      </c>
+      <c r="D69" s="60" t="n">
+        <v>800000</v>
+      </c>
+      <c r="E69" s="60" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="F69" s="60" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="G69" s="60" t="n">
+        <v>1500000</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" s="20" t="inlineStr">
+        <is>
+          <t>In-house origination — one-off setup / licensing (Y2) (R)</t>
+        </is>
+      </c>
+      <c r="C70" s="60" t="n">
+        <v>0</v>
+      </c>
+      <c r="D70" s="60" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="E70" s="60" t="n">
+        <v>0</v>
+      </c>
+      <c r="F70" s="60" t="n">
+        <v>0</v>
+      </c>
+      <c r="G70" s="60" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" s="22" t="inlineStr">
+        <is>
+          <t>Bonded registered deals (base) = deals x bonded share</t>
+        </is>
+      </c>
+      <c r="C71" s="62">
+        <f>C32*C16</f>
+        <v/>
+      </c>
+      <c r="D71" s="62">
+        <f>D32*D16</f>
+        <v/>
+      </c>
+      <c r="E71" s="62">
+        <f>E32*E16</f>
+        <v/>
+      </c>
+      <c r="F71" s="62">
+        <f>F32*F16</f>
+        <v/>
+      </c>
+      <c r="G71" s="62">
+        <f>G32*G16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" s="22" t="inlineStr">
+        <is>
+          <t>Bond origination cost — in-house (R)</t>
+        </is>
+      </c>
+      <c r="C72" s="62">
+        <f>C71*C68+C69+C70</f>
+        <v/>
+      </c>
+      <c r="D72" s="62">
+        <f>D71*D68+D69+D70</f>
+        <v/>
+      </c>
+      <c r="E72" s="62">
+        <f>E71*E68+E69+E70</f>
+        <v/>
+      </c>
+      <c r="F72" s="62">
+        <f>F71*F68+F69+F70</f>
+        <v/>
+      </c>
+      <c r="G72" s="62">
+        <f>G71*G68+G69+G70</f>
         <v/>
       </c>
     </row>
@@ -2152,7 +2329,7 @@
     <row r="7">
       <c r="B7" s="99" t="inlineStr">
         <is>
-          <t>Regulatory — PPRA/FFC, bond-steering, NCA if originating</t>
+          <t>Regulatory — PPRA/FFC; bond-steering; FAIS/FSP &amp; NCA once originating in-house</t>
         </is>
       </c>
       <c r="C7" s="88" t="inlineStr">
@@ -2172,7 +2349,7 @@
       </c>
       <c r="G7" s="99" t="inlineStr">
         <is>
-          <t>Registered practitioner + FFC; multi-bank (no steering); legal sign-off before launch</t>
+          <t>Registered practitioner + FFC; multi-bank (no steering); FSP accreditation before Y2 switch; legal sign-off before launch</t>
         </is>
       </c>
     </row>
@@ -2419,10 +2596,37 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="B17" s="99" t="inlineStr">
+        <is>
+          <t>In-house bond origination — bank aggregation agreements &amp; FAIS/FSP accreditation (Y2)</t>
+        </is>
+      </c>
+      <c r="C17" s="88" t="inlineStr">
+        <is>
+          <t>Regulatory/Partner</t>
+        </is>
+      </c>
+      <c r="D17" s="105" t="n">
+        <v>2</v>
+      </c>
+      <c r="E17" s="105" t="n">
+        <v>3</v>
+      </c>
+      <c r="F17" s="107">
+        <f>D17*E17</f>
+        <v/>
+      </c>
+      <c r="G17" s="99" t="inlineStr">
+        <is>
+          <t>Y1 via ooba = runway; sign multi-bank aggregation pre-Y2; FSP accreditation; phase-in; ooba fallback if a bank agreement slips</t>
+        </is>
+      </c>
+    </row>
     <row r="18">
       <c r="B18" s="70" t="inlineStr">
         <is>
-          <t>Top risks (Sev 6): marketing-conversion, prime-share, regulatory, POPIA, trust/adoption — each has an owner action above.</t>
+          <t>Top risks (Sev 6): marketing-conversion, prime-share, in-house-origination readiness, regulatory, POPIA, trust/adoption — each has an owner action above.</t>
         </is>
       </c>
     </row>
@@ -2945,7 +3149,7 @@
     <row r="6">
       <c r="B6" s="55" t="inlineStr">
         <is>
-          <t>• Free 0% requires a qualifying &gt;=80% bond via our MULTI-BANK originator (ooba) + our conveyancer. Buyer keeps full rate choice; we earn the origination referral (~0.5% of bond).</t>
+          <t>• Free 0% requires a qualifying &gt;=80% bond + our conveyancer; buyer keeps full rate choice. Y1: placed via our MULTI-BANK originator (ooba) — referral ~0.5% of bond. Y2+: origination goes IN-HOUSE, direct with the banks (full commission ~1.5% of bond, ~3x the referral) — needs bank aggregation agreements + FAIS/FSP accreditation; Y1 via ooba is the runway to secure them.</t>
         </is>
       </c>
     </row>
@@ -3091,7 +3295,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:G20"/>
+  <dimension ref="B1:G21"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="1" customWidth="1" min="1" max="1"/>
@@ -3485,110 +3689,137 @@
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="33" t="inlineStr">
+      <c r="B17" s="24" t="inlineStr">
+        <is>
+          <t>Bond origination (in-house)</t>
+        </is>
+      </c>
+      <c r="C17" s="63">
+        <f>Assumptions!C72</f>
+        <v/>
+      </c>
+      <c r="D17" s="63">
+        <f>Assumptions!D72</f>
+        <v/>
+      </c>
+      <c r="E17" s="63">
+        <f>Assumptions!E72</f>
+        <v/>
+      </c>
+      <c r="F17" s="63">
+        <f>Assumptions!F72</f>
+        <v/>
+      </c>
+      <c r="G17" s="63">
+        <f>Assumptions!G72</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="33" t="inlineStr">
         <is>
           <t>Total operating expenses</t>
         </is>
       </c>
-      <c r="C17" s="65">
-        <f>SUM(C12:C16)</f>
-        <v/>
-      </c>
-      <c r="D17" s="65">
-        <f>SUM(D12:D16)</f>
-        <v/>
-      </c>
-      <c r="E17" s="65">
-        <f>SUM(E12:E16)</f>
-        <v/>
-      </c>
-      <c r="F17" s="65">
-        <f>SUM(F12:F16)</f>
-        <v/>
-      </c>
-      <c r="G17" s="65">
-        <f>SUM(G12:G16)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="30" t="inlineStr">
+      <c r="C18" s="65">
+        <f>SUM(C12:C17)</f>
+        <v/>
+      </c>
+      <c r="D18" s="65">
+        <f>SUM(D12:D17)</f>
+        <v/>
+      </c>
+      <c r="E18" s="65">
+        <f>SUM(E12:E17)</f>
+        <v/>
+      </c>
+      <c r="F18" s="65">
+        <f>SUM(F12:F17)</f>
+        <v/>
+      </c>
+      <c r="G18" s="65">
+        <f>SUM(G12:G17)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="30" t="inlineStr">
         <is>
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="C18" s="64">
-        <f>C10-C17</f>
-        <v/>
-      </c>
-      <c r="D18" s="64">
-        <f>D10-D17</f>
-        <v/>
-      </c>
-      <c r="E18" s="64">
-        <f>E10-E17</f>
-        <v/>
-      </c>
-      <c r="F18" s="64">
-        <f>F10-F17</f>
-        <v/>
-      </c>
-      <c r="G18" s="64">
-        <f>G10-G17</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" s="24" t="inlineStr">
+      <c r="C19" s="64">
+        <f>C10-C18</f>
+        <v/>
+      </c>
+      <c r="D19" s="64">
+        <f>D10-D18</f>
+        <v/>
+      </c>
+      <c r="E19" s="64">
+        <f>E10-E18</f>
+        <v/>
+      </c>
+      <c r="F19" s="64">
+        <f>F10-F18</f>
+        <v/>
+      </c>
+      <c r="G19" s="64">
+        <f>G10-G18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="24" t="inlineStr">
         <is>
           <t>EBITDA margin</t>
         </is>
       </c>
-      <c r="C19" s="5">
-        <f>IF(C8=0,"",C18/C8)</f>
-        <v/>
-      </c>
-      <c r="D19" s="5">
-        <f>IF(D8=0,"",D18/D8)</f>
-        <v/>
-      </c>
-      <c r="E19" s="5">
-        <f>IF(E8=0,"",E18/E8)</f>
-        <v/>
-      </c>
-      <c r="F19" s="5">
-        <f>IF(F8=0,"",F18/F8)</f>
-        <v/>
-      </c>
-      <c r="G19" s="5">
-        <f>IF(G8=0,"",G18/G8)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="33" t="inlineStr">
+      <c r="C20" s="5">
+        <f>IF(C8=0,"",C19/C8)</f>
+        <v/>
+      </c>
+      <c r="D20" s="5">
+        <f>IF(D8=0,"",D19/D8)</f>
+        <v/>
+      </c>
+      <c r="E20" s="5">
+        <f>IF(E8=0,"",E19/E8)</f>
+        <v/>
+      </c>
+      <c r="F20" s="5">
+        <f>IF(F8=0,"",F19/F8)</f>
+        <v/>
+      </c>
+      <c r="G20" s="5">
+        <f>IF(G8=0,"",G19/G8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="33" t="inlineStr">
         <is>
           <t>Cumulative EBITDA (cash proxy)</t>
         </is>
       </c>
-      <c r="C20" s="65">
-        <f>C18</f>
-        <v/>
-      </c>
-      <c r="D20" s="65">
-        <f>C20+D18</f>
-        <v/>
-      </c>
-      <c r="E20" s="65">
-        <f>D20+E18</f>
-        <v/>
-      </c>
-      <c r="F20" s="65">
-        <f>E20+F18</f>
-        <v/>
-      </c>
-      <c r="G20" s="65">
-        <f>F20+G18</f>
+      <c r="C21" s="65">
+        <f>C19</f>
+        <v/>
+      </c>
+      <c r="D21" s="65">
+        <f>C21+D19</f>
+        <v/>
+      </c>
+      <c r="E21" s="65">
+        <f>D21+E19</f>
+        <v/>
+      </c>
+      <c r="F21" s="65">
+        <f>E21+F19</f>
+        <v/>
+      </c>
+      <c r="G21" s="65">
+        <f>F21+G19</f>
         <v/>
       </c>
     </row>

--- a/docs/dataroom/sold-direct-model.xlsx
+++ b/docs/dataroom/sold-direct-model.xlsx
@@ -9,15 +9,16 @@
     <sheet name="Assumptions" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="P&amp;L (Base)" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Scenarios" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Market Sizing" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Capital &amp; Valuation" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Use of Funds" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Cap Table" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Funder Growth" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Competitive Landscape" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Risk Register" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Ancillary Revenue" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Notes &amp; Sources" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="COGS Build" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Market Sizing" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Capital &amp; Valuation" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Use of Funds" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Cap Table" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Funder Growth" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Competitive Landscape" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Risk Register" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Ancillary Revenue" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Notes &amp; Sources" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1" iterateDelta="0.0001"/>
@@ -344,7 +345,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="112">
+  <cellXfs count="114">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -495,6 +496,8 @@
     <xf numFmtId="167" fontId="0" fillId="13" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="13" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="9" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="9" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1093,11 +1096,12 @@
     <row r="7">
       <c r="B7" s="20" t="inlineStr">
         <is>
-          <t>Gross margin</t>
-        </is>
-      </c>
-      <c r="C7" s="12" t="n">
-        <v>0.88</v>
+          <t>Gross margin (derived from COGS Build, blended)</t>
+        </is>
+      </c>
+      <c r="C7" s="12">
+        <f>1-SUM('COGS Build'!C20:G20)/SUM('COGS Build'!C22:G22)</f>
+        <v/>
       </c>
     </row>
     <row r="8">
@@ -2209,6 +2213,378 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="000EA5E9"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B1:H12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="69" t="inlineStr">
+        <is>
+          <t>Competitive Landscape</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="B2" s="70" t="inlineStr">
+        <is>
+          <t>Sold Direct is the only 0%-to-consumer player that monetises the financial ecosystem around the deal via WhatsApp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="100" t="inlineStr">
+        <is>
+          <t>Player</t>
+        </is>
+      </c>
+      <c r="C4" s="100" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="D4" s="100" t="inlineStr">
+        <is>
+          <t>Cost to seller</t>
+        </is>
+      </c>
+      <c r="E4" s="100" t="inlineStr">
+        <is>
+          <t>Channel</t>
+        </is>
+      </c>
+      <c r="F4" s="100" t="inlineStr">
+        <is>
+          <t>Bond / finance</t>
+        </is>
+      </c>
+      <c r="G4" s="100" t="inlineStr">
+        <is>
+          <t>Ecosystem revenue</t>
+        </is>
+      </c>
+      <c r="H4" s="100" t="inlineStr">
+        <is>
+          <t>Segment / status</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="101" t="inlineStr">
+        <is>
+          <t>Sold Direct</t>
+        </is>
+      </c>
+      <c r="C5" s="102" t="inlineStr">
+        <is>
+          <t>0% marketplace + concierge</t>
+        </is>
+      </c>
+      <c r="D5" s="102" t="inlineStr">
+        <is>
+          <t>0% (1% non-partner)</t>
+        </is>
+      </c>
+      <c r="E5" s="102" t="inlineStr">
+        <is>
+          <t>WhatsApp-native</t>
+        </is>
+      </c>
+      <c r="F5" s="102" t="inlineStr">
+        <is>
+          <t>Multi-bank origination referral (core)</t>
+        </is>
+      </c>
+      <c r="G5" s="102" t="inlineStr">
+        <is>
+          <t>Yes — insurance, solar, moving, life cover…</t>
+        </is>
+      </c>
+      <c r="H5" s="102" t="inlineStr">
+        <is>
+          <t>Prime first; launching</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="103" t="inlineStr">
+        <is>
+          <t>Traditional agencies
+(Pam Golding, Seeff, RE/MAX, Rawson)</t>
+        </is>
+      </c>
+      <c r="C6" s="99" t="inlineStr">
+        <is>
+          <t>Full-service agency</t>
+        </is>
+      </c>
+      <c r="D6" s="99" t="inlineStr">
+        <is>
+          <t>5–7% + VAT</t>
+        </is>
+      </c>
+      <c r="E6" s="99" t="inlineStr">
+        <is>
+          <t>Agents + portals</t>
+        </is>
+      </c>
+      <c r="F6" s="99" t="inlineStr">
+        <is>
+          <t>Refer to originators</t>
+        </is>
+      </c>
+      <c r="G6" s="99" t="inlineStr">
+        <is>
+          <t>Limited (referrals)</t>
+        </is>
+      </c>
+      <c r="H6" s="99" t="inlineStr">
+        <is>
+          <t>All; incumbent, high cost</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="103" t="inlineStr">
+        <is>
+          <t>Property24</t>
+        </is>
+      </c>
+      <c r="C7" s="99" t="inlineStr">
+        <is>
+          <t>Listings portal</t>
+        </is>
+      </c>
+      <c r="D7" s="99" t="inlineStr">
+        <is>
+          <t>Portal fees (to agents)</t>
+        </is>
+      </c>
+      <c r="E7" s="99" t="inlineStr">
+        <is>
+          <t>Web / app portal</t>
+        </is>
+      </c>
+      <c r="F7" s="99" t="inlineStr">
+        <is>
+          <t>Bond calculators &amp; leads</t>
+        </is>
+      </c>
+      <c r="G7" s="99" t="inlineStr">
+        <is>
+          <t>Ad / lead revenue</t>
+        </is>
+      </c>
+      <c r="H7" s="99" t="inlineStr">
+        <is>
+          <t>All; dominant portal (Prosus)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="103" t="inlineStr">
+        <is>
+          <t>Private Property</t>
+        </is>
+      </c>
+      <c r="C8" s="99" t="inlineStr">
+        <is>
+          <t>Listings portal</t>
+        </is>
+      </c>
+      <c r="D8" s="99" t="inlineStr">
+        <is>
+          <t>Listing / portal fees</t>
+        </is>
+      </c>
+      <c r="E8" s="99" t="inlineStr">
+        <is>
+          <t>Web portal</t>
+        </is>
+      </c>
+      <c r="F8" s="99" t="inlineStr">
+        <is>
+          <t>Bond referral</t>
+        </is>
+      </c>
+      <c r="G8" s="99" t="inlineStr">
+        <is>
+          <t>Ad / lead revenue</t>
+        </is>
+      </c>
+      <c r="H8" s="99" t="inlineStr">
+        <is>
+          <t>All; #2 portal</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="103" t="inlineStr">
+        <is>
+          <t>PropertyFox</t>
+        </is>
+      </c>
+      <c r="C9" s="99" t="inlineStr">
+        <is>
+          <t>Low-commission hybrid</t>
+        </is>
+      </c>
+      <c r="D9" s="99" t="inlineStr">
+        <is>
+          <t>~1.5% flat</t>
+        </is>
+      </c>
+      <c r="E9" s="99" t="inlineStr">
+        <is>
+          <t>Online + agents</t>
+        </is>
+      </c>
+      <c r="F9" s="99" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G9" s="99" t="inlineStr">
+        <is>
+          <t>Limited</t>
+        </is>
+      </c>
+      <c r="H9" s="99" t="inlineStr">
+        <is>
+          <t>Mid; struggled / sold — cautionary</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="103" t="inlineStr">
+        <is>
+          <t>Leadhome</t>
+        </is>
+      </c>
+      <c r="C10" s="99" t="inlineStr">
+        <is>
+          <t>Fixed-fee online agency</t>
+        </is>
+      </c>
+      <c r="D10" s="99" t="inlineStr">
+        <is>
+          <t>Low fixed fee</t>
+        </is>
+      </c>
+      <c r="E10" s="99" t="inlineStr">
+        <is>
+          <t>Online + agents</t>
+        </is>
+      </c>
+      <c r="F10" s="99" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="99" t="inlineStr">
+        <is>
+          <t>Limited</t>
+        </is>
+      </c>
+      <c r="H10" s="99" t="inlineStr">
+        <is>
+          <t>Mid; wound down — cautionary</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="103" t="inlineStr">
+        <is>
+          <t>ooba / BetterBond</t>
+        </is>
+      </c>
+      <c r="C11" s="99" t="inlineStr">
+        <is>
+          <t>Bond originators</t>
+        </is>
+      </c>
+      <c r="D11" s="99" t="inlineStr">
+        <is>
+          <t>Free to consumer</t>
+        </is>
+      </c>
+      <c r="E11" s="99" t="inlineStr">
+        <is>
+          <t>Web / agents</t>
+        </is>
+      </c>
+      <c r="F11" s="99" t="inlineStr">
+        <is>
+          <t>Core business</t>
+        </is>
+      </c>
+      <c r="G11" s="99" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H11" s="99" t="inlineStr">
+        <is>
+          <t>Bonded buyers — PARTNERS, not rivals</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="103" t="inlineStr">
+        <is>
+          <t>Purplebricks (UK)</t>
+        </is>
+      </c>
+      <c r="C12" s="99" t="inlineStr">
+        <is>
+          <t>Fixed-fee online agency</t>
+        </is>
+      </c>
+      <c r="D12" s="99" t="inlineStr">
+        <is>
+          <t>Fixed fee</t>
+        </is>
+      </c>
+      <c r="E12" s="99" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="F12" s="99" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="99" t="inlineStr">
+        <is>
+          <t>Limited</t>
+        </is>
+      </c>
+      <c r="H12" s="99" t="inlineStr">
+        <is>
+          <t>Defunct: £240m IPO → £1 — CAC warning</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00EF4444"/>
@@ -2635,7 +3011,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FF0EA5E9"/>
@@ -3105,14 +3481,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FF64748B"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:B28"/>
+  <dimension ref="B1:B29"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="1" customWidth="1" min="1" max="1"/>
@@ -3282,6 +3658,13 @@
     </row>
     <row r="28">
       <c r="B28" s="57" t="n"/>
+    </row>
+    <row r="29">
+      <c r="B29" s="54" t="inlineStr">
+        <is>
+          <t>COGS (bottom-up): see the COGS Build tab — ~7 direct per-deal lines (messaging, FICA/KYC, e-sign, property data, listing media &amp; portal syndication, add-on/compliance-cert fulfilment, contingency) + ~0.7% payment processing. Blends to ~12% of revenue (~88% gross margin, now DERIVED on Assumptions!C7). Excludes in-house origination cost (own line) and the concierge team (payroll).</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4649,6 +5032,555 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="FFEF4444"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B1:G28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="52" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="8" t="inlineStr">
+        <is>
+          <t>COGS Build — bottom-up cost of delivering a deal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>Amber = editable input. Grey = calculated. The blended COGS here feeds the derived gross margin on Assumptions!C7.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>PER-DEAL DIRECT COSTS (R)</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>Y1</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>Y2</t>
+        </is>
+      </c>
+      <c r="E4" s="10" t="inlineStr">
+        <is>
+          <t>Y3</t>
+        </is>
+      </c>
+      <c r="F4" s="10" t="inlineStr">
+        <is>
+          <t>Y4</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="inlineStr">
+        <is>
+          <t>Y5</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>Platform &amp; messaging (WhatsApp/BSP, funnel-loaded)</t>
+        </is>
+      </c>
+      <c r="C5" s="16" t="n">
+        <v>400</v>
+      </c>
+      <c r="D5" s="16" t="n">
+        <v>370</v>
+      </c>
+      <c r="E5" s="16" t="n">
+        <v>340</v>
+      </c>
+      <c r="F5" s="16" t="n">
+        <v>320</v>
+      </c>
+      <c r="G5" s="16" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>FICA / KYC / AML + affordability checks</t>
+        </is>
+      </c>
+      <c r="C6" s="16" t="n">
+        <v>250</v>
+      </c>
+      <c r="D6" s="16" t="n">
+        <v>240</v>
+      </c>
+      <c r="E6" s="16" t="n">
+        <v>230</v>
+      </c>
+      <c r="F6" s="16" t="n">
+        <v>225</v>
+      </c>
+      <c r="G6" s="16" t="n">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>E-signature &amp; digital documents</t>
+        </is>
+      </c>
+      <c r="C7" s="16" t="n">
+        <v>180</v>
+      </c>
+      <c r="D7" s="16" t="n">
+        <v>170</v>
+      </c>
+      <c r="E7" s="16" t="n">
+        <v>160</v>
+      </c>
+      <c r="F7" s="16" t="n">
+        <v>155</v>
+      </c>
+      <c r="G7" s="16" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>Property data / AVM / deeds / CMA</t>
+        </is>
+      </c>
+      <c r="C8" s="16" t="n">
+        <v>300</v>
+      </c>
+      <c r="D8" s="16" t="n">
+        <v>285</v>
+      </c>
+      <c r="E8" s="16" t="n">
+        <v>270</v>
+      </c>
+      <c r="F8" s="16" t="n">
+        <v>260</v>
+      </c>
+      <c r="G8" s="16" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>Listing media &amp; portal syndication (amortised incl. unsold)</t>
+        </is>
+      </c>
+      <c r="C9" s="16" t="n">
+        <v>3600</v>
+      </c>
+      <c r="D9" s="16" t="n">
+        <v>3400</v>
+      </c>
+      <c r="E9" s="16" t="n">
+        <v>3200</v>
+      </c>
+      <c r="F9" s="16" t="n">
+        <v>3050</v>
+      </c>
+      <c r="G9" s="16" t="n">
+        <v>2900</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>Add-on / compliance-cert fulfilment (resold services)</t>
+        </is>
+      </c>
+      <c r="C10" s="16" t="n">
+        <v>3900</v>
+      </c>
+      <c r="D10" s="16" t="n">
+        <v>3800</v>
+      </c>
+      <c r="E10" s="16" t="n">
+        <v>3700</v>
+      </c>
+      <c r="F10" s="16" t="n">
+        <v>3600</v>
+      </c>
+      <c r="G10" s="16" t="n">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>Other / contingency &amp; per-deal SaaS</t>
+        </is>
+      </c>
+      <c r="C11" s="16" t="n">
+        <v>600</v>
+      </c>
+      <c r="D11" s="16" t="n">
+        <v>570</v>
+      </c>
+      <c r="E11" s="16" t="n">
+        <v>540</v>
+      </c>
+      <c r="F11" s="16" t="n">
+        <v>520</v>
+      </c>
+      <c r="G11" s="16" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>COGS per deal (R)</t>
+        </is>
+      </c>
+      <c r="C12" s="112">
+        <f>SUM(C5:C11)</f>
+        <v/>
+      </c>
+      <c r="D12" s="112">
+        <f>SUM(D5:D11)</f>
+        <v/>
+      </c>
+      <c r="E12" s="112">
+        <f>SUM(E5:E11)</f>
+        <v/>
+      </c>
+      <c r="F12" s="112">
+        <f>SUM(F5:F11)</f>
+        <v/>
+      </c>
+      <c r="G12" s="112">
+        <f>SUM(G5:G11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>BUILD-UP TO TOTAL COGS</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>Y1</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="inlineStr">
+        <is>
+          <t>Y2</t>
+        </is>
+      </c>
+      <c r="E14" s="10" t="inlineStr">
+        <is>
+          <t>Y3</t>
+        </is>
+      </c>
+      <c r="F14" s="10" t="inlineStr">
+        <is>
+          <t>Y4</t>
+        </is>
+      </c>
+      <c r="G14" s="10" t="inlineStr">
+        <is>
+          <t>Y5</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>Registered deals (base)</t>
+        </is>
+      </c>
+      <c r="C15" s="112">
+        <f>Assumptions!C32</f>
+        <v/>
+      </c>
+      <c r="D15" s="112">
+        <f>Assumptions!D32</f>
+        <v/>
+      </c>
+      <c r="E15" s="112">
+        <f>Assumptions!E32</f>
+        <v/>
+      </c>
+      <c r="F15" s="112">
+        <f>Assumptions!F32</f>
+        <v/>
+      </c>
+      <c r="G15" s="112">
+        <f>Assumptions!G32</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="22" t="inlineStr">
+        <is>
+          <t>Deal-driven COGS (R)</t>
+        </is>
+      </c>
+      <c r="C16" s="112">
+        <f>C12*C15</f>
+        <v/>
+      </c>
+      <c r="D16" s="112">
+        <f>D12*D15</f>
+        <v/>
+      </c>
+      <c r="E16" s="112">
+        <f>E12*E15</f>
+        <v/>
+      </c>
+      <c r="F16" s="112">
+        <f>F12*F15</f>
+        <v/>
+      </c>
+      <c r="G16" s="112">
+        <f>G12*G15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="22" t="inlineStr">
+        <is>
+          <t>Transactional revenue — base (R)</t>
+        </is>
+      </c>
+      <c r="C17" s="112">
+        <f>Assumptions!C23*C15</f>
+        <v/>
+      </c>
+      <c r="D17" s="112">
+        <f>Assumptions!D23*D15</f>
+        <v/>
+      </c>
+      <c r="E17" s="112">
+        <f>Assumptions!E23*E15</f>
+        <v/>
+      </c>
+      <c r="F17" s="112">
+        <f>Assumptions!F23*F15</f>
+        <v/>
+      </c>
+      <c r="G17" s="112">
+        <f>Assumptions!G23*G15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="20" t="inlineStr">
+        <is>
+          <t>Payment processing &amp; risk (% of transactional)</t>
+        </is>
+      </c>
+      <c r="C18" s="12" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="D18" s="12" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="E18" s="12" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="F18" s="12" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="G18" s="12" t="n">
+        <v>0.007</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="22" t="inlineStr">
+        <is>
+          <t>Processing &amp; risk cost (R)</t>
+        </is>
+      </c>
+      <c r="C19" s="112">
+        <f>C17*C18</f>
+        <v/>
+      </c>
+      <c r="D19" s="112">
+        <f>D17*D18</f>
+        <v/>
+      </c>
+      <c r="E19" s="112">
+        <f>E17*E18</f>
+        <v/>
+      </c>
+      <c r="F19" s="112">
+        <f>F17*F18</f>
+        <v/>
+      </c>
+      <c r="G19" s="112">
+        <f>G17*G18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t>TOTAL COGS (R)</t>
+        </is>
+      </c>
+      <c r="C20" s="112">
+        <f>C16+C19</f>
+        <v/>
+      </c>
+      <c r="D20" s="112">
+        <f>D16+D19</f>
+        <v/>
+      </c>
+      <c r="E20" s="112">
+        <f>E16+E19</f>
+        <v/>
+      </c>
+      <c r="F20" s="112">
+        <f>F16+F19</f>
+        <v/>
+      </c>
+      <c r="G20" s="112">
+        <f>G16+G19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="22" t="inlineStr">
+        <is>
+          <t>Bank sponsorship (R, 0 COGS)</t>
+        </is>
+      </c>
+      <c r="C21" s="112">
+        <f>Assumptions!C27</f>
+        <v/>
+      </c>
+      <c r="D21" s="112">
+        <f>Assumptions!D27</f>
+        <v/>
+      </c>
+      <c r="E21" s="112">
+        <f>Assumptions!E27</f>
+        <v/>
+      </c>
+      <c r="F21" s="112">
+        <f>Assumptions!F27</f>
+        <v/>
+      </c>
+      <c r="G21" s="112">
+        <f>Assumptions!G27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="22" t="inlineStr">
+        <is>
+          <t>Total revenue — base (R)</t>
+        </is>
+      </c>
+      <c r="C22" s="112">
+        <f>C17+C21</f>
+        <v/>
+      </c>
+      <c r="D22" s="112">
+        <f>D17+D21</f>
+        <v/>
+      </c>
+      <c r="E22" s="112">
+        <f>E17+E21</f>
+        <v/>
+      </c>
+      <c r="F22" s="112">
+        <f>F17+F21</f>
+        <v/>
+      </c>
+      <c r="G22" s="112">
+        <f>G17+G21</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="22" t="inlineStr">
+        <is>
+          <t>COGS as % of revenue</t>
+        </is>
+      </c>
+      <c r="C23" s="113">
+        <f>IF(C22=0,"",C20/C22)</f>
+        <v/>
+      </c>
+      <c r="D23" s="113">
+        <f>IF(D22=0,"",D20/D22)</f>
+        <v/>
+      </c>
+      <c r="E23" s="113">
+        <f>IF(E22=0,"",E20/E22)</f>
+        <v/>
+      </c>
+      <c r="F23" s="113">
+        <f>IF(F22=0,"",F20/F22)</f>
+        <v/>
+      </c>
+      <c r="G23" s="113">
+        <f>IF(G22=0,"",G20/G22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="22" t="inlineStr">
+        <is>
+          <t>Blended COGS % (5-yr)</t>
+        </is>
+      </c>
+      <c r="C25" s="113">
+        <f>SUM(C20:G20)/SUM(C22:G22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="22" t="inlineStr">
+        <is>
+          <t>Implied blended gross margin</t>
+        </is>
+      </c>
+      <c r="C26" s="113">
+        <f>1-C25</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="1" t="inlineStr">
+        <is>
+          <t>Excludes: in-house bond-origination consultant cost (own opex line) and the concierge team (payroll). Media &amp; add-on fulfilment are the largest lines — validate vs supplier quotes (photographer, CoC inspectors, Property24/Private Property, BSP).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
     <tabColor rgb="000EA5E9"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -5398,7 +6330,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FF7C3AED"/>
@@ -5701,7 +6633,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="007C3AED"/>
@@ -5916,7 +6848,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="007C3AED"/>
@@ -6369,7 +7301,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00F59E0B"/>
@@ -6606,376 +7538,4 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="000EA5E9"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="B1:H12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="26" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="B1" s="69" t="inlineStr">
-        <is>
-          <t>Competitive Landscape</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="B2" s="70" t="inlineStr">
-        <is>
-          <t>Sold Direct is the only 0%-to-consumer player that monetises the financial ecosystem around the deal via WhatsApp.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="B4" s="100" t="inlineStr">
-        <is>
-          <t>Player</t>
-        </is>
-      </c>
-      <c r="C4" s="100" t="inlineStr">
-        <is>
-          <t>Model</t>
-        </is>
-      </c>
-      <c r="D4" s="100" t="inlineStr">
-        <is>
-          <t>Cost to seller</t>
-        </is>
-      </c>
-      <c r="E4" s="100" t="inlineStr">
-        <is>
-          <t>Channel</t>
-        </is>
-      </c>
-      <c r="F4" s="100" t="inlineStr">
-        <is>
-          <t>Bond / finance</t>
-        </is>
-      </c>
-      <c r="G4" s="100" t="inlineStr">
-        <is>
-          <t>Ecosystem revenue</t>
-        </is>
-      </c>
-      <c r="H4" s="100" t="inlineStr">
-        <is>
-          <t>Segment / status</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="B5" s="101" t="inlineStr">
-        <is>
-          <t>Sold Direct</t>
-        </is>
-      </c>
-      <c r="C5" s="102" t="inlineStr">
-        <is>
-          <t>0% marketplace + concierge</t>
-        </is>
-      </c>
-      <c r="D5" s="102" t="inlineStr">
-        <is>
-          <t>0% (1% non-partner)</t>
-        </is>
-      </c>
-      <c r="E5" s="102" t="inlineStr">
-        <is>
-          <t>WhatsApp-native</t>
-        </is>
-      </c>
-      <c r="F5" s="102" t="inlineStr">
-        <is>
-          <t>Multi-bank origination referral (core)</t>
-        </is>
-      </c>
-      <c r="G5" s="102" t="inlineStr">
-        <is>
-          <t>Yes — insurance, solar, moving, life cover…</t>
-        </is>
-      </c>
-      <c r="H5" s="102" t="inlineStr">
-        <is>
-          <t>Prime first; launching</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="B6" s="103" t="inlineStr">
-        <is>
-          <t>Traditional agencies
-(Pam Golding, Seeff, RE/MAX, Rawson)</t>
-        </is>
-      </c>
-      <c r="C6" s="99" t="inlineStr">
-        <is>
-          <t>Full-service agency</t>
-        </is>
-      </c>
-      <c r="D6" s="99" t="inlineStr">
-        <is>
-          <t>5–7% + VAT</t>
-        </is>
-      </c>
-      <c r="E6" s="99" t="inlineStr">
-        <is>
-          <t>Agents + portals</t>
-        </is>
-      </c>
-      <c r="F6" s="99" t="inlineStr">
-        <is>
-          <t>Refer to originators</t>
-        </is>
-      </c>
-      <c r="G6" s="99" t="inlineStr">
-        <is>
-          <t>Limited (referrals)</t>
-        </is>
-      </c>
-      <c r="H6" s="99" t="inlineStr">
-        <is>
-          <t>All; incumbent, high cost</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" s="103" t="inlineStr">
-        <is>
-          <t>Property24</t>
-        </is>
-      </c>
-      <c r="C7" s="99" t="inlineStr">
-        <is>
-          <t>Listings portal</t>
-        </is>
-      </c>
-      <c r="D7" s="99" t="inlineStr">
-        <is>
-          <t>Portal fees (to agents)</t>
-        </is>
-      </c>
-      <c r="E7" s="99" t="inlineStr">
-        <is>
-          <t>Web / app portal</t>
-        </is>
-      </c>
-      <c r="F7" s="99" t="inlineStr">
-        <is>
-          <t>Bond calculators &amp; leads</t>
-        </is>
-      </c>
-      <c r="G7" s="99" t="inlineStr">
-        <is>
-          <t>Ad / lead revenue</t>
-        </is>
-      </c>
-      <c r="H7" s="99" t="inlineStr">
-        <is>
-          <t>All; dominant portal (Prosus)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" s="103" t="inlineStr">
-        <is>
-          <t>Private Property</t>
-        </is>
-      </c>
-      <c r="C8" s="99" t="inlineStr">
-        <is>
-          <t>Listings portal</t>
-        </is>
-      </c>
-      <c r="D8" s="99" t="inlineStr">
-        <is>
-          <t>Listing / portal fees</t>
-        </is>
-      </c>
-      <c r="E8" s="99" t="inlineStr">
-        <is>
-          <t>Web portal</t>
-        </is>
-      </c>
-      <c r="F8" s="99" t="inlineStr">
-        <is>
-          <t>Bond referral</t>
-        </is>
-      </c>
-      <c r="G8" s="99" t="inlineStr">
-        <is>
-          <t>Ad / lead revenue</t>
-        </is>
-      </c>
-      <c r="H8" s="99" t="inlineStr">
-        <is>
-          <t>All; #2 portal</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" s="103" t="inlineStr">
-        <is>
-          <t>PropertyFox</t>
-        </is>
-      </c>
-      <c r="C9" s="99" t="inlineStr">
-        <is>
-          <t>Low-commission hybrid</t>
-        </is>
-      </c>
-      <c r="D9" s="99" t="inlineStr">
-        <is>
-          <t>~1.5% flat</t>
-        </is>
-      </c>
-      <c r="E9" s="99" t="inlineStr">
-        <is>
-          <t>Online + agents</t>
-        </is>
-      </c>
-      <c r="F9" s="99" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G9" s="99" t="inlineStr">
-        <is>
-          <t>Limited</t>
-        </is>
-      </c>
-      <c r="H9" s="99" t="inlineStr">
-        <is>
-          <t>Mid; struggled / sold — cautionary</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="B10" s="103" t="inlineStr">
-        <is>
-          <t>Leadhome</t>
-        </is>
-      </c>
-      <c r="C10" s="99" t="inlineStr">
-        <is>
-          <t>Fixed-fee online agency</t>
-        </is>
-      </c>
-      <c r="D10" s="99" t="inlineStr">
-        <is>
-          <t>Low fixed fee</t>
-        </is>
-      </c>
-      <c r="E10" s="99" t="inlineStr">
-        <is>
-          <t>Online + agents</t>
-        </is>
-      </c>
-      <c r="F10" s="99" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G10" s="99" t="inlineStr">
-        <is>
-          <t>Limited</t>
-        </is>
-      </c>
-      <c r="H10" s="99" t="inlineStr">
-        <is>
-          <t>Mid; wound down — cautionary</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" s="103" t="inlineStr">
-        <is>
-          <t>ooba / BetterBond</t>
-        </is>
-      </c>
-      <c r="C11" s="99" t="inlineStr">
-        <is>
-          <t>Bond originators</t>
-        </is>
-      </c>
-      <c r="D11" s="99" t="inlineStr">
-        <is>
-          <t>Free to consumer</t>
-        </is>
-      </c>
-      <c r="E11" s="99" t="inlineStr">
-        <is>
-          <t>Web / agents</t>
-        </is>
-      </c>
-      <c r="F11" s="99" t="inlineStr">
-        <is>
-          <t>Core business</t>
-        </is>
-      </c>
-      <c r="G11" s="99" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H11" s="99" t="inlineStr">
-        <is>
-          <t>Bonded buyers — PARTNERS, not rivals</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" s="103" t="inlineStr">
-        <is>
-          <t>Purplebricks (UK)</t>
-        </is>
-      </c>
-      <c r="C12" s="99" t="inlineStr">
-        <is>
-          <t>Fixed-fee online agency</t>
-        </is>
-      </c>
-      <c r="D12" s="99" t="inlineStr">
-        <is>
-          <t>Fixed fee</t>
-        </is>
-      </c>
-      <c r="E12" s="99" t="inlineStr">
-        <is>
-          <t>Online</t>
-        </is>
-      </c>
-      <c r="F12" s="99" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G12" s="99" t="inlineStr">
-        <is>
-          <t>Limited</t>
-        </is>
-      </c>
-      <c r="H12" s="99" t="inlineStr">
-        <is>
-          <t>Defunct: £240m IPO → £1 — CAC warning</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/docs/dataroom/sold-direct-model.xlsx
+++ b/docs/dataroom/sold-direct-model.xlsx
@@ -2219,7 +2219,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:H12"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="2" max="2"/>
@@ -2245,6 +2245,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="100" t="inlineStr">
         <is>
@@ -2353,7 +2354,7 @@
       </c>
       <c r="H6" s="99" t="inlineStr">
         <is>
-          <t>All; incumbent, high cost</t>
+          <t>Full-service sellers; established, commission-funded</t>
         </is>
       </c>
     </row>
@@ -2576,6 +2577,13 @@
       <c r="H12" s="99" t="inlineStr">
         <is>
           <t>Defunct: £240m IPO → £1 — CAC warning</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>NOTE: Traditional agents serve the full-service segment - complementary, not a target. Sold Direct serves sellers who choose to sell privately, assisted by our own employed, registered practitioners (PPRA/FFC).</t>
         </is>
       </c>
     </row>
@@ -2813,7 +2821,7 @@
     <row r="11">
       <c r="B11" s="99" t="inlineStr">
         <is>
-          <t>Incumbent retaliation (portals / agencies cut fees or copy)</t>
+          <t>Industry response (portals / agencies compete on price or copy features)</t>
         </is>
       </c>
       <c r="C11" s="88" t="inlineStr">
@@ -2833,7 +2841,7 @@
       </c>
       <c r="G11" s="99" t="inlineStr">
         <is>
-          <t>Speed + brand + WhatsApp UX + ecosystem lock-in + data advantage</t>
+          <t>Position as complementary to full-service agents (private-sale segment only); we employ registered practitioners; no anti-agent marketing; speed + WhatsApp UX + ecosystem + data advantage</t>
         </is>
       </c>
     </row>
@@ -3532,7 +3540,7 @@
     <row r="7">
       <c r="B7" s="55" t="inlineStr">
         <is>
-          <t>• Otherwise a 1% facilitation fee on the price (cash / sub-80% / not using our partners) - still ~6x cheaper than 5-7% agent commission.</t>
+          <t>• Otherwise a 1% facilitation fee on the price (cash / sub-80% / not using our partners) - ~6x less than a typical full-service commission (5-7% + VAT), stated as a neutral benchmark.</t>
         </is>
       </c>
     </row>
@@ -5658,7 +5666,7 @@
     <row r="10">
       <c r="B10" s="71" t="inlineStr">
         <is>
-          <t>1. THE MARKET WE DISRUPT (context)</t>
+          <t>1. THE MARKET CONTEXT (full-service commission pool)</t>
         </is>
       </c>
       <c r="C10" s="71" t="n"/>
@@ -5740,7 +5748,7 @@
       </c>
       <c r="D15" s="70" t="inlineStr">
         <is>
-          <t>~R24bn - the cost we remove</t>
+          <t>~R24bn - what sellers pay for full service (context for the private-sale segment we serve)</t>
         </is>
       </c>
     </row>
@@ -6093,7 +6101,7 @@
     <row r="47">
       <c r="B47" s="71" t="inlineStr">
         <is>
-          <t>6. CONSUMER COMMISSION SAVED (value delivered to sellers)</t>
+          <t>6. CONSUMER VALUE - KEPT VS FULL-SERVICE BENCHMARK (sellers who choose self-service)</t>
         </is>
       </c>
       <c r="C47" s="71" t="n"/>
@@ -6321,7 +6329,7 @@
     <row r="57">
       <c r="B57" s="70" t="inlineStr">
         <is>
-          <t>Sellers carry the commission in SA; buyers benefit via free bond pre-qual, no agent mark-up and a faster, transparent process.</t>
+          <t>On a full-service sale the seller carries the commission; sellers who choose our self-service path keep it. Full-service agents continue to serve those who want them - complementary, not adversarial.</t>
         </is>
       </c>
     </row>
